--- a/Financial Analysis/LOGI.xlsx
+++ b/Financial Analysis/LOGI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242A05D8-8248-4B1D-8CA5-4A8BEC5E0584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA914A0-7041-4EC9-8CAC-0C761392BD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{439F4133-7664-46FF-BA84-0DE877A2D3CB}"/>
   </bookViews>
@@ -271,7 +271,7 @@
     <t>Q425 8K</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -332,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -351,7 +351,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,14 +796,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>78.150000000000006</v>
+        <v>85.53</v>
       </c>
       <c r="E3" s="4">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
         <v>45866</v>
@@ -828,7 +827,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>11644.35</v>
+        <v>12743.97</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -869,7 +868,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>10141.15</v>
+        <v>11240.769999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1323,7 +1322,7 @@
         <v>1142.6100000000001</v>
       </c>
       <c r="AJ3" s="9">
-        <f t="shared" ref="AJ3:AL3" si="0">AF3*1.05</f>
+        <f t="shared" ref="AJ3:AK3" si="0">AF3*1.05</f>
         <v>1171.8</v>
       </c>
       <c r="AK3" s="9">
@@ -1555,12 +1554,12 @@
         <f>SUM(AE4:AH4)</f>
         <v>2582.6999999999998</v>
       </c>
-      <c r="AW4" s="12">
+      <c r="AW4" s="6">
         <f>SUM(AI4:AL4)</f>
         <v>2720.3483699999997</v>
       </c>
       <c r="AX4" s="6">
-        <f t="shared" ref="AW4:BC4" si="3">AX3-AX5</f>
+        <f t="shared" ref="AX4:BC4" si="3">AX3-AX5</f>
         <v>2779.5278784000002</v>
       </c>
       <c r="AY4" s="6">
@@ -1965,7 +1964,7 @@
         <f t="shared" ref="AV6:AV11" si="15">SUM(AE6:AH6)</f>
         <v>814.4</v>
       </c>
-      <c r="AW6" s="12">
+      <c r="AW6" s="6">
         <f t="shared" ref="AW6:AW11" si="16">SUM(AI6:AL6)</f>
         <v>804.20199000000002</v>
       </c>
@@ -2111,7 +2110,7 @@
         <v>79.064999999999998</v>
       </c>
       <c r="AJ7" s="6">
-        <f t="shared" ref="AJ7:AL8" si="19">AF7*1.05</f>
+        <f t="shared" ref="AJ7:AL7" si="19">AF7*1.05</f>
         <v>80.010000000000005</v>
       </c>
       <c r="AK7" s="6">
@@ -2154,7 +2153,7 @@
         <f t="shared" si="15"/>
         <v>309</v>
       </c>
-      <c r="AW7" s="12">
+      <c r="AW7" s="6">
         <f t="shared" si="16"/>
         <v>324.45</v>
       </c>
@@ -2343,7 +2342,7 @@
         <f t="shared" si="15"/>
         <v>164.10000000000002</v>
       </c>
-      <c r="AW8" s="12">
+      <c r="AW8" s="6">
         <f t="shared" si="16"/>
         <v>170.55500000000001</v>
       </c>
@@ -2560,12 +2559,12 @@
         <f t="shared" si="15"/>
         <v>20.200000000000003</v>
       </c>
-      <c r="AW9" s="12">
+      <c r="AW9" s="6">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
       <c r="AX9" s="6">
-        <f t="shared" ref="AW9:BC9" si="25">AW9*1.01</f>
+        <f t="shared" ref="AX9:BC9" si="25">AW9*1.01</f>
         <v>20.2</v>
       </c>
       <c r="AY9" s="6">
@@ -2727,7 +2726,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AW10" s="12">
+      <c r="AW10" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -2899,7 +2898,7 @@
         <f t="shared" si="15"/>
         <v>9.6</v>
       </c>
-      <c r="AW11" s="12">
+      <c r="AW11" s="6">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
@@ -3521,7 +3520,7 @@
         <f>SUM(AE14:AH14)</f>
         <v>-54.999999999999993</v>
       </c>
-      <c r="AW14" s="12">
+      <c r="AW14" s="6">
         <f t="shared" ref="AW14:AW15" si="56">SUM(AI14:AL14)</f>
         <v>-56.65</v>
       </c>
@@ -3706,7 +3705,7 @@
         <f>SUM(AE15:AH15)</f>
         <v>3</v>
       </c>
-      <c r="AW15" s="12">
+      <c r="AW15" s="6">
         <f t="shared" si="56"/>
         <v>8</v>
       </c>
@@ -4107,12 +4106,12 @@
         <f>SUM(AE17:AH17)</f>
         <v>75.400000000000006</v>
       </c>
-      <c r="AW17" s="12">
+      <c r="AW17" s="6">
         <f>SUM(AI17:AL17)</f>
         <v>132.87805879999999</v>
       </c>
       <c r="AX17" s="6">
-        <f t="shared" ref="AW17:BC17" si="73">AX16*0.18</f>
+        <f t="shared" ref="AX17:BC17" si="73">AX16*0.18</f>
         <v>164.25751305599996</v>
       </c>
       <c r="AY17" s="6">
@@ -6983,7 +6982,7 @@
       </c>
       <c r="BI30" s="5">
         <f>Main!D3</f>
-        <v>78.150000000000006</v>
+        <v>85.53</v>
       </c>
     </row>
     <row r="31" spans="2:168" x14ac:dyDescent="0.3">
@@ -6992,7 +6991,7 @@
       </c>
       <c r="BI31" s="11">
         <f>BI29/BI30-1</f>
-        <v>-4.3547613894122761E-2</v>
+        <v>-0.12607559950690628</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">

--- a/Financial Analysis/LOGI.xlsx
+++ b/Financial Analysis/LOGI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA914A0-7041-4EC9-8CAC-0C761392BD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB961E0-B7A9-4FEE-BB2F-B190E906EDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{439F4133-7664-46FF-BA84-0DE877A2D3CB}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>LOGI</t>
   </si>
@@ -266,9 +266,6 @@
   </si>
   <si>
     <t>Q426</t>
-  </si>
-  <si>
-    <t>Q425 8K</t>
   </si>
   <si>
     <t>Slightly overvalued</t>
@@ -372,14 +369,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -396,7 +393,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25283160" y="7620"/>
+          <a:off x="25991820" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -796,17 +793,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>85.53</v>
+        <v>96.92</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45868</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45868</v>
       </c>
       <c r="G3" s="4">
-        <v>45866</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -814,11 +811,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -827,7 +824,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>12743.97</v>
+        <v>14334.468000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -835,11 +832,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1503.2</f>
-        <v>1503.2</v>
+        <f>1487.8</f>
+        <v>1487.8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -850,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -859,7 +856,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>1503.2</v>
+        <v>1487.8</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -868,7 +865,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>11240.769999999999</v>
+        <v>12846.668000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1318,8 +1315,7 @@
         <v>1010.4</v>
       </c>
       <c r="AI3" s="9">
-        <f>AE3*1.05</f>
-        <v>1142.6100000000001</v>
+        <v>1147.7</v>
       </c>
       <c r="AJ3" s="9">
         <f t="shared" ref="AJ3:AK3" si="0">AF3*1.05</f>
@@ -1367,43 +1363,43 @@
       </c>
       <c r="AW3" s="9">
         <f>SUM(AI3:AL3)</f>
-        <v>4772.5410000000002</v>
+        <v>4777.6310000000003</v>
       </c>
       <c r="AX3" s="9">
         <f>AW3*1.04</f>
-        <v>4963.4426400000002</v>
+        <v>4968.7362400000002</v>
       </c>
       <c r="AY3" s="9">
         <f>AX3*1.03</f>
-        <v>5112.3459192</v>
+        <v>5117.7983272000001</v>
       </c>
       <c r="AZ3" s="9">
         <f>AY3*1.02</f>
-        <v>5214.5928375840003</v>
+        <v>5220.1542937439999</v>
       </c>
       <c r="BA3" s="9">
         <f t="shared" ref="BA3:BF3" si="1">AZ3*1.02</f>
-        <v>5318.8846943356803</v>
+        <v>5324.5573796188801</v>
       </c>
       <c r="BB3" s="9">
         <f t="shared" si="1"/>
-        <v>5425.2623882223943</v>
+        <v>5431.0485272112574</v>
       </c>
       <c r="BC3" s="9">
         <f t="shared" si="1"/>
-        <v>5533.7676359868419</v>
+        <v>5539.6694977554826</v>
       </c>
       <c r="BD3" s="9">
         <f t="shared" si="1"/>
-        <v>5644.4429887065789</v>
+        <v>5650.4628877105924</v>
       </c>
       <c r="BE3" s="9">
         <f t="shared" si="1"/>
-        <v>5757.3318484807105</v>
+        <v>5763.4721454648043</v>
       </c>
       <c r="BF3" s="9">
         <f t="shared" si="1"/>
-        <v>5872.478485450325</v>
+        <v>5878.7415883741005</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1507,8 +1503,7 @@
         <v>572.29999999999995</v>
       </c>
       <c r="AI4" s="6">
-        <f>AI3-AI5</f>
-        <v>651.28770000000009</v>
+        <v>666.6</v>
       </c>
       <c r="AJ4" s="6">
         <f t="shared" ref="AJ4:AL4" si="2">AJ3-AJ5</f>
@@ -1556,43 +1551,43 @@
       </c>
       <c r="AW4" s="6">
         <f>SUM(AI4:AL4)</f>
-        <v>2720.3483699999997</v>
+        <v>2735.6606700000002</v>
       </c>
       <c r="AX4" s="6">
         <f t="shared" ref="AX4:BC4" si="3">AX3-AX5</f>
-        <v>2779.5278784000002</v>
+        <v>2782.4922944</v>
       </c>
       <c r="AY4" s="6">
         <f t="shared" si="3"/>
-        <v>2862.913714752</v>
+        <v>2865.9670632319999</v>
       </c>
       <c r="AZ4" s="6">
         <f t="shared" si="3"/>
-        <v>2920.1719890470404</v>
+        <v>2923.28640449664</v>
       </c>
       <c r="BA4" s="6">
         <f t="shared" si="3"/>
-        <v>2978.5754288279809</v>
+        <v>2981.7521325865728</v>
       </c>
       <c r="BB4" s="6">
         <f t="shared" si="3"/>
-        <v>3038.1469374045409</v>
+        <v>3041.3871752383043</v>
       </c>
       <c r="BC4" s="6">
         <f t="shared" si="3"/>
-        <v>3098.9098761526316</v>
+        <v>3102.21491874307</v>
       </c>
       <c r="BD4" s="6">
         <f t="shared" ref="BD4:BF4" si="4">BD3-BD5</f>
-        <v>3160.8880736756842</v>
+        <v>3164.2592171179317</v>
       </c>
       <c r="BE4" s="6">
         <f t="shared" si="4"/>
-        <v>3224.1058351491979</v>
+        <v>3227.5444014602904</v>
       </c>
       <c r="BF4" s="6">
         <f t="shared" si="4"/>
-        <v>3288.587951852182</v>
+        <v>3292.0952894894963</v>
       </c>
     </row>
     <row r="5" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1664,7 +1659,7 @@
         <v>714.80000000000007</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" ref="S5:AH5" si="6">S3-S4</f>
+        <f t="shared" ref="S5:AI5" si="6">S3-S4</f>
         <v>572.99999999999989</v>
       </c>
       <c r="T5" s="9">
@@ -1728,8 +1723,8 @@
         <v>438.1</v>
       </c>
       <c r="AI5" s="9">
-        <f>AI3*0.43</f>
-        <v>491.32230000000004</v>
+        <f t="shared" si="6"/>
+        <v>481.1</v>
       </c>
       <c r="AJ5" s="9">
         <f t="shared" ref="AJ5:AL5" si="7">AJ3*0.43</f>
@@ -1777,43 +1772,43 @@
       </c>
       <c r="AW5" s="9">
         <f t="shared" si="8"/>
-        <v>2052.1926300000005</v>
+        <v>2041.9703300000001</v>
       </c>
       <c r="AX5" s="9">
         <f>AX3*0.44</f>
-        <v>2183.9147616</v>
+        <v>2186.2439456000002</v>
       </c>
       <c r="AY5" s="9">
         <f t="shared" ref="AY5:BF5" si="9">AY3*0.44</f>
-        <v>2249.432204448</v>
+        <v>2251.8312639680003</v>
       </c>
       <c r="AZ5" s="9">
         <f t="shared" si="9"/>
-        <v>2294.42084853696</v>
+        <v>2296.8678892473599</v>
       </c>
       <c r="BA5" s="9">
         <f t="shared" si="9"/>
-        <v>2340.3092655076994</v>
+        <v>2342.8052470323073</v>
       </c>
       <c r="BB5" s="9">
         <f t="shared" si="9"/>
-        <v>2387.1154508178533</v>
+        <v>2389.6613519729531</v>
       </c>
       <c r="BC5" s="9">
         <f t="shared" si="9"/>
-        <v>2434.8577598342104</v>
+        <v>2437.4545790124125</v>
       </c>
       <c r="BD5" s="9">
         <f t="shared" si="9"/>
-        <v>2483.5549150308948</v>
+        <v>2486.2036705926607</v>
       </c>
       <c r="BE5" s="9">
         <f t="shared" si="9"/>
-        <v>2533.2260133315126</v>
+        <v>2535.9277440045139</v>
       </c>
       <c r="BF5" s="9">
         <f t="shared" si="9"/>
-        <v>2583.8905335981431</v>
+        <v>2586.6462988846042</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1917,8 +1912,7 @@
         <v>198.6</v>
       </c>
       <c r="AI6" s="6">
-        <f>AI3*0.17</f>
-        <v>194.24370000000005</v>
+        <v>195.8</v>
       </c>
       <c r="AJ6" s="6">
         <f>AJ3*0.17</f>
@@ -1966,43 +1960,43 @@
       </c>
       <c r="AW6" s="6">
         <f t="shared" ref="AW6:AW11" si="16">SUM(AI6:AL6)</f>
-        <v>804.20199000000002</v>
+        <v>805.75828999999999</v>
       </c>
       <c r="AX6" s="6">
         <f t="shared" ref="AX6:BC6" si="17">AX3*0.16</f>
-        <v>794.15082240000004</v>
+        <v>794.99779840000008</v>
       </c>
       <c r="AY6" s="6">
         <f t="shared" si="17"/>
-        <v>817.97534707199998</v>
+        <v>818.84773235200009</v>
       </c>
       <c r="AZ6" s="6">
         <f t="shared" si="17"/>
-        <v>834.33485401344012</v>
+        <v>835.22468699904005</v>
       </c>
       <c r="BA6" s="6">
         <f t="shared" si="17"/>
-        <v>851.02155109370881</v>
+        <v>851.92918073902081</v>
       </c>
       <c r="BB6" s="6">
         <f t="shared" si="17"/>
-        <v>868.0419821155831</v>
+        <v>868.96776435380116</v>
       </c>
       <c r="BC6" s="6">
         <f t="shared" si="17"/>
-        <v>885.40282175789469</v>
+        <v>886.34711964087728</v>
       </c>
       <c r="BD6" s="6">
         <f t="shared" ref="BD6:BF6" si="18">BD3*0.16</f>
-        <v>903.1108781930526</v>
+        <v>904.07406203369476</v>
       </c>
       <c r="BE6" s="6">
         <f t="shared" si="18"/>
-        <v>921.17309575691365</v>
+        <v>922.15554327436871</v>
       </c>
       <c r="BF6" s="6">
         <f t="shared" si="18"/>
-        <v>939.59655767205197</v>
+        <v>940.59865413985608</v>
       </c>
     </row>
     <row r="7" spans="2:58" x14ac:dyDescent="0.3">
@@ -2106,19 +2100,18 @@
         <v>79.5</v>
       </c>
       <c r="AI7" s="6">
-        <f>AE7*1.05</f>
-        <v>79.064999999999998</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="AJ7" s="6">
-        <f t="shared" ref="AJ7:AL7" si="19">AF7*1.05</f>
-        <v>80.010000000000005</v>
+        <f>AF7*1.04</f>
+        <v>79.248000000000005</v>
       </c>
       <c r="AK7" s="6">
-        <f t="shared" si="19"/>
-        <v>81.900000000000006</v>
+        <f>AG7*1.04</f>
+        <v>81.12</v>
       </c>
       <c r="AL7" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="AJ7:AL7" si="19">AH7*1.05</f>
         <v>83.475000000000009</v>
       </c>
       <c r="AO7" s="6">
@@ -2155,43 +2148,43 @@
       </c>
       <c r="AW7" s="6">
         <f t="shared" si="16"/>
-        <v>324.45</v>
+        <v>318.44300000000004</v>
       </c>
       <c r="AX7" s="6">
-        <f>AW7*1.04</f>
-        <v>337.428</v>
+        <f>AW7*1.03</f>
+        <v>327.99629000000004</v>
       </c>
       <c r="AY7" s="6">
         <f>AX7*1.03</f>
-        <v>347.55083999999999</v>
+        <v>337.83617870000006</v>
       </c>
       <c r="AZ7" s="6">
-        <f>AY7*1.03</f>
-        <v>357.97736520000001</v>
+        <f>AY7*1.02</f>
+        <v>344.5929022740001</v>
       </c>
       <c r="BA7" s="6">
         <f t="shared" ref="BA7:BC7" si="20">AZ7*1.02</f>
-        <v>365.13691250400001</v>
+        <v>351.48476031948013</v>
       </c>
       <c r="BB7" s="6">
         <f t="shared" si="20"/>
-        <v>372.43965075407999</v>
+        <v>358.51445552586972</v>
       </c>
       <c r="BC7" s="6">
         <f t="shared" si="20"/>
-        <v>379.8884437691616</v>
+        <v>365.68474463638711</v>
       </c>
       <c r="BD7" s="6">
         <f t="shared" ref="BD7:BD8" si="21">BC7*1.02</f>
-        <v>387.48621264454482</v>
+        <v>372.99843952911488</v>
       </c>
       <c r="BE7" s="6">
         <f t="shared" ref="BE7:BE8" si="22">BD7*1.02</f>
-        <v>395.23593689743575</v>
+        <v>380.45840831969718</v>
       </c>
       <c r="BF7" s="6">
         <f t="shared" ref="BF7:BF8" si="23">BE7*1.02</f>
-        <v>403.14065563538446</v>
+        <v>388.06757648609113</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -2295,8 +2288,7 @@
         <v>40.299999999999997</v>
       </c>
       <c r="AI8" s="6">
-        <f>AE8*1.05</f>
-        <v>39.375</v>
+        <v>41.8</v>
       </c>
       <c r="AJ8" s="6">
         <f>AF8*1.01</f>
@@ -2344,43 +2336,43 @@
       </c>
       <c r="AW8" s="6">
         <f t="shared" si="16"/>
-        <v>170.55500000000001</v>
+        <v>172.98000000000002</v>
       </c>
       <c r="AX8" s="6">
         <f>AW8*1.04</f>
-        <v>177.37720000000002</v>
+        <v>179.89920000000004</v>
       </c>
       <c r="AY8" s="6">
         <f>AX8*1.03</f>
-        <v>182.69851600000001</v>
+        <v>185.29617600000003</v>
       </c>
       <c r="AZ8" s="6">
         <f>AY8*1.02</f>
-        <v>186.35248632000003</v>
+        <v>189.00209952000003</v>
       </c>
       <c r="BA8" s="6">
         <f t="shared" ref="BA8:BC8" si="24">AZ8*1.02</f>
-        <v>190.07953604640002</v>
+        <v>192.78214151040004</v>
       </c>
       <c r="BB8" s="6">
         <f t="shared" si="24"/>
-        <v>193.88112676732803</v>
+        <v>196.63778434060805</v>
       </c>
       <c r="BC8" s="6">
         <f t="shared" si="24"/>
-        <v>197.7587493026746</v>
+        <v>200.57054002742021</v>
       </c>
       <c r="BD8" s="6">
         <f t="shared" si="21"/>
-        <v>201.71392428872809</v>
+        <v>204.58195082796863</v>
       </c>
       <c r="BE8" s="6">
         <f t="shared" si="22"/>
-        <v>205.74820277450266</v>
+        <v>208.67358984452801</v>
       </c>
       <c r="BF8" s="6">
         <f t="shared" si="23"/>
-        <v>209.86316682999271</v>
+        <v>212.84706164141858</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2516,7 +2508,8 @@
         <v>4.8000000000000007</v>
       </c>
       <c r="AI9" s="6">
-        <v>5</v>
+        <f>2.6+2.1</f>
+        <v>4.7</v>
       </c>
       <c r="AJ9" s="6">
         <v>5</v>
@@ -2561,43 +2554,43 @@
       </c>
       <c r="AW9" s="6">
         <f t="shared" si="16"/>
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="AX9" s="6">
         <f t="shared" ref="AX9:BC9" si="25">AW9*1.01</f>
-        <v>20.2</v>
+        <v>19.896999999999998</v>
       </c>
       <c r="AY9" s="6">
         <f t="shared" si="25"/>
-        <v>20.402000000000001</v>
+        <v>20.095969999999998</v>
       </c>
       <c r="AZ9" s="6">
         <f t="shared" si="25"/>
-        <v>20.606020000000001</v>
+        <v>20.296929699999996</v>
       </c>
       <c r="BA9" s="6">
         <f t="shared" si="25"/>
-        <v>20.8120802</v>
+        <v>20.499898996999995</v>
       </c>
       <c r="BB9" s="6">
         <f t="shared" si="25"/>
-        <v>21.020201002</v>
+        <v>20.704897986969996</v>
       </c>
       <c r="BC9" s="6">
         <f t="shared" si="25"/>
-        <v>21.230403012020002</v>
+        <v>20.911946966839697</v>
       </c>
       <c r="BD9" s="6">
         <f t="shared" ref="BD9" si="26">BC9*1.01</f>
-        <v>21.442707042140203</v>
+        <v>21.121066436508094</v>
       </c>
       <c r="BE9" s="6">
         <f t="shared" ref="BE9" si="27">BD9*1.01</f>
-        <v>21.657134112561604</v>
+        <v>21.332277100873174</v>
       </c>
       <c r="BF9" s="6">
         <f t="shared" ref="BF9" si="28">BE9*1.01</f>
-        <v>21.873705453687219</v>
+        <v>21.545599871881905</v>
       </c>
     </row>
     <row r="10" spans="2:58" x14ac:dyDescent="0.3">
@@ -2855,10 +2848,10 @@
         <v>8.9</v>
       </c>
       <c r="AI11" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" s="6">
         <v>0</v>
@@ -2900,7 +2893,7 @@
       </c>
       <c r="AW11" s="6">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX11" s="6">
         <v>0</v>
@@ -3064,15 +3057,15 @@
       </c>
       <c r="AI12" s="6">
         <f t="shared" ref="AI12:AL12" si="39">SUM(AI6:AI11)</f>
-        <v>317.68370000000004</v>
+        <v>318.89999999999998</v>
       </c>
       <c r="AJ12" s="6">
         <f t="shared" si="39"/>
-        <v>328.858</v>
+        <v>329.096</v>
       </c>
       <c r="AK12" s="6">
         <f t="shared" si="39"/>
-        <v>342.62324999999998</v>
+        <v>341.84325000000001</v>
       </c>
       <c r="AL12" s="6">
         <f t="shared" si="39"/>
@@ -3112,43 +3105,43 @@
       </c>
       <c r="AW12" s="6">
         <f t="shared" si="40"/>
-        <v>1319.2069900000001</v>
+        <v>1319.88129</v>
       </c>
       <c r="AX12" s="6">
         <f t="shared" si="40"/>
-        <v>1329.1560224000002</v>
+        <v>1322.7902884000002</v>
       </c>
       <c r="AY12" s="6">
         <f t="shared" si="40"/>
-        <v>1368.6267030720001</v>
+        <v>1362.0760570520004</v>
       </c>
       <c r="AZ12" s="6">
         <f t="shared" si="40"/>
-        <v>1399.2707255334401</v>
+        <v>1389.1166184930401</v>
       </c>
       <c r="BA12" s="6">
         <f t="shared" si="40"/>
-        <v>1427.050079844109</v>
+        <v>1416.6959815659011</v>
       </c>
       <c r="BB12" s="6">
         <f t="shared" si="40"/>
-        <v>1455.3829606389911</v>
+        <v>1444.8249022072491</v>
       </c>
       <c r="BC12" s="6">
         <f t="shared" si="40"/>
-        <v>1484.2804178417509</v>
+        <v>1473.5143512715244</v>
       </c>
       <c r="BD12" s="6">
         <f t="shared" ref="BD12:BF12" si="41">SUM(BD6:BD11)</f>
-        <v>1513.7537221684659</v>
+        <v>1502.7755188272863</v>
       </c>
       <c r="BE12" s="6">
         <f t="shared" si="41"/>
-        <v>1543.8143695414137</v>
+        <v>1532.6198185394671</v>
       </c>
       <c r="BF12" s="6">
         <f t="shared" si="41"/>
-        <v>1574.4740855911164</v>
+        <v>1563.0588921392477</v>
       </c>
     </row>
     <row r="13" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3285,15 +3278,15 @@
       </c>
       <c r="AI13" s="9">
         <f t="shared" ref="AI13:AL13" si="52">AI5-AI12</f>
-        <v>173.6386</v>
+        <v>162.20000000000005</v>
       </c>
       <c r="AJ13" s="9">
         <f t="shared" si="52"/>
-        <v>175.01599999999996</v>
+        <v>174.77799999999996</v>
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="52"/>
-        <v>262.5222</v>
+        <v>263.30219999999997</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="52"/>
@@ -3333,43 +3326,43 @@
       </c>
       <c r="AW13" s="9">
         <f t="shared" si="53"/>
-        <v>732.98564000000033</v>
+        <v>722.08904000000007</v>
       </c>
       <c r="AX13" s="9">
         <f t="shared" si="53"/>
-        <v>854.75873919999981</v>
+        <v>863.45365719999995</v>
       </c>
       <c r="AY13" s="9">
         <f t="shared" si="53"/>
-        <v>880.80550137599994</v>
+        <v>889.75520691599991</v>
       </c>
       <c r="AZ13" s="9">
         <f t="shared" si="53"/>
-        <v>895.15012300351987</v>
+        <v>907.75127075431988</v>
       </c>
       <c r="BA13" s="9">
         <f t="shared" si="53"/>
-        <v>913.25918566359042</v>
+        <v>926.10926546640621</v>
       </c>
       <c r="BB13" s="9">
         <f t="shared" si="53"/>
-        <v>931.73249017886224</v>
+        <v>944.83644976570395</v>
       </c>
       <c r="BC13" s="9">
         <f t="shared" si="53"/>
-        <v>950.57734199245942</v>
+        <v>963.94022774088808</v>
       </c>
       <c r="BD13" s="9">
         <f t="shared" ref="BD13:BF13" si="54">BD5-BD12</f>
-        <v>969.80119286242893</v>
+        <v>983.42815176537442</v>
       </c>
       <c r="BE13" s="9">
         <f t="shared" si="54"/>
-        <v>989.41164379009888</v>
+        <v>1003.3079254650468</v>
       </c>
       <c r="BF13" s="9">
         <f t="shared" si="54"/>
-        <v>1009.4164480070267</v>
+        <v>1023.5874067453565</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3473,20 +3466,19 @@
         <v>-12.4</v>
       </c>
       <c r="AI14" s="6">
-        <f>AE14*1.03</f>
-        <v>-16.274000000000001</v>
+        <v>-11.2</v>
       </c>
       <c r="AJ14" s="6">
-        <f t="shared" ref="AJ14:AL14" si="55">AF14*1.03</f>
-        <v>-15.038</v>
+        <f>AI14*1.03</f>
+        <v>-11.536</v>
       </c>
       <c r="AK14" s="6">
-        <f t="shared" si="55"/>
-        <v>-12.565999999999999</v>
+        <f t="shared" ref="AK14:AL14" si="55">AJ14*1.03</f>
+        <v>-11.88208</v>
       </c>
       <c r="AL14" s="6">
         <f t="shared" si="55"/>
-        <v>-12.772</v>
+        <v>-12.2385424</v>
       </c>
       <c r="AO14" s="6">
         <f>SUM(C14:F14)</f>
@@ -3522,43 +3514,43 @@
       </c>
       <c r="AW14" s="6">
         <f t="shared" ref="AW14:AW15" si="56">SUM(AI14:AL14)</f>
-        <v>-56.65</v>
+        <v>-46.856622399999999</v>
       </c>
       <c r="AX14" s="6">
         <f t="shared" ref="AX14:BF14" si="57">AW14*1.02</f>
-        <v>-57.783000000000001</v>
+        <v>-47.793754847999999</v>
       </c>
       <c r="AY14" s="6">
         <f t="shared" si="57"/>
-        <v>-58.938660000000006</v>
+        <v>-48.749629944959999</v>
       </c>
       <c r="AZ14" s="6">
         <f t="shared" si="57"/>
-        <v>-60.117433200000008</v>
+        <v>-49.724622543859198</v>
       </c>
       <c r="BA14" s="6">
         <f t="shared" si="57"/>
-        <v>-61.319781864000007</v>
+        <v>-50.71911499473638</v>
       </c>
       <c r="BB14" s="6">
         <f t="shared" si="57"/>
-        <v>-62.546177501280006</v>
+        <v>-51.733497294631107</v>
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="57"/>
-        <v>-63.79710105130561</v>
+        <v>-52.768167240523731</v>
       </c>
       <c r="BD14" s="6">
         <f t="shared" si="57"/>
-        <v>-65.073043072331728</v>
+        <v>-53.823530585334204</v>
       </c>
       <c r="BE14" s="6">
         <f t="shared" si="57"/>
-        <v>-66.374503933778371</v>
+        <v>-54.900001197040886</v>
       </c>
       <c r="BF14" s="6">
         <f t="shared" si="57"/>
-        <v>-67.701994012453937</v>
+        <v>-55.998001220981706</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3662,7 +3654,7 @@
         <v>0.1</v>
       </c>
       <c r="AI15" s="6">
-        <v>2</v>
+        <v>-1.2</v>
       </c>
       <c r="AJ15" s="6">
         <v>2</v>
@@ -3707,7 +3699,7 @@
       </c>
       <c r="AW15" s="6">
         <f t="shared" si="56"/>
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AX15" s="6">
         <v>0</v>
@@ -3871,19 +3863,19 @@
       </c>
       <c r="AI16" s="9">
         <f t="shared" ref="AI16:AL16" si="68">AI13-AI14-AI15</f>
-        <v>187.9126</v>
+        <v>174.60000000000002</v>
       </c>
       <c r="AJ16" s="9">
         <f t="shared" si="68"/>
-        <v>188.05399999999997</v>
+        <v>184.31399999999996</v>
       </c>
       <c r="AK16" s="9">
         <f t="shared" si="68"/>
-        <v>273.08819999999997</v>
+        <v>273.18427999999994</v>
       </c>
       <c r="AL16" s="9">
         <f t="shared" si="68"/>
-        <v>132.58084000000002</v>
+        <v>132.04738240000003</v>
       </c>
       <c r="AO16" s="9">
         <f t="shared" ref="AO16:AT16" si="69">AO13-AO14-AO15</f>
@@ -3919,43 +3911,43 @@
       </c>
       <c r="AW16" s="9">
         <f t="shared" si="70"/>
-        <v>781.63564000000031</v>
+        <v>764.14566240000011</v>
       </c>
       <c r="AX16" s="9">
         <f t="shared" si="70"/>
-        <v>912.54173919999982</v>
+        <v>911.247412048</v>
       </c>
       <c r="AY16" s="9">
         <f t="shared" si="70"/>
-        <v>939.74416137599997</v>
+        <v>938.50483686095993</v>
       </c>
       <c r="AZ16" s="9">
         <f t="shared" si="70"/>
-        <v>955.26755620351992</v>
+        <v>957.47589329817902</v>
       </c>
       <c r="BA16" s="9">
         <f t="shared" si="70"/>
-        <v>974.57896752759041</v>
+        <v>976.82838046114261</v>
       </c>
       <c r="BB16" s="9">
         <f t="shared" si="70"/>
-        <v>994.27866768014223</v>
+        <v>996.56994706033504</v>
       </c>
       <c r="BC16" s="9">
         <f t="shared" si="70"/>
-        <v>1014.374443043765</v>
+        <v>1016.7083949814119</v>
       </c>
       <c r="BD16" s="9">
         <f t="shared" ref="BD16:BF16" si="71">BD13-BD14-BD15</f>
-        <v>1034.8742359347607</v>
+        <v>1037.2516823507087</v>
       </c>
       <c r="BE16" s="9">
         <f t="shared" si="71"/>
-        <v>1055.7861477238773</v>
+        <v>1058.2079266620876</v>
       </c>
       <c r="BF16" s="9">
         <f t="shared" si="71"/>
-        <v>1077.1184420194807</v>
+        <v>1079.5854079663382</v>
       </c>
     </row>
     <row r="17" spans="2:168" x14ac:dyDescent="0.3">
@@ -4059,20 +4051,19 @@
         <v>-25.9</v>
       </c>
       <c r="AI17" s="6">
-        <f>AI16*0.17</f>
-        <v>31.945142000000001</v>
+        <v>28.5</v>
       </c>
       <c r="AJ17" s="6">
         <f t="shared" ref="AJ17:AL17" si="72">AJ16*0.17</f>
-        <v>31.969179999999998</v>
+        <v>31.333379999999995</v>
       </c>
       <c r="AK17" s="6">
         <f t="shared" si="72"/>
-        <v>46.424993999999998</v>
+        <v>46.441327599999994</v>
       </c>
       <c r="AL17" s="6">
         <f t="shared" si="72"/>
-        <v>22.538742800000005</v>
+        <v>22.448055008000008</v>
       </c>
       <c r="AO17" s="6">
         <f>SUM(C17:F17)</f>
@@ -4108,43 +4099,43 @@
       </c>
       <c r="AW17" s="6">
         <f>SUM(AI17:AL17)</f>
-        <v>132.87805879999999</v>
+        <v>128.72276260799998</v>
       </c>
       <c r="AX17" s="6">
         <f t="shared" ref="AX17:BC17" si="73">AX16*0.18</f>
-        <v>164.25751305599996</v>
+        <v>164.02453416864</v>
       </c>
       <c r="AY17" s="6">
         <f t="shared" si="73"/>
-        <v>169.15394904767999</v>
+        <v>168.93087063497279</v>
       </c>
       <c r="AZ17" s="6">
         <f t="shared" si="73"/>
-        <v>171.94816011663357</v>
+        <v>172.34566079367221</v>
       </c>
       <c r="BA17" s="6">
         <f t="shared" si="73"/>
-        <v>175.42421415496628</v>
+        <v>175.82910848300565</v>
       </c>
       <c r="BB17" s="6">
         <f t="shared" si="73"/>
-        <v>178.97016018242559</v>
+        <v>179.38259047086029</v>
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="73"/>
-        <v>182.5873997478777</v>
+        <v>183.00751109665413</v>
       </c>
       <c r="BD17" s="6">
         <f t="shared" ref="BD17:BF17" si="74">BD16*0.18</f>
-        <v>186.27736246825691</v>
+        <v>186.70530282312757</v>
       </c>
       <c r="BE17" s="6">
         <f t="shared" si="74"/>
-        <v>190.0415065902979</v>
+        <v>190.47742679917576</v>
       </c>
       <c r="BF17" s="6">
         <f t="shared" si="74"/>
-        <v>193.88131956350651</v>
+        <v>194.32537343394085</v>
       </c>
     </row>
     <row r="18" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4281,19 +4272,19 @@
       </c>
       <c r="AI18" s="9">
         <f t="shared" ref="AI18:AL18" si="85">AI16-AI17</f>
-        <v>155.96745799999999</v>
+        <v>146.10000000000002</v>
       </c>
       <c r="AJ18" s="9">
         <f t="shared" si="85"/>
-        <v>156.08481999999998</v>
+        <v>152.98061999999996</v>
       </c>
       <c r="AK18" s="9">
         <f t="shared" si="85"/>
-        <v>226.66320599999997</v>
+        <v>226.74295239999995</v>
       </c>
       <c r="AL18" s="9">
         <f t="shared" si="85"/>
-        <v>110.04209720000001</v>
+        <v>109.59932739200002</v>
       </c>
       <c r="AO18" s="9">
         <f t="shared" ref="AO18:AT18" si="86">AO16-AO17</f>
@@ -4329,483 +4320,483 @@
       </c>
       <c r="AW18" s="9">
         <f t="shared" si="87"/>
-        <v>648.75758120000035</v>
+        <v>635.42289979200018</v>
       </c>
       <c r="AX18" s="9">
         <f t="shared" si="87"/>
-        <v>748.28422614399983</v>
+        <v>747.22287787936</v>
       </c>
       <c r="AY18" s="9">
         <f t="shared" si="87"/>
-        <v>770.59021232831992</v>
+        <v>769.57396622598708</v>
       </c>
       <c r="AZ18" s="9">
         <f t="shared" si="87"/>
-        <v>783.3193960868864</v>
+        <v>785.13023250450681</v>
       </c>
       <c r="BA18" s="9">
         <f t="shared" si="87"/>
-        <v>799.1547533726241</v>
+        <v>800.9992719781369</v>
       </c>
       <c r="BB18" s="9">
         <f t="shared" si="87"/>
-        <v>815.30850749771662</v>
+        <v>817.1873565894748</v>
       </c>
       <c r="BC18" s="9">
         <f t="shared" si="87"/>
-        <v>831.78704329588732</v>
+        <v>833.70088388475779</v>
       </c>
       <c r="BD18" s="9">
         <f t="shared" ref="BD18:BF18" si="88">BD16-BD17</f>
-        <v>848.59687346650378</v>
+        <v>850.54637952758117</v>
       </c>
       <c r="BE18" s="9">
         <f t="shared" si="88"/>
-        <v>865.74464113357942</v>
+        <v>867.73049986291187</v>
       </c>
       <c r="BF18" s="9">
         <f t="shared" si="88"/>
-        <v>883.23712245597414</v>
+        <v>885.2600345323973</v>
       </c>
       <c r="BG18" s="1">
         <f>BF18*(1+$BI$24)</f>
-        <v>874.40475123141437</v>
+        <v>876.40743418707336</v>
       </c>
       <c r="BH18" s="1">
         <f t="shared" ref="BH18:DS18" si="89">BG18*(1+$BI$24)</f>
-        <v>865.66070371910018</v>
+        <v>867.64335984520267</v>
       </c>
       <c r="BI18" s="1">
         <f t="shared" si="89"/>
-        <v>857.00409668190912</v>
+        <v>858.96692624675063</v>
       </c>
       <c r="BJ18" s="1">
         <f t="shared" si="89"/>
-        <v>848.43405571509004</v>
+        <v>850.37725698428312</v>
       </c>
       <c r="BK18" s="1">
         <f t="shared" si="89"/>
-        <v>839.94971515793918</v>
+        <v>841.87348441444033</v>
       </c>
       <c r="BL18" s="1">
         <f t="shared" si="89"/>
-        <v>831.55021800635973</v>
+        <v>833.45474957029592</v>
       </c>
       <c r="BM18" s="1">
         <f t="shared" si="89"/>
-        <v>823.23471582629611</v>
+        <v>825.12020207459295</v>
       </c>
       <c r="BN18" s="1">
         <f t="shared" si="89"/>
-        <v>815.00236866803311</v>
+        <v>816.869000053847</v>
       </c>
       <c r="BO18" s="1">
         <f t="shared" si="89"/>
-        <v>806.85234498135276</v>
+        <v>808.7003100533085</v>
       </c>
       <c r="BP18" s="1">
         <f t="shared" si="89"/>
-        <v>798.78382153153927</v>
+        <v>800.61330695277536</v>
       </c>
       <c r="BQ18" s="1">
         <f t="shared" si="89"/>
-        <v>790.7959833162239</v>
+        <v>792.60717388324758</v>
       </c>
       <c r="BR18" s="1">
         <f t="shared" si="89"/>
-        <v>782.8880234830616</v>
+        <v>784.68110214441515</v>
       </c>
       <c r="BS18" s="1">
         <f t="shared" si="89"/>
-        <v>775.05914324823095</v>
+        <v>776.83429112297097</v>
       </c>
       <c r="BT18" s="1">
         <f t="shared" si="89"/>
-        <v>767.30855181574861</v>
+        <v>769.06594821174122</v>
       </c>
       <c r="BU18" s="1">
         <f t="shared" si="89"/>
-        <v>759.63546629759117</v>
+        <v>761.37528872962378</v>
       </c>
       <c r="BV18" s="1">
         <f t="shared" si="89"/>
-        <v>752.03911163461521</v>
+        <v>753.76153584232748</v>
       </c>
       <c r="BW18" s="1">
         <f t="shared" si="89"/>
-        <v>744.51872051826911</v>
+        <v>746.22392048390418</v>
       </c>
       <c r="BX18" s="1">
         <f t="shared" si="89"/>
-        <v>737.07353331308639</v>
+        <v>738.7616812790651</v>
       </c>
       <c r="BY18" s="1">
         <f t="shared" si="89"/>
-        <v>729.70279797995556</v>
+        <v>731.37406446627449</v>
       </c>
       <c r="BZ18" s="1">
         <f t="shared" si="89"/>
-        <v>722.40577000015605</v>
+        <v>724.06032382161175</v>
       </c>
       <c r="CA18" s="1">
         <f t="shared" si="89"/>
-        <v>715.18171230015446</v>
+        <v>716.81972058339568</v>
       </c>
       <c r="CB18" s="1">
         <f t="shared" si="89"/>
-        <v>708.02989517715287</v>
+        <v>709.65152337756172</v>
       </c>
       <c r="CC18" s="1">
         <f t="shared" si="89"/>
-        <v>700.94959622538136</v>
+        <v>702.55500814378604</v>
       </c>
       <c r="CD18" s="1">
         <f t="shared" si="89"/>
-        <v>693.94010026312753</v>
+        <v>695.52945806234823</v>
       </c>
       <c r="CE18" s="1">
         <f t="shared" si="89"/>
-        <v>687.00069926049628</v>
+        <v>688.57416348172478</v>
       </c>
       <c r="CF18" s="1">
         <f t="shared" si="89"/>
-        <v>680.13069226789128</v>
+        <v>681.68842184690754</v>
       </c>
       <c r="CG18" s="1">
         <f t="shared" si="89"/>
-        <v>673.32938534521236</v>
+        <v>674.87153762843843</v>
       </c>
       <c r="CH18" s="1">
         <f t="shared" si="89"/>
-        <v>666.59609149176026</v>
+        <v>668.12282225215404</v>
       </c>
       <c r="CI18" s="1">
         <f t="shared" si="89"/>
-        <v>659.93013057684266</v>
+        <v>661.44159402963248</v>
       </c>
       <c r="CJ18" s="1">
         <f t="shared" si="89"/>
-        <v>653.33082927107421</v>
+        <v>654.82717808933614</v>
       </c>
       <c r="CK18" s="1">
         <f t="shared" si="89"/>
-        <v>646.79752097836342</v>
+        <v>648.27890630844274</v>
       </c>
       <c r="CL18" s="1">
         <f t="shared" si="89"/>
-        <v>640.32954576857981</v>
+        <v>641.79611724535835</v>
       </c>
       <c r="CM18" s="1">
         <f t="shared" si="89"/>
-        <v>633.92625031089403</v>
+        <v>635.37815607290474</v>
       </c>
       <c r="CN18" s="1">
         <f t="shared" si="89"/>
-        <v>627.58698780778514</v>
+        <v>629.02437451217565</v>
       </c>
       <c r="CO18" s="1">
         <f t="shared" si="89"/>
-        <v>621.31111792970728</v>
+        <v>622.7341307670539</v>
       </c>
       <c r="CP18" s="1">
         <f t="shared" si="89"/>
-        <v>615.09800675041015</v>
+        <v>616.5067894593833</v>
       </c>
       <c r="CQ18" s="1">
         <f t="shared" si="89"/>
-        <v>608.94702668290608</v>
+        <v>610.34172156478951</v>
       </c>
       <c r="CR18" s="1">
         <f t="shared" si="89"/>
-        <v>602.85755641607705</v>
+        <v>604.23830434914157</v>
       </c>
       <c r="CS18" s="1">
         <f t="shared" si="89"/>
-        <v>596.8289808519163</v>
+        <v>598.19592130565013</v>
       </c>
       <c r="CT18" s="1">
         <f t="shared" si="89"/>
-        <v>590.86069104339708</v>
+        <v>592.21396209259365</v>
       </c>
       <c r="CU18" s="1">
         <f t="shared" si="89"/>
-        <v>584.95208413296314</v>
+        <v>586.29182247166773</v>
       </c>
       <c r="CV18" s="1">
         <f t="shared" si="89"/>
-        <v>579.10256329163349</v>
+        <v>580.42890424695099</v>
       </c>
       <c r="CW18" s="1">
         <f t="shared" si="89"/>
-        <v>573.31153765871716</v>
+        <v>574.62461520448153</v>
       </c>
       <c r="CX18" s="1">
         <f t="shared" si="89"/>
-        <v>567.57842228212996</v>
+        <v>568.87836905243671</v>
       </c>
       <c r="CY18" s="1">
         <f t="shared" si="89"/>
-        <v>561.90263805930863</v>
+        <v>563.18958536191235</v>
       </c>
       <c r="CZ18" s="1">
         <f t="shared" si="89"/>
-        <v>556.28361167871549</v>
+        <v>557.55768950829327</v>
       </c>
       <c r="DA18" s="1">
         <f t="shared" si="89"/>
-        <v>550.72077556192835</v>
+        <v>551.98211261321035</v>
       </c>
       <c r="DB18" s="1">
         <f t="shared" si="89"/>
-        <v>545.21356780630902</v>
+        <v>546.46229148707823</v>
       </c>
       <c r="DC18" s="1">
         <f t="shared" si="89"/>
-        <v>539.76143212824593</v>
+        <v>540.99766857220743</v>
       </c>
       <c r="DD18" s="1">
         <f t="shared" si="89"/>
-        <v>534.36381780696343</v>
+        <v>535.58769188648535</v>
       </c>
       <c r="DE18" s="1">
         <f t="shared" si="89"/>
-        <v>529.02017962889374</v>
+        <v>530.23181496762049</v>
       </c>
       <c r="DF18" s="1">
         <f t="shared" si="89"/>
-        <v>523.72997783260485</v>
+        <v>524.92949681794425</v>
       </c>
       <c r="DG18" s="1">
         <f t="shared" si="89"/>
-        <v>518.49267805427883</v>
+        <v>519.68020184976479</v>
       </c>
       <c r="DH18" s="1">
         <f t="shared" si="89"/>
-        <v>513.30775127373602</v>
+        <v>514.48339983126709</v>
       </c>
       <c r="DI18" s="1">
         <f t="shared" si="89"/>
-        <v>508.17467376099864</v>
+        <v>509.33856583295443</v>
       </c>
       <c r="DJ18" s="1">
         <f t="shared" si="89"/>
-        <v>503.09292702338865</v>
+        <v>504.24518017462486</v>
       </c>
       <c r="DK18" s="1">
         <f t="shared" si="89"/>
-        <v>498.06199775315474</v>
+        <v>499.2027283728786</v>
       </c>
       <c r="DL18" s="1">
         <f t="shared" si="89"/>
-        <v>493.0813777756232</v>
+        <v>494.21070108914978</v>
       </c>
       <c r="DM18" s="1">
         <f t="shared" si="89"/>
-        <v>488.15056399786698</v>
+        <v>489.26859407825827</v>
       </c>
       <c r="DN18" s="1">
         <f t="shared" si="89"/>
-        <v>483.2690583578883</v>
+        <v>484.37590813747568</v>
       </c>
       <c r="DO18" s="1">
         <f t="shared" si="89"/>
-        <v>478.43636777430942</v>
+        <v>479.53214905610093</v>
       </c>
       <c r="DP18" s="1">
         <f t="shared" si="89"/>
-        <v>473.65200409656632</v>
+        <v>474.7368275655399</v>
       </c>
       <c r="DQ18" s="1">
         <f t="shared" si="89"/>
-        <v>468.91548405560064</v>
+        <v>469.98945928988451</v>
       </c>
       <c r="DR18" s="1">
         <f t="shared" si="89"/>
-        <v>464.22632921504464</v>
+        <v>465.28956469698568</v>
       </c>
       <c r="DS18" s="1">
         <f t="shared" si="89"/>
-        <v>459.58406592289418</v>
+        <v>460.63666905001583</v>
       </c>
       <c r="DT18" s="1">
         <f t="shared" ref="DT18:FL18" si="90">DS18*(1+$BI$24)</f>
-        <v>454.98822526366524</v>
+        <v>456.03030235951564</v>
       </c>
       <c r="DU18" s="1">
         <f t="shared" si="90"/>
-        <v>450.43834301102856</v>
+        <v>451.46999933592048</v>
       </c>
       <c r="DV18" s="1">
         <f t="shared" si="90"/>
-        <v>445.93395958091827</v>
+        <v>446.95529934256126</v>
       </c>
       <c r="DW18" s="1">
         <f t="shared" si="90"/>
-        <v>441.47461998510909</v>
+        <v>442.48574634913564</v>
       </c>
       <c r="DX18" s="1">
         <f t="shared" si="90"/>
-        <v>437.05987378525799</v>
+        <v>438.06088888564426</v>
       </c>
       <c r="DY18" s="1">
         <f t="shared" si="90"/>
-        <v>432.68927504740543</v>
+        <v>433.68027999678782</v>
       </c>
       <c r="DZ18" s="1">
         <f t="shared" si="90"/>
-        <v>428.3623822969314</v>
+        <v>429.34347719681995</v>
       </c>
       <c r="EA18" s="1">
         <f t="shared" si="90"/>
-        <v>424.07875847396207</v>
+        <v>425.05004242485177</v>
       </c>
       <c r="EB18" s="1">
         <f t="shared" si="90"/>
-        <v>419.83797088922245</v>
+        <v>420.79954200060325</v>
       </c>
       <c r="EC18" s="1">
         <f t="shared" si="90"/>
-        <v>415.63959118033023</v>
+        <v>416.5915465805972</v>
       </c>
       <c r="ED18" s="1">
         <f t="shared" si="90"/>
-        <v>411.48319526852691</v>
+        <v>412.4256311147912</v>
       </c>
       <c r="EE18" s="1">
         <f t="shared" si="90"/>
-        <v>407.36836331584163</v>
+        <v>408.30137480364328</v>
       </c>
       <c r="EF18" s="1">
         <f t="shared" si="90"/>
-        <v>403.29467968268324</v>
+        <v>404.21836105560686</v>
       </c>
       <c r="EG18" s="1">
         <f t="shared" si="90"/>
-        <v>399.26173288585642</v>
+        <v>400.17617744505077</v>
       </c>
       <c r="EH18" s="1">
         <f t="shared" si="90"/>
-        <v>395.26911555699786</v>
+        <v>396.17441567060024</v>
       </c>
       <c r="EI18" s="1">
         <f t="shared" si="90"/>
-        <v>391.31642440142787</v>
+        <v>392.21267151389424</v>
       </c>
       <c r="EJ18" s="1">
         <f t="shared" si="90"/>
-        <v>387.40326015741357</v>
+        <v>388.29054479875526</v>
       </c>
       <c r="EK18" s="1">
         <f t="shared" si="90"/>
-        <v>383.52922755583944</v>
+        <v>384.40763935076768</v>
       </c>
       <c r="EL18" s="1">
         <f t="shared" si="90"/>
-        <v>379.69393528028104</v>
+        <v>380.56356295725999</v>
       </c>
       <c r="EM18" s="1">
         <f t="shared" si="90"/>
-        <v>375.8969959274782</v>
+        <v>376.75792732768741</v>
       </c>
       <c r="EN18" s="1">
         <f t="shared" si="90"/>
-        <v>372.13802596820341</v>
+        <v>372.99034805441056</v>
       </c>
       <c r="EO18" s="1">
         <f t="shared" si="90"/>
-        <v>368.41664570852134</v>
+        <v>369.26044457386644</v>
       </c>
       <c r="EP18" s="1">
         <f t="shared" si="90"/>
-        <v>364.73247925143613</v>
+        <v>365.56784012812778</v>
       </c>
       <c r="EQ18" s="1">
         <f t="shared" si="90"/>
-        <v>361.08515445892175</v>
+        <v>361.91216172684648</v>
       </c>
       <c r="ER18" s="1">
         <f t="shared" si="90"/>
-        <v>357.47430291433255</v>
+        <v>358.29304010957799</v>
       </c>
       <c r="ES18" s="1">
         <f t="shared" si="90"/>
-        <v>353.89955988518921</v>
+        <v>354.71010970848221</v>
       </c>
       <c r="ET18" s="1">
         <f t="shared" si="90"/>
-        <v>350.36056428633731</v>
+        <v>351.1630086113974</v>
       </c>
       <c r="EU18" s="1">
         <f t="shared" si="90"/>
-        <v>346.85695864347394</v>
+        <v>347.65137852528341</v>
       </c>
       <c r="EV18" s="1">
         <f t="shared" si="90"/>
-        <v>343.38838905703921</v>
+        <v>344.17486474003056</v>
       </c>
       <c r="EW18" s="1">
         <f t="shared" si="90"/>
-        <v>339.95450516646883</v>
+        <v>340.73311609263027</v>
       </c>
       <c r="EX18" s="1">
         <f t="shared" si="90"/>
-        <v>336.55496011480415</v>
+        <v>337.32578493170394</v>
       </c>
       <c r="EY18" s="1">
         <f t="shared" si="90"/>
-        <v>333.18941051365613</v>
+        <v>333.95252708238689</v>
       </c>
       <c r="EZ18" s="1">
         <f t="shared" si="90"/>
-        <v>329.85751640851959</v>
+        <v>330.61300181156304</v>
       </c>
       <c r="FA18" s="1">
         <f t="shared" si="90"/>
-        <v>326.55894124443438</v>
+        <v>327.30687179344739</v>
       </c>
       <c r="FB18" s="1">
         <f t="shared" si="90"/>
-        <v>323.29335183199004</v>
+        <v>324.03380307551294</v>
       </c>
       <c r="FC18" s="1">
         <f t="shared" si="90"/>
-        <v>320.06041831367014</v>
+        <v>320.7934650447578</v>
       </c>
       <c r="FD18" s="1">
         <f t="shared" si="90"/>
-        <v>316.85981413053344</v>
+        <v>317.58553039431024</v>
       </c>
       <c r="FE18" s="1">
         <f t="shared" si="90"/>
-        <v>313.69121598922811</v>
+        <v>314.40967509036716</v>
       </c>
       <c r="FF18" s="1">
         <f t="shared" si="90"/>
-        <v>310.55430382933582</v>
+        <v>311.2655783394635</v>
       </c>
       <c r="FG18" s="1">
         <f t="shared" si="90"/>
-        <v>307.44876079104245</v>
+        <v>308.15292255606886</v>
       </c>
       <c r="FH18" s="1">
         <f t="shared" si="90"/>
-        <v>304.374273183132</v>
+        <v>305.07139333050816</v>
       </c>
       <c r="FI18" s="1">
         <f t="shared" si="90"/>
-        <v>301.33053045130066</v>
+        <v>302.02067939720308</v>
       </c>
       <c r="FJ18" s="1">
         <f t="shared" si="90"/>
-        <v>298.31722514678768</v>
+        <v>299.00047260323106</v>
       </c>
       <c r="FK18" s="1">
         <f t="shared" si="90"/>
-        <v>295.33405289531981</v>
+        <v>296.01046787719872</v>
       </c>
       <c r="FL18" s="1">
         <f t="shared" si="90"/>
-        <v>292.38071236636659</v>
+        <v>293.05036319842674</v>
       </c>
     </row>
     <row r="19" spans="2:168" x14ac:dyDescent="0.3">
@@ -4911,20 +4902,20 @@
         <v>149</v>
       </c>
       <c r="AI19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AJ19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AK19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AL19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AO19" s="6">
         <v>168.4</v>
@@ -4952,44 +4943,44 @@
         <v>149</v>
       </c>
       <c r="AW19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AX19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AY19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="AZ19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="BA19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="BB19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="BC19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="BD19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="BE19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
       <c r="BF19" s="6">
-        <f>149</f>
-        <v>149</v>
+        <f>147.9</f>
+        <v>147.9</v>
       </c>
     </row>
     <row r="20" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5126,19 +5117,19 @@
       </c>
       <c r="AI20" s="8">
         <f t="shared" ref="AI20:AL20" si="101">AI18/AI19</f>
-        <v>1.0467614630872484</v>
+        <v>0.98782961460446261</v>
       </c>
       <c r="AJ20" s="8">
         <f t="shared" si="101"/>
-        <v>1.0475491275167783</v>
+        <v>1.0343517241379308</v>
       </c>
       <c r="AK20" s="8">
         <f t="shared" si="101"/>
-        <v>1.5212295704697985</v>
+        <v>1.533082842461122</v>
       </c>
       <c r="AL20" s="8">
         <f t="shared" si="101"/>
-        <v>0.73853756510067126</v>
+        <v>0.7410366963624071</v>
       </c>
       <c r="AO20" s="8">
         <f t="shared" ref="AO20:AT20" si="102">AO18/AO19</f>
@@ -5174,43 +5165,43 @@
       </c>
       <c r="AW20" s="8">
         <f t="shared" si="103"/>
-        <v>4.3540777261744994</v>
+        <v>4.2963008775659244</v>
       </c>
       <c r="AX20" s="8">
         <f t="shared" si="103"/>
-        <v>5.0220417862013411</v>
+        <v>5.0522168889747121</v>
       </c>
       <c r="AY20" s="8">
         <f t="shared" si="103"/>
-        <v>5.1717463914652342</v>
+        <v>5.2033398663014676</v>
       </c>
       <c r="AZ20" s="8">
         <f t="shared" si="103"/>
-        <v>5.2571771549455466</v>
+        <v>5.3085208418154615</v>
       </c>
       <c r="BA20" s="8">
         <f t="shared" si="103"/>
-        <v>5.3634547206216379</v>
+        <v>5.415816578621615</v>
       </c>
       <c r="BB20" s="8">
         <f t="shared" si="103"/>
-        <v>5.4718691778370241</v>
+        <v>5.5252694833635889</v>
       </c>
       <c r="BC20" s="8">
         <f t="shared" si="103"/>
-        <v>5.5824633778247472</v>
+        <v>5.6369228119321013</v>
       </c>
       <c r="BD20" s="8">
         <f t="shared" ref="BD20:BF20" si="104">BD18/BD19</f>
-        <v>5.6952810299765355</v>
+        <v>5.7508206864609948</v>
       </c>
       <c r="BE20" s="8">
         <f t="shared" si="104"/>
-        <v>5.8103667190173116</v>
+        <v>5.867008112663366</v>
       </c>
       <c r="BF20" s="8">
         <f t="shared" si="104"/>
-        <v>5.9277659225233164</v>
+        <v>5.9855309975145188</v>
       </c>
     </row>
     <row r="22" spans="2:168" x14ac:dyDescent="0.3">
@@ -5335,7 +5326,7 @@
       </c>
       <c r="AI22" s="10">
         <f t="shared" ref="AI22" si="118">AI3/AE3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>5.4677448998345923E-2</v>
       </c>
       <c r="AJ22" s="10">
         <f t="shared" ref="AJ22" si="119">AJ3/AF3-1</f>
@@ -5380,7 +5371,7 @@
       </c>
       <c r="AW22" s="10">
         <f t="shared" si="122"/>
-        <v>4.7781729565962161E-2</v>
+        <v>4.8899207446925441E-2</v>
       </c>
       <c r="AX22" s="10">
         <f t="shared" si="122"/>
@@ -5553,7 +5544,7 @@
       </c>
       <c r="AI23" s="10">
         <f t="shared" ref="AI23:AL23" si="129">AI5/AI3</f>
-        <v>0.43</v>
+        <v>0.41918619848392435</v>
       </c>
       <c r="AJ23" s="10">
         <f t="shared" si="129"/>
@@ -5601,7 +5592,7 @@
       </c>
       <c r="AW23" s="10">
         <f t="shared" si="130"/>
-        <v>0.4300000000000001</v>
+        <v>0.42740226903249751</v>
       </c>
       <c r="AX23" s="10">
         <f t="shared" si="130"/>
@@ -5609,11 +5600,11 @@
       </c>
       <c r="AY23" s="10">
         <f t="shared" si="130"/>
-        <v>0.44</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="AZ23" s="10">
         <f t="shared" si="130"/>
-        <v>0.43999999999999995</v>
+        <v>0.44</v>
       </c>
       <c r="BA23" s="10">
         <f t="shared" si="130"/>
@@ -5625,7 +5616,7 @@
       </c>
       <c r="BC23" s="10">
         <f t="shared" si="130"/>
-        <v>0.44</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="BD23" s="10">
         <f t="shared" ref="BD23:BF23" si="131">BD5/BD3</f>
@@ -5774,15 +5765,15 @@
       </c>
       <c r="AI24" s="10">
         <f t="shared" ref="AI24:AL24" si="135">AI13/AI3</f>
-        <v>0.15196663778542108</v>
+        <v>0.14132613052191342</v>
       </c>
       <c r="AJ24" s="10">
         <f t="shared" si="135"/>
-        <v>0.14935654548557772</v>
+        <v>0.14915343915343912</v>
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="135"/>
-        <v>0.18654117948007376</v>
+        <v>0.18709542639707524</v>
       </c>
       <c r="AL24" s="10">
         <f t="shared" si="135"/>
@@ -5822,43 +5813,43 @@
       </c>
       <c r="AW24" s="10">
         <f t="shared" si="136"/>
-        <v>0.15358393778073365</v>
+        <v>0.15113955849666916</v>
       </c>
       <c r="AX24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17221086274102682</v>
+        <v>0.17377731791212969</v>
       </c>
       <c r="AY24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17228988712755802</v>
+        <v>0.17385507400460504</v>
       </c>
       <c r="AZ24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17166251534573435</v>
+        <v>0.17389357089352667</v>
       </c>
       <c r="BA24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17170125658790109</v>
+        <v>0.17393169036196865</v>
       </c>
       <c r="BB24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17173961801396809</v>
+        <v>0.17396943611013174</v>
       </c>
       <c r="BC24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17177760334762268</v>
+        <v>0.17400681180194041</v>
       </c>
       <c r="BD24" s="10">
         <f t="shared" ref="BD24:BF24" si="137">BD13/BD3</f>
-        <v>0.1718152162760454</v>
+        <v>0.17404382106539801</v>
       </c>
       <c r="BE24" s="10">
         <f t="shared" si="137"/>
-        <v>0.17185246045026786</v>
+        <v>0.17408046749293926</v>
       </c>
       <c r="BF24" s="10">
         <f t="shared" si="137"/>
-        <v>0.1718893394855274</v>
+        <v>0.17411675464177917</v>
       </c>
       <c r="BH24" t="s">
         <v>55</v>
@@ -6001,7 +5992,7 @@
       </c>
       <c r="AI25" s="10">
         <f t="shared" ref="AI25:AL25" si="141">AI6/AI3</f>
-        <v>0.17</v>
+        <v>0.17060207371264269</v>
       </c>
       <c r="AJ25" s="10">
         <f t="shared" si="141"/>
@@ -6049,7 +6040,7 @@
       </c>
       <c r="AW25" s="10">
         <f t="shared" si="142"/>
-        <v>0.16850604112149062</v>
+        <v>0.1686522651079583</v>
       </c>
       <c r="AX25" s="10">
         <f t="shared" si="142"/>
@@ -6216,15 +6207,15 @@
       </c>
       <c r="AI26" s="10">
         <f t="shared" ref="AI26:AI27" si="172">AI7/AE7-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>-9.2961487383798058E-3</v>
       </c>
       <c r="AJ26" s="10">
         <f t="shared" ref="AJ26:AJ27" si="173">AJ7/AF7-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" ref="AK26:AK27" si="174">AK7/AG7-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AL26" s="10">
         <f t="shared" ref="AL26:AL27" si="175">AL7/AH7-1</f>
@@ -6261,11 +6252,11 @@
       </c>
       <c r="AW26" s="10">
         <f t="shared" si="176"/>
-        <v>5.0000000000000044E-2</v>
+        <v>3.0559870550161961E-2</v>
       </c>
       <c r="AX26" s="10">
         <f t="shared" si="176"/>
-        <v>4.0000000000000036E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY26" s="10">
         <f t="shared" si="176"/>
@@ -6273,7 +6264,7 @@
       </c>
       <c r="AZ26" s="10">
         <f t="shared" si="176"/>
-        <v>3.0000000000000027E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA26" s="10">
         <f t="shared" si="176"/>
@@ -6303,8 +6294,8 @@
         <v>57</v>
       </c>
       <c r="BI26" s="6">
-        <f>NPV(BI25,AV18:FL18)</f>
-        <v>9634.0663421519712</v>
+        <f>NPV(BI25,AW18:FL18)</f>
+        <v>9777.4050859448016</v>
       </c>
     </row>
     <row r="27" spans="2:168" x14ac:dyDescent="0.3">
@@ -6429,7 +6420,7 @@
       </c>
       <c r="AI27" s="10">
         <f t="shared" si="172"/>
-        <v>5.0000000000000044E-2</v>
+        <v>0.11466666666666669</v>
       </c>
       <c r="AJ27" s="10">
         <f t="shared" si="173"/>
@@ -6474,7 +6465,7 @@
       </c>
       <c r="AW27" s="10">
         <f t="shared" si="180"/>
-        <v>3.9335770871419706E-2</v>
+        <v>5.4113345521023648E-2</v>
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="180"/>
@@ -6517,7 +6508,7 @@
       </c>
       <c r="BI27" s="6">
         <f>Main!D8</f>
-        <v>1503.2</v>
+        <v>1487.8</v>
       </c>
     </row>
     <row r="28" spans="2:168" x14ac:dyDescent="0.3">
@@ -6654,7 +6645,7 @@
       </c>
       <c r="AI28" s="10">
         <f t="shared" ref="AI28:AL28" si="184">AI17/AI16</f>
-        <v>0.17</v>
+        <v>0.16323024054982815</v>
       </c>
       <c r="AJ28" s="10">
         <f t="shared" si="184"/>
@@ -6702,7 +6693,7 @@
       </c>
       <c r="AW28" s="10">
         <f t="shared" si="185"/>
-        <v>0.16999999999999993</v>
+        <v>0.16845317449517719</v>
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="185"/>
@@ -6745,7 +6736,7 @@
       </c>
       <c r="BI28" s="6">
         <f>BI26+BI27</f>
-        <v>11137.266342151972</v>
+        <v>11265.205085944801</v>
       </c>
     </row>
     <row r="29" spans="2:168" x14ac:dyDescent="0.3">
@@ -6882,19 +6873,19 @@
       </c>
       <c r="AI29" s="10">
         <f t="shared" ref="AI29:AL29" si="190">AI18/AI3</f>
-        <v>0.13650104410078678</v>
+        <v>0.12729807440968896</v>
       </c>
       <c r="AJ29" s="10">
         <f t="shared" si="190"/>
-        <v>0.13320090459122716</v>
+        <v>0.13055181771633381</v>
       </c>
       <c r="AK29" s="10">
         <f t="shared" si="190"/>
-        <v>0.16106074759382225</v>
+        <v>0.1611174132301581</v>
       </c>
       <c r="AL29" s="10">
         <f t="shared" si="190"/>
-        <v>0.1047206144558134</v>
+        <v>0.1042992563798039</v>
       </c>
       <c r="AO29" s="10">
         <f t="shared" ref="AO29:BC29" si="191">AO18/AO3</f>
@@ -6930,50 +6921,50 @@
       </c>
       <c r="AW29" s="10">
         <f t="shared" si="191"/>
-        <v>0.13593546523749095</v>
+        <v>0.13299957652485095</v>
       </c>
       <c r="AX29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15075911628627178</v>
+        <v>0.15038489502903457</v>
       </c>
       <c r="AY29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15073123464401739</v>
+        <v>0.15037207740990233</v>
       </c>
       <c r="AZ29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15021678978292197</v>
+        <v>0.15040364485881808</v>
       </c>
       <c r="BA29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15024855760149866</v>
+        <v>0.1504349028229405</v>
       </c>
       <c r="BB29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15028001397087362</v>
+        <v>0.15046585433643425</v>
       </c>
       <c r="BC29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15031116194447039</v>
+        <v>0.15049650240371737</v>
       </c>
       <c r="BD29" s="10">
         <f t="shared" ref="BD29:BF29" si="192">BD18/BD3</f>
-        <v>0.15034200454577704</v>
+        <v>0.15052684999975258</v>
       </c>
       <c r="BE29" s="10">
         <f t="shared" si="192"/>
-        <v>0.15037254476863945</v>
+        <v>0.1505569000703364</v>
       </c>
       <c r="BF29" s="10">
         <f t="shared" si="192"/>
-        <v>0.15040278557755227</v>
+        <v>0.15058665553238512</v>
       </c>
       <c r="BH29" t="s">
         <v>60</v>
       </c>
       <c r="BI29" s="5">
         <f>BI28/BC19</f>
-        <v>74.746753974174311</v>
+        <v>76.167715253176468</v>
       </c>
     </row>
     <row r="30" spans="2:168" x14ac:dyDescent="0.3">
@@ -6982,7 +6973,7 @@
       </c>
       <c r="BI30" s="5">
         <f>Main!D3</f>
-        <v>85.53</v>
+        <v>96.92</v>
       </c>
     </row>
     <row r="31" spans="2:168" x14ac:dyDescent="0.3">
@@ -6991,7 +6982,7 @@
       </c>
       <c r="BI31" s="11">
         <f>BI29/BI30-1</f>
-        <v>-0.12607559950690628</v>
+        <v>-0.21411767175839391</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">
@@ -6999,7 +6990,7 @@
         <v>63</v>
       </c>
       <c r="BI32" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LOGI.xlsx
+++ b/Financial Analysis/LOGI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB961E0-B7A9-4FEE-BB2F-B190E906EDAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49AC922-E0A1-4C71-BAEA-3A9A9EEC12D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{439F4133-7664-46FF-BA84-0DE877A2D3CB}"/>
   </bookViews>
@@ -268,7 +268,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -369,13 +369,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>7620</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -393,7 +393,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25991820" y="7620"/>
+          <a:off x="26715720" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -793,17 +793,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>96.92</v>
+        <v>115.3</v>
       </c>
       <c r="E3" s="4">
-        <v>45868</v>
+        <v>45959</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45868</v>
+        <v>45959</v>
       </c>
       <c r="G3" s="4">
-        <v>45957</v>
+        <v>46048</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,11 +811,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f>147.1</f>
+        <v>147.1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>14334.468000000001</v>
+        <v>16960.629999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -832,11 +832,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1487.8</f>
-        <v>1487.8</v>
+        <f>1375.8</f>
+        <v>1375.8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -856,7 +856,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>1487.8</v>
+        <v>1375.8</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>12846.668000000001</v>
+        <v>15584.829999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1318,11 +1318,10 @@
         <v>1147.7</v>
       </c>
       <c r="AJ3" s="9">
-        <f t="shared" ref="AJ3:AK3" si="0">AF3*1.05</f>
-        <v>1171.8</v>
+        <v>1186.0999999999999</v>
       </c>
       <c r="AK3" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AK3" si="0">AG3*1.05</f>
         <v>1407.3150000000001</v>
       </c>
       <c r="AL3" s="9">
@@ -1363,43 +1362,43 @@
       </c>
       <c r="AW3" s="9">
         <f>SUM(AI3:AL3)</f>
-        <v>4777.6310000000003</v>
+        <v>4791.9310000000005</v>
       </c>
       <c r="AX3" s="9">
         <f>AW3*1.04</f>
-        <v>4968.7362400000002</v>
+        <v>4983.6082400000005</v>
       </c>
       <c r="AY3" s="9">
         <f>AX3*1.03</f>
-        <v>5117.7983272000001</v>
+        <v>5133.1164872000008</v>
       </c>
       <c r="AZ3" s="9">
         <f>AY3*1.02</f>
-        <v>5220.1542937439999</v>
+        <v>5235.7788169440009</v>
       </c>
       <c r="BA3" s="9">
         <f t="shared" ref="BA3:BF3" si="1">AZ3*1.02</f>
-        <v>5324.5573796188801</v>
+        <v>5340.494393282881</v>
       </c>
       <c r="BB3" s="9">
         <f t="shared" si="1"/>
-        <v>5431.0485272112574</v>
+        <v>5447.3042811485384</v>
       </c>
       <c r="BC3" s="9">
         <f t="shared" si="1"/>
-        <v>5539.6694977554826</v>
+        <v>5556.2503667715091</v>
       </c>
       <c r="BD3" s="9">
         <f t="shared" si="1"/>
-        <v>5650.4628877105924</v>
+        <v>5667.3753741069395</v>
       </c>
       <c r="BE3" s="9">
         <f t="shared" si="1"/>
-        <v>5763.4721454648043</v>
+        <v>5780.7228815890785</v>
       </c>
       <c r="BF3" s="9">
         <f t="shared" si="1"/>
-        <v>5878.7415883741005</v>
+        <v>5896.3373392208605</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1506,12 +1505,11 @@
         <v>666.6</v>
       </c>
       <c r="AJ4" s="6">
-        <f t="shared" ref="AJ4:AL4" si="2">AJ3-AJ5</f>
-        <v>667.92599999999993</v>
+        <v>669.4</v>
       </c>
       <c r="AK4" s="6">
-        <f t="shared" si="2"/>
-        <v>802.16955000000007</v>
+        <f t="shared" ref="AK4:AL4" si="2">AK3-AK5</f>
+        <v>788.09640000000002</v>
       </c>
       <c r="AL4" s="6">
         <f t="shared" si="2"/>
@@ -1551,43 +1549,43 @@
       </c>
       <c r="AW4" s="6">
         <f>SUM(AI4:AL4)</f>
-        <v>2735.6606700000002</v>
+        <v>2723.0615200000002</v>
       </c>
       <c r="AX4" s="6">
         <f t="shared" ref="AX4:BC4" si="3">AX3-AX5</f>
-        <v>2782.4922944</v>
+        <v>2790.8206144000001</v>
       </c>
       <c r="AY4" s="6">
         <f t="shared" si="3"/>
-        <v>2865.9670632319999</v>
+        <v>2874.5452328320002</v>
       </c>
       <c r="AZ4" s="6">
         <f t="shared" si="3"/>
-        <v>2923.28640449664</v>
+        <v>2932.0361374886406</v>
       </c>
       <c r="BA4" s="6">
         <f t="shared" si="3"/>
-        <v>2981.7521325865728</v>
+        <v>2990.6768602384132</v>
       </c>
       <c r="BB4" s="6">
         <f t="shared" si="3"/>
-        <v>3041.3871752383043</v>
+        <v>3050.4903974431813</v>
       </c>
       <c r="BC4" s="6">
         <f t="shared" si="3"/>
-        <v>3102.21491874307</v>
+        <v>3111.5002053920452</v>
       </c>
       <c r="BD4" s="6">
         <f t="shared" ref="BD4:BF4" si="4">BD3-BD5</f>
-        <v>3164.2592171179317</v>
+        <v>3173.7302094998863</v>
       </c>
       <c r="BE4" s="6">
         <f t="shared" si="4"/>
-        <v>3227.5444014602904</v>
+        <v>3237.2048136898838</v>
       </c>
       <c r="BF4" s="6">
         <f t="shared" si="4"/>
-        <v>3292.0952894894963</v>
+        <v>3301.9489099636817</v>
       </c>
     </row>
     <row r="5" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1659,7 +1657,7 @@
         <v>714.80000000000007</v>
       </c>
       <c r="S5" s="9">
-        <f t="shared" ref="S5:AI5" si="6">S3-S4</f>
+        <f t="shared" ref="S5:AJ5" si="6">S3-S4</f>
         <v>572.99999999999989</v>
       </c>
       <c r="T5" s="9">
@@ -1727,15 +1725,15 @@
         <v>481.1</v>
       </c>
       <c r="AJ5" s="9">
-        <f t="shared" ref="AJ5:AL5" si="7">AJ3*0.43</f>
-        <v>503.87399999999997</v>
+        <f t="shared" si="6"/>
+        <v>516.69999999999993</v>
       </c>
       <c r="AK5" s="9">
-        <f t="shared" si="7"/>
-        <v>605.14544999999998</v>
+        <f>AK3*0.44</f>
+        <v>619.21860000000004</v>
       </c>
       <c r="AL5" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="AL5" si="7">AL3*0.43</f>
         <v>451.85088000000002</v>
       </c>
       <c r="AO5" s="9">
@@ -1772,43 +1770,43 @@
       </c>
       <c r="AW5" s="9">
         <f t="shared" si="8"/>
-        <v>2041.9703300000001</v>
+        <v>2068.8694800000003</v>
       </c>
       <c r="AX5" s="9">
         <f>AX3*0.44</f>
-        <v>2186.2439456000002</v>
+        <v>2192.7876256000004</v>
       </c>
       <c r="AY5" s="9">
         <f t="shared" ref="AY5:BF5" si="9">AY3*0.44</f>
-        <v>2251.8312639680003</v>
+        <v>2258.5712543680006</v>
       </c>
       <c r="AZ5" s="9">
         <f t="shared" si="9"/>
-        <v>2296.8678892473599</v>
+        <v>2303.7426794553603</v>
       </c>
       <c r="BA5" s="9">
         <f t="shared" si="9"/>
-        <v>2342.8052470323073</v>
+        <v>2349.8175330444678</v>
       </c>
       <c r="BB5" s="9">
         <f t="shared" si="9"/>
-        <v>2389.6613519729531</v>
+        <v>2396.8138837053571</v>
       </c>
       <c r="BC5" s="9">
         <f t="shared" si="9"/>
-        <v>2437.4545790124125</v>
+        <v>2444.7501613794639</v>
       </c>
       <c r="BD5" s="9">
         <f t="shared" si="9"/>
-        <v>2486.2036705926607</v>
+        <v>2493.6451646070532</v>
       </c>
       <c r="BE5" s="9">
         <f t="shared" si="9"/>
-        <v>2535.9277440045139</v>
+        <v>2543.5180678991946</v>
       </c>
       <c r="BF5" s="9">
         <f t="shared" si="9"/>
-        <v>2586.6462988846042</v>
+        <v>2594.3884292571788</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1915,8 +1913,7 @@
         <v>195.8</v>
       </c>
       <c r="AJ6" s="6">
-        <f>AJ3*0.17</f>
-        <v>199.20600000000002</v>
+        <v>199</v>
       </c>
       <c r="AK6" s="6">
         <f>AK3*0.15</f>
@@ -1960,43 +1957,43 @@
       </c>
       <c r="AW6" s="6">
         <f t="shared" ref="AW6:AW11" si="16">SUM(AI6:AL6)</f>
-        <v>805.75828999999999</v>
+        <v>805.55228999999997</v>
       </c>
       <c r="AX6" s="6">
         <f t="shared" ref="AX6:BC6" si="17">AX3*0.16</f>
-        <v>794.99779840000008</v>
+        <v>797.37731840000015</v>
       </c>
       <c r="AY6" s="6">
         <f t="shared" si="17"/>
-        <v>818.84773235200009</v>
+        <v>821.29863795200015</v>
       </c>
       <c r="AZ6" s="6">
         <f t="shared" si="17"/>
-        <v>835.22468699904005</v>
+        <v>837.72461071104021</v>
       </c>
       <c r="BA6" s="6">
         <f t="shared" si="17"/>
-        <v>851.92918073902081</v>
+        <v>854.47910292526103</v>
       </c>
       <c r="BB6" s="6">
         <f t="shared" si="17"/>
-        <v>868.96776435380116</v>
+        <v>871.56868498376616</v>
       </c>
       <c r="BC6" s="6">
         <f t="shared" si="17"/>
-        <v>886.34711964087728</v>
+        <v>889.00005868344147</v>
       </c>
       <c r="BD6" s="6">
         <f t="shared" ref="BD6:BF6" si="18">BD3*0.16</f>
-        <v>904.07406203369476</v>
+        <v>906.78005985711036</v>
       </c>
       <c r="BE6" s="6">
         <f t="shared" si="18"/>
-        <v>922.15554327436871</v>
+        <v>924.91566105425261</v>
       </c>
       <c r="BF6" s="6">
         <f t="shared" si="18"/>
-        <v>940.59865413985608</v>
+        <v>943.41397427533775</v>
       </c>
     </row>
     <row r="7" spans="2:58" x14ac:dyDescent="0.3">
@@ -2103,15 +2100,14 @@
         <v>74.599999999999994</v>
       </c>
       <c r="AJ7" s="6">
-        <f>AF7*1.04</f>
-        <v>79.248000000000005</v>
+        <v>76.099999999999994</v>
       </c>
       <c r="AK7" s="6">
         <f>AG7*1.04</f>
         <v>81.12</v>
       </c>
       <c r="AL7" s="6">
-        <f t="shared" ref="AJ7:AL7" si="19">AH7*1.05</f>
+        <f t="shared" ref="AL7" si="19">AH7*1.05</f>
         <v>83.475000000000009</v>
       </c>
       <c r="AO7" s="6">
@@ -2148,43 +2144,43 @@
       </c>
       <c r="AW7" s="6">
         <f t="shared" si="16"/>
-        <v>318.44300000000004</v>
+        <v>315.29500000000002</v>
       </c>
       <c r="AX7" s="6">
         <f>AW7*1.03</f>
-        <v>327.99629000000004</v>
+        <v>324.75385</v>
       </c>
       <c r="AY7" s="6">
         <f>AX7*1.03</f>
-        <v>337.83617870000006</v>
+        <v>334.4964655</v>
       </c>
       <c r="AZ7" s="6">
         <f>AY7*1.02</f>
-        <v>344.5929022740001</v>
+        <v>341.18639481000002</v>
       </c>
       <c r="BA7" s="6">
         <f t="shared" ref="BA7:BC7" si="20">AZ7*1.02</f>
-        <v>351.48476031948013</v>
+        <v>348.01012270620004</v>
       </c>
       <c r="BB7" s="6">
         <f t="shared" si="20"/>
-        <v>358.51445552586972</v>
+        <v>354.97032516032402</v>
       </c>
       <c r="BC7" s="6">
         <f t="shared" si="20"/>
-        <v>365.68474463638711</v>
+        <v>362.06973166353049</v>
       </c>
       <c r="BD7" s="6">
         <f t="shared" ref="BD7:BD8" si="21">BC7*1.02</f>
-        <v>372.99843952911488</v>
+        <v>369.31112629680109</v>
       </c>
       <c r="BE7" s="6">
         <f t="shared" ref="BE7:BE8" si="22">BD7*1.02</f>
-        <v>380.45840831969718</v>
+        <v>376.69734882273713</v>
       </c>
       <c r="BF7" s="6">
         <f t="shared" ref="BF7:BF8" si="23">BE7*1.02</f>
-        <v>388.06757648609113</v>
+        <v>384.23129579919186</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -2291,16 +2287,15 @@
         <v>41.8</v>
       </c>
       <c r="AJ8" s="6">
-        <f>AF8*1.01</f>
-        <v>44.642000000000003</v>
+        <v>41.8</v>
       </c>
       <c r="AK8" s="6">
-        <f>AG8*1.06</f>
-        <v>44.626000000000005</v>
+        <f>AG8*1.02</f>
+        <v>42.942</v>
       </c>
       <c r="AL8" s="6">
-        <f>AH8*1.04</f>
-        <v>41.911999999999999</v>
+        <f>AH8*1.07</f>
+        <v>43.121000000000002</v>
       </c>
       <c r="AO8" s="6">
         <f t="shared" si="10"/>
@@ -2336,43 +2331,43 @@
       </c>
       <c r="AW8" s="6">
         <f t="shared" si="16"/>
-        <v>172.98000000000002</v>
+        <v>169.66300000000001</v>
       </c>
       <c r="AX8" s="6">
         <f>AW8*1.04</f>
-        <v>179.89920000000004</v>
+        <v>176.44952000000001</v>
       </c>
       <c r="AY8" s="6">
         <f>AX8*1.03</f>
-        <v>185.29617600000003</v>
+        <v>181.7430056</v>
       </c>
       <c r="AZ8" s="6">
         <f>AY8*1.02</f>
-        <v>189.00209952000003</v>
+        <v>185.37786571200002</v>
       </c>
       <c r="BA8" s="6">
         <f t="shared" ref="BA8:BC8" si="24">AZ8*1.02</f>
-        <v>192.78214151040004</v>
+        <v>189.08542302624002</v>
       </c>
       <c r="BB8" s="6">
         <f t="shared" si="24"/>
-        <v>196.63778434060805</v>
+        <v>192.86713148676483</v>
       </c>
       <c r="BC8" s="6">
         <f t="shared" si="24"/>
-        <v>200.57054002742021</v>
+        <v>196.72447411650015</v>
       </c>
       <c r="BD8" s="6">
         <f t="shared" si="21"/>
-        <v>204.58195082796863</v>
+        <v>200.65896359883016</v>
       </c>
       <c r="BE8" s="6">
         <f t="shared" si="22"/>
-        <v>208.67358984452801</v>
+        <v>204.67214287080677</v>
       </c>
       <c r="BF8" s="6">
         <f t="shared" si="23"/>
-        <v>212.84706164141858</v>
+        <v>208.7655857282229</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2512,7 +2507,8 @@
         <v>4.7</v>
       </c>
       <c r="AJ9" s="6">
-        <v>5</v>
+        <f>1.8+2.2</f>
+        <v>4</v>
       </c>
       <c r="AK9" s="6">
         <v>5</v>
@@ -2554,43 +2550,43 @@
       </c>
       <c r="AW9" s="6">
         <f t="shared" si="16"/>
-        <v>19.7</v>
+        <v>18.7</v>
       </c>
       <c r="AX9" s="6">
         <f t="shared" ref="AX9:BC9" si="25">AW9*1.01</f>
-        <v>19.896999999999998</v>
+        <v>18.887</v>
       </c>
       <c r="AY9" s="6">
         <f t="shared" si="25"/>
-        <v>20.095969999999998</v>
+        <v>19.075870000000002</v>
       </c>
       <c r="AZ9" s="6">
         <f t="shared" si="25"/>
-        <v>20.296929699999996</v>
+        <v>19.266628700000002</v>
       </c>
       <c r="BA9" s="6">
         <f t="shared" si="25"/>
-        <v>20.499898996999995</v>
+        <v>19.459294987000003</v>
       </c>
       <c r="BB9" s="6">
         <f t="shared" si="25"/>
-        <v>20.704897986969996</v>
+        <v>19.653887936870003</v>
       </c>
       <c r="BC9" s="6">
         <f t="shared" si="25"/>
-        <v>20.911946966839697</v>
+        <v>19.850426816238702</v>
       </c>
       <c r="BD9" s="6">
         <f t="shared" ref="BD9" si="26">BC9*1.01</f>
-        <v>21.121066436508094</v>
+        <v>20.04893108440109</v>
       </c>
       <c r="BE9" s="6">
         <f t="shared" ref="BE9" si="27">BD9*1.01</f>
-        <v>21.332277100873174</v>
+        <v>20.2494203952451</v>
       </c>
       <c r="BF9" s="6">
         <f t="shared" ref="BF9" si="28">BE9*1.01</f>
-        <v>21.545599871881905</v>
+        <v>20.451914599197551</v>
       </c>
     </row>
     <row r="10" spans="2:58" x14ac:dyDescent="0.3">
@@ -2851,7 +2847,7 @@
         <v>2</v>
       </c>
       <c r="AJ11" s="6">
-        <v>1</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="AK11" s="6">
         <v>0</v>
@@ -2893,7 +2889,7 @@
       </c>
       <c r="AW11" s="6">
         <f t="shared" si="16"/>
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" s="6">
         <v>0</v>
@@ -3061,15 +3057,15 @@
       </c>
       <c r="AJ12" s="6">
         <f t="shared" si="39"/>
-        <v>329.096</v>
+        <v>325.3</v>
       </c>
       <c r="AK12" s="6">
         <f t="shared" si="39"/>
-        <v>341.84325000000001</v>
+        <v>340.15925000000004</v>
       </c>
       <c r="AL12" s="6">
         <f t="shared" si="39"/>
-        <v>330.04203999999999</v>
+        <v>331.25103999999999</v>
       </c>
       <c r="AO12" s="6">
         <f>SUM(AO6:AO11)</f>
@@ -3105,43 +3101,43 @@
       </c>
       <c r="AW12" s="6">
         <f t="shared" si="40"/>
-        <v>1319.88129</v>
+        <v>1315.6102900000001</v>
       </c>
       <c r="AX12" s="6">
         <f t="shared" si="40"/>
-        <v>1322.7902884000002</v>
+        <v>1317.4676884000003</v>
       </c>
       <c r="AY12" s="6">
         <f t="shared" si="40"/>
-        <v>1362.0760570520004</v>
+        <v>1356.6139790520001</v>
       </c>
       <c r="AZ12" s="6">
         <f t="shared" si="40"/>
-        <v>1389.1166184930401</v>
+        <v>1383.5554999330404</v>
       </c>
       <c r="BA12" s="6">
         <f t="shared" si="40"/>
-        <v>1416.6959815659011</v>
+        <v>1411.0339436447011</v>
       </c>
       <c r="BB12" s="6">
         <f t="shared" si="40"/>
-        <v>1444.8249022072491</v>
+        <v>1439.060029567725</v>
       </c>
       <c r="BC12" s="6">
         <f t="shared" si="40"/>
-        <v>1473.5143512715244</v>
+        <v>1467.644691279711</v>
       </c>
       <c r="BD12" s="6">
         <f t="shared" ref="BD12:BF12" si="41">SUM(BD6:BD11)</f>
-        <v>1502.7755188272863</v>
+        <v>1496.7990808371426</v>
       </c>
       <c r="BE12" s="6">
         <f t="shared" si="41"/>
-        <v>1532.6198185394671</v>
+        <v>1526.5345731430416</v>
       </c>
       <c r="BF12" s="6">
         <f t="shared" si="41"/>
-        <v>1563.0588921392477</v>
+        <v>1556.8627704019502</v>
       </c>
     </row>
     <row r="13" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3282,15 +3278,15 @@
       </c>
       <c r="AJ13" s="9">
         <f t="shared" si="52"/>
-        <v>174.77799999999996</v>
+        <v>191.39999999999992</v>
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="52"/>
-        <v>263.30219999999997</v>
+        <v>279.05934999999999</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="52"/>
-        <v>121.80884000000003</v>
+        <v>120.59984000000003</v>
       </c>
       <c r="AO13" s="9">
         <f>AO5-AO12</f>
@@ -3326,43 +3322,43 @@
       </c>
       <c r="AW13" s="9">
         <f t="shared" si="53"/>
-        <v>722.08904000000007</v>
+        <v>753.25919000000022</v>
       </c>
       <c r="AX13" s="9">
         <f t="shared" si="53"/>
-        <v>863.45365719999995</v>
+        <v>875.31993720000014</v>
       </c>
       <c r="AY13" s="9">
         <f t="shared" si="53"/>
-        <v>889.75520691599991</v>
+        <v>901.9572753160005</v>
       </c>
       <c r="AZ13" s="9">
         <f t="shared" si="53"/>
-        <v>907.75127075431988</v>
+        <v>920.18717952231987</v>
       </c>
       <c r="BA13" s="9">
         <f t="shared" si="53"/>
-        <v>926.10926546640621</v>
+        <v>938.7835893997667</v>
       </c>
       <c r="BB13" s="9">
         <f t="shared" si="53"/>
-        <v>944.83644976570395</v>
+        <v>957.75385413763206</v>
       </c>
       <c r="BC13" s="9">
         <f t="shared" si="53"/>
-        <v>963.94022774088808</v>
+        <v>977.10547009975289</v>
       </c>
       <c r="BD13" s="9">
         <f t="shared" ref="BD13:BF13" si="54">BD5-BD12</f>
-        <v>983.42815176537442</v>
+        <v>996.84608376991059</v>
       </c>
       <c r="BE13" s="9">
         <f t="shared" si="54"/>
-        <v>1003.3079254650468</v>
+        <v>1016.983494756153</v>
       </c>
       <c r="BF13" s="9">
         <f t="shared" si="54"/>
-        <v>1023.5874067453565</v>
+        <v>1037.5256588552286</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3469,16 +3465,15 @@
         <v>-11.2</v>
       </c>
       <c r="AJ14" s="6">
-        <f>AI14*1.03</f>
-        <v>-11.536</v>
+        <v>-11.8</v>
       </c>
       <c r="AK14" s="6">
         <f t="shared" ref="AK14:AL14" si="55">AJ14*1.03</f>
-        <v>-11.88208</v>
+        <v>-12.154000000000002</v>
       </c>
       <c r="AL14" s="6">
         <f t="shared" si="55"/>
-        <v>-12.2385424</v>
+        <v>-12.518620000000002</v>
       </c>
       <c r="AO14" s="6">
         <f>SUM(C14:F14)</f>
@@ -3514,43 +3509,43 @@
       </c>
       <c r="AW14" s="6">
         <f t="shared" ref="AW14:AW15" si="56">SUM(AI14:AL14)</f>
-        <v>-46.856622399999999</v>
+        <v>-47.672620000000009</v>
       </c>
       <c r="AX14" s="6">
         <f t="shared" ref="AX14:BF14" si="57">AW14*1.02</f>
-        <v>-47.793754847999999</v>
+        <v>-48.626072400000012</v>
       </c>
       <c r="AY14" s="6">
         <f t="shared" si="57"/>
-        <v>-48.749629944959999</v>
+        <v>-49.598593848000014</v>
       </c>
       <c r="AZ14" s="6">
         <f t="shared" si="57"/>
-        <v>-49.724622543859198</v>
+        <v>-50.590565724960015</v>
       </c>
       <c r="BA14" s="6">
         <f t="shared" si="57"/>
-        <v>-50.71911499473638</v>
+        <v>-51.602377039459213</v>
       </c>
       <c r="BB14" s="6">
         <f t="shared" si="57"/>
-        <v>-51.733497294631107</v>
+        <v>-52.6344245802484</v>
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="57"/>
-        <v>-52.768167240523731</v>
+        <v>-53.687113071853368</v>
       </c>
       <c r="BD14" s="6">
         <f t="shared" si="57"/>
-        <v>-53.823530585334204</v>
+        <v>-54.760855333290436</v>
       </c>
       <c r="BE14" s="6">
         <f t="shared" si="57"/>
-        <v>-54.900001197040886</v>
+        <v>-55.856072439956243</v>
       </c>
       <c r="BF14" s="6">
         <f t="shared" si="57"/>
-        <v>-55.998001220981706</v>
+        <v>-56.973193888755368</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3657,7 +3652,7 @@
         <v>-1.2</v>
       </c>
       <c r="AJ15" s="6">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" s="6">
         <v>2</v>
@@ -3699,7 +3694,7 @@
       </c>
       <c r="AW15" s="6">
         <f t="shared" si="56"/>
-        <v>4.8</v>
+        <v>2.9000000000000004</v>
       </c>
       <c r="AX15" s="6">
         <v>0</v>
@@ -3867,15 +3862,15 @@
       </c>
       <c r="AJ16" s="9">
         <f t="shared" si="68"/>
-        <v>184.31399999999996</v>
+        <v>203.09999999999994</v>
       </c>
       <c r="AK16" s="9">
         <f t="shared" si="68"/>
-        <v>273.18427999999994</v>
+        <v>289.21334999999999</v>
       </c>
       <c r="AL16" s="9">
         <f t="shared" si="68"/>
-        <v>132.04738240000003</v>
+        <v>131.11846000000003</v>
       </c>
       <c r="AO16" s="9">
         <f t="shared" ref="AO16:AT16" si="69">AO13-AO14-AO15</f>
@@ -3911,43 +3906,43 @@
       </c>
       <c r="AW16" s="9">
         <f t="shared" si="70"/>
-        <v>764.14566240000011</v>
+        <v>798.03181000000029</v>
       </c>
       <c r="AX16" s="9">
         <f t="shared" si="70"/>
-        <v>911.247412048</v>
+        <v>923.94600960000014</v>
       </c>
       <c r="AY16" s="9">
         <f t="shared" si="70"/>
-        <v>938.50483686095993</v>
+        <v>951.55586916400057</v>
       </c>
       <c r="AZ16" s="9">
         <f t="shared" si="70"/>
-        <v>957.47589329817902</v>
+        <v>970.77774524727988</v>
       </c>
       <c r="BA16" s="9">
         <f t="shared" si="70"/>
-        <v>976.82838046114261</v>
+        <v>990.38596643922597</v>
       </c>
       <c r="BB16" s="9">
         <f t="shared" si="70"/>
-        <v>996.56994706033504</v>
+        <v>1010.3882787178804</v>
       </c>
       <c r="BC16" s="9">
         <f t="shared" si="70"/>
-        <v>1016.7083949814119</v>
+        <v>1030.7925831716063</v>
       </c>
       <c r="BD16" s="9">
         <f t="shared" ref="BD16:BF16" si="71">BD13-BD14-BD15</f>
-        <v>1037.2516823507087</v>
+        <v>1051.6069391032011</v>
       </c>
       <c r="BE16" s="9">
         <f t="shared" si="71"/>
-        <v>1058.2079266620876</v>
+        <v>1072.8395671961093</v>
       </c>
       <c r="BF16" s="9">
         <f t="shared" si="71"/>
-        <v>1079.5854079663382</v>
+        <v>1094.4988527439839</v>
       </c>
     </row>
     <row r="17" spans="2:168" x14ac:dyDescent="0.3">
@@ -4054,16 +4049,15 @@
         <v>28.5</v>
       </c>
       <c r="AJ17" s="6">
-        <f t="shared" ref="AJ17:AL17" si="72">AJ16*0.17</f>
-        <v>31.333379999999995</v>
+        <v>32.4</v>
       </c>
       <c r="AK17" s="6">
-        <f t="shared" si="72"/>
-        <v>46.441327599999994</v>
+        <f t="shared" ref="AK17:AL17" si="72">AK16*0.17</f>
+        <v>49.166269499999999</v>
       </c>
       <c r="AL17" s="6">
         <f t="shared" si="72"/>
-        <v>22.448055008000008</v>
+        <v>22.290138200000005</v>
       </c>
       <c r="AO17" s="6">
         <f>SUM(C17:F17)</f>
@@ -4099,43 +4093,43 @@
       </c>
       <c r="AW17" s="6">
         <f>SUM(AI17:AL17)</f>
-        <v>128.72276260799998</v>
+        <v>132.35640770000001</v>
       </c>
       <c r="AX17" s="6">
-        <f t="shared" ref="AX17:BC17" si="73">AX16*0.18</f>
-        <v>164.02453416864</v>
+        <f>AX16*0.17</f>
+        <v>157.07082163200005</v>
       </c>
       <c r="AY17" s="6">
-        <f t="shared" si="73"/>
-        <v>168.93087063497279</v>
+        <f t="shared" ref="AY17:BF17" si="73">AY16*0.17</f>
+        <v>161.76449775788012</v>
       </c>
       <c r="AZ17" s="6">
         <f t="shared" si="73"/>
-        <v>172.34566079367221</v>
+        <v>165.03221669203759</v>
       </c>
       <c r="BA17" s="6">
         <f t="shared" si="73"/>
-        <v>175.82910848300565</v>
+        <v>168.36561429466843</v>
       </c>
       <c r="BB17" s="6">
         <f t="shared" si="73"/>
-        <v>179.38259047086029</v>
+        <v>171.76600738203967</v>
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="73"/>
-        <v>183.00751109665413</v>
+        <v>175.23473913917309</v>
       </c>
       <c r="BD17" s="6">
-        <f t="shared" ref="BD17:BF17" si="74">BD16*0.18</f>
-        <v>186.70530282312757</v>
+        <f t="shared" si="73"/>
+        <v>178.7731796475442</v>
       </c>
       <c r="BE17" s="6">
-        <f t="shared" si="74"/>
-        <v>190.47742679917576</v>
+        <f t="shared" si="73"/>
+        <v>182.3827264233386</v>
       </c>
       <c r="BF17" s="6">
-        <f t="shared" si="74"/>
-        <v>194.32537343394085</v>
+        <f t="shared" si="73"/>
+        <v>186.06480496647728</v>
       </c>
     </row>
     <row r="18" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4143,660 +4137,660 @@
         <v>44</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:S18" si="75">C16-C17</f>
+        <f t="shared" ref="C18:S18" si="74">C16-C17</f>
         <v>36.799999999999962</v>
       </c>
       <c r="D18" s="9">
+        <f t="shared" si="74"/>
+        <v>56.4</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="74"/>
+        <v>80.799999999999969</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="74"/>
+        <v>34.39999999999997</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="74"/>
+        <v>38.400000000000006</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" si="74"/>
+        <v>64.2</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="74"/>
+        <v>112.89999999999995</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="74"/>
+        <v>42.199999999999989</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="74"/>
+        <v>45.400000000000063</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="74"/>
+        <v>73.000000000000057</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="74"/>
+        <v>117.50000000000006</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="74"/>
+        <v>213.80000000000007</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="74"/>
+        <v>72.199999999999989</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="74"/>
+        <v>266.90000000000003</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" si="74"/>
+        <v>382.59999999999997</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="74"/>
+        <v>225.7000000000001</v>
+      </c>
+      <c r="S18" s="9">
+        <f t="shared" si="74"/>
+        <v>186.89999999999989</v>
+      </c>
+      <c r="T18" s="9">
+        <f t="shared" ref="T18:U18" si="75">T16-T17</f>
+        <v>139.39999999999998</v>
+      </c>
+      <c r="U18" s="9">
         <f t="shared" si="75"/>
-        <v>56.4</v>
-      </c>
-      <c r="E18" s="9">
-        <f t="shared" si="75"/>
-        <v>80.799999999999969</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" si="75"/>
-        <v>34.39999999999997</v>
-      </c>
-      <c r="G18" s="9">
-        <f t="shared" si="75"/>
-        <v>38.400000000000006</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="75"/>
-        <v>64.2</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="75"/>
-        <v>112.89999999999995</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="75"/>
-        <v>42.199999999999989</v>
-      </c>
-      <c r="K18" s="9">
-        <f t="shared" si="75"/>
-        <v>45.400000000000063</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="75"/>
-        <v>73.000000000000057</v>
-      </c>
-      <c r="M18" s="9">
-        <f t="shared" si="75"/>
-        <v>117.50000000000006</v>
-      </c>
-      <c r="N18" s="9">
-        <f t="shared" si="75"/>
-        <v>213.80000000000007</v>
-      </c>
-      <c r="O18" s="9">
-        <f t="shared" si="75"/>
-        <v>72.199999999999989</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" si="75"/>
-        <v>266.90000000000003</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="75"/>
-        <v>382.59999999999997</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="75"/>
-        <v>225.7000000000001</v>
-      </c>
-      <c r="S18" s="9">
-        <f t="shared" si="75"/>
-        <v>186.89999999999989</v>
-      </c>
-      <c r="T18" s="9">
-        <f t="shared" ref="T18:U18" si="76">T16-T17</f>
-        <v>139.39999999999998</v>
-      </c>
-      <c r="U18" s="9">
+        <v>210.09999999999997</v>
+      </c>
+      <c r="V18" s="9">
+        <f t="shared" ref="V18:W18" si="76">V16-V17</f>
+        <v>108.20000000000005</v>
+      </c>
+      <c r="W18" s="9">
         <f t="shared" si="76"/>
-        <v>210.09999999999997</v>
-      </c>
-      <c r="V18" s="9">
-        <f t="shared" ref="V18:W18" si="77">V16-V17</f>
-        <v>108.20000000000005</v>
-      </c>
-      <c r="W18" s="9">
+        <v>100.80000000000011</v>
+      </c>
+      <c r="X18" s="9">
+        <f t="shared" ref="X18:Y18" si="77">X16-X17</f>
+        <v>82.199999999999932</v>
+      </c>
+      <c r="Y18" s="9">
         <f t="shared" si="77"/>
-        <v>100.80000000000011</v>
-      </c>
-      <c r="X18" s="9">
-        <f t="shared" ref="X18:Y18" si="78">X16-X17</f>
-        <v>82.199999999999932</v>
-      </c>
-      <c r="Y18" s="9">
-        <f t="shared" si="78"/>
         <v>140.00000000000011</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="79">Z16-Z17</f>
+        <f t="shared" ref="Z18" si="78">Z16-Z17</f>
         <v>41.59999999999998</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18" si="80">AA16-AA17</f>
+        <f t="shared" ref="AA18" si="79">AA16-AA17</f>
         <v>62.699999999999974</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" ref="AB18:AC18" si="81">AB16-AB17</f>
+        <f t="shared" ref="AB18:AC18" si="80">AB16-AB17</f>
         <v>137.20000000000002</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>244.50000000000003</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="82">AD16-AD17</f>
+        <f t="shared" ref="AD18" si="81">AD16-AD17</f>
         <v>167.6</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" ref="AE18" si="83">AE16-AE17</f>
+        <f t="shared" ref="AE18" si="82">AE16-AE17</f>
         <v>141.80000000000007</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18:AH18" si="84">AF16-AF17</f>
+        <f t="shared" ref="AF18:AH18" si="83">AF16-AF17</f>
         <v>145.30000000000001</v>
       </c>
       <c r="AG18" s="9">
+        <f t="shared" si="83"/>
+        <v>200.1999999999999</v>
+      </c>
+      <c r="AH18" s="9">
+        <f t="shared" si="83"/>
+        <v>144.20000000000002</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" ref="AI18:AL18" si="84">AI16-AI17</f>
+        <v>146.10000000000002</v>
+      </c>
+      <c r="AJ18" s="9">
         <f t="shared" si="84"/>
-        <v>200.1999999999999</v>
-      </c>
-      <c r="AH18" s="9">
+        <v>170.69999999999993</v>
+      </c>
+      <c r="AK18" s="9">
         <f t="shared" si="84"/>
-        <v>144.20000000000002</v>
-      </c>
-      <c r="AI18" s="9">
-        <f t="shared" ref="AI18:AL18" si="85">AI16-AI17</f>
-        <v>146.10000000000002</v>
-      </c>
-      <c r="AJ18" s="9">
+        <v>240.04708049999999</v>
+      </c>
+      <c r="AL18" s="9">
+        <f t="shared" si="84"/>
+        <v>108.82832180000003</v>
+      </c>
+      <c r="AO18" s="9">
+        <f t="shared" ref="AO18:AT18" si="85">AO16-AO17</f>
+        <v>208.40000000000043</v>
+      </c>
+      <c r="AP18" s="9">
         <f t="shared" si="85"/>
-        <v>152.98061999999996</v>
-      </c>
-      <c r="AK18" s="9">
+        <v>257.70000000000016</v>
+      </c>
+      <c r="AQ18" s="9">
         <f t="shared" si="85"/>
-        <v>226.74295239999995</v>
-      </c>
-      <c r="AL18" s="9">
+        <v>448.00000000000034</v>
+      </c>
+      <c r="AR18" s="9">
         <f t="shared" si="85"/>
-        <v>109.59932739200002</v>
-      </c>
-      <c r="AO18" s="9">
-        <f t="shared" ref="AO18:AT18" si="86">AO16-AO17</f>
-        <v>208.40000000000043</v>
-      </c>
-      <c r="AP18" s="9">
+        <v>947.39999999999918</v>
+      </c>
+      <c r="AS18" s="9">
+        <f t="shared" si="85"/>
+        <v>646.79999999999995</v>
+      </c>
+      <c r="AT18" s="9">
+        <f t="shared" si="85"/>
+        <v>364.60000000000088</v>
+      </c>
+      <c r="AU18" s="9">
+        <f t="shared" ref="AU18:BC18" si="86">AU16-AU17</f>
+        <v>612.00000000000045</v>
+      </c>
+      <c r="AV18" s="9">
         <f t="shared" si="86"/>
-        <v>257.70000000000016</v>
-      </c>
-      <c r="AQ18" s="9">
+        <v>631.49999999999989</v>
+      </c>
+      <c r="AW18" s="9">
         <f t="shared" si="86"/>
-        <v>448.00000000000034</v>
-      </c>
-      <c r="AR18" s="9">
+        <v>665.67540230000031</v>
+      </c>
+      <c r="AX18" s="9">
         <f t="shared" si="86"/>
-        <v>947.39999999999918</v>
-      </c>
-      <c r="AS18" s="9">
+        <v>766.87518796800009</v>
+      </c>
+      <c r="AY18" s="9">
         <f t="shared" si="86"/>
-        <v>646.79999999999995</v>
-      </c>
-      <c r="AT18" s="9">
+        <v>789.79137140612045</v>
+      </c>
+      <c r="AZ18" s="9">
         <f t="shared" si="86"/>
-        <v>364.60000000000088</v>
-      </c>
-      <c r="AU18" s="9">
-        <f t="shared" ref="AU18:BC18" si="87">AU16-AU17</f>
-        <v>612.00000000000045</v>
-      </c>
-      <c r="AV18" s="9">
+        <v>805.74552855524234</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="86"/>
+        <v>822.02035214455759</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" si="86"/>
+        <v>838.62227133584076</v>
+      </c>
+      <c r="BC18" s="9">
+        <f t="shared" si="86"/>
+        <v>855.5578440324332</v>
+      </c>
+      <c r="BD18" s="9">
+        <f t="shared" ref="BD18:BF18" si="87">BD16-BD17</f>
+        <v>872.83375945565683</v>
+      </c>
+      <c r="BE18" s="9">
         <f t="shared" si="87"/>
-        <v>631.49999999999989</v>
-      </c>
-      <c r="AW18" s="9">
+        <v>890.45684077277076</v>
+      </c>
+      <c r="BF18" s="9">
         <f t="shared" si="87"/>
-        <v>635.42289979200018</v>
-      </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="87"/>
-        <v>747.22287787936</v>
-      </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="87"/>
-        <v>769.57396622598708</v>
-      </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="87"/>
-        <v>785.13023250450681</v>
-      </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="87"/>
-        <v>800.9992719781369</v>
-      </c>
-      <c r="BB18" s="9">
-        <f t="shared" si="87"/>
-        <v>817.1873565894748</v>
-      </c>
-      <c r="BC18" s="9">
-        <f t="shared" si="87"/>
-        <v>833.70088388475779</v>
-      </c>
-      <c r="BD18" s="9">
-        <f t="shared" ref="BD18:BF18" si="88">BD16-BD17</f>
-        <v>850.54637952758117</v>
-      </c>
-      <c r="BE18" s="9">
-        <f t="shared" si="88"/>
-        <v>867.73049986291187</v>
-      </c>
-      <c r="BF18" s="9">
-        <f t="shared" si="88"/>
-        <v>885.2600345323973</v>
+        <v>908.43404777750663</v>
       </c>
       <c r="BG18" s="1">
         <f>BF18*(1+$BI$24)</f>
-        <v>876.40743418707336</v>
+        <v>899.34970729973156</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" ref="BH18:DS18" si="89">BG18*(1+$BI$24)</f>
-        <v>867.64335984520267</v>
+        <f t="shared" ref="BH18:DS18" si="88">BG18*(1+$BI$24)</f>
+        <v>890.35621022673422</v>
       </c>
       <c r="BI18" s="1">
+        <f t="shared" si="88"/>
+        <v>881.45264812446692</v>
+      </c>
+      <c r="BJ18" s="1">
+        <f t="shared" si="88"/>
+        <v>872.63812164322223</v>
+      </c>
+      <c r="BK18" s="1">
+        <f t="shared" si="88"/>
+        <v>863.91174042679006</v>
+      </c>
+      <c r="BL18" s="1">
+        <f t="shared" si="88"/>
+        <v>855.27262302252211</v>
+      </c>
+      <c r="BM18" s="1">
+        <f t="shared" si="88"/>
+        <v>846.71989679229694</v>
+      </c>
+      <c r="BN18" s="1">
+        <f t="shared" si="88"/>
+        <v>838.25269782437397</v>
+      </c>
+      <c r="BO18" s="1">
+        <f t="shared" si="88"/>
+        <v>829.87017084613024</v>
+      </c>
+      <c r="BP18" s="1">
+        <f t="shared" si="88"/>
+        <v>821.57146913766894</v>
+      </c>
+      <c r="BQ18" s="1">
+        <f t="shared" si="88"/>
+        <v>813.35575444629228</v>
+      </c>
+      <c r="BR18" s="1">
+        <f t="shared" si="88"/>
+        <v>805.22219690182931</v>
+      </c>
+      <c r="BS18" s="1">
+        <f t="shared" si="88"/>
+        <v>797.16997493281099</v>
+      </c>
+      <c r="BT18" s="1">
+        <f t="shared" si="88"/>
+        <v>789.19827518348291</v>
+      </c>
+      <c r="BU18" s="1">
+        <f t="shared" si="88"/>
+        <v>781.3062924316481</v>
+      </c>
+      <c r="BV18" s="1">
+        <f t="shared" si="88"/>
+        <v>773.49322950733165</v>
+      </c>
+      <c r="BW18" s="1">
+        <f t="shared" si="88"/>
+        <v>765.7582972122583</v>
+      </c>
+      <c r="BX18" s="1">
+        <f t="shared" si="88"/>
+        <v>758.10071424013574</v>
+      </c>
+      <c r="BY18" s="1">
+        <f t="shared" si="88"/>
+        <v>750.51970709773434</v>
+      </c>
+      <c r="BZ18" s="1">
+        <f t="shared" si="88"/>
+        <v>743.01451002675697</v>
+      </c>
+      <c r="CA18" s="1">
+        <f t="shared" si="88"/>
+        <v>735.58436492648934</v>
+      </c>
+      <c r="CB18" s="1">
+        <f t="shared" si="88"/>
+        <v>728.22852127722444</v>
+      </c>
+      <c r="CC18" s="1">
+        <f t="shared" si="88"/>
+        <v>720.94623606445225</v>
+      </c>
+      <c r="CD18" s="1">
+        <f t="shared" si="88"/>
+        <v>713.73677370380767</v>
+      </c>
+      <c r="CE18" s="1">
+        <f t="shared" si="88"/>
+        <v>706.59940596676961</v>
+      </c>
+      <c r="CF18" s="1">
+        <f t="shared" si="88"/>
+        <v>699.53341190710194</v>
+      </c>
+      <c r="CG18" s="1">
+        <f t="shared" si="88"/>
+        <v>692.53807778803093</v>
+      </c>
+      <c r="CH18" s="1">
+        <f t="shared" si="88"/>
+        <v>685.61269701015067</v>
+      </c>
+      <c r="CI18" s="1">
+        <f t="shared" si="88"/>
+        <v>678.75657004004916</v>
+      </c>
+      <c r="CJ18" s="1">
+        <f t="shared" si="88"/>
+        <v>671.96900433964868</v>
+      </c>
+      <c r="CK18" s="1">
+        <f t="shared" si="88"/>
+        <v>665.24931429625224</v>
+      </c>
+      <c r="CL18" s="1">
+        <f t="shared" si="88"/>
+        <v>658.59682115328974</v>
+      </c>
+      <c r="CM18" s="1">
+        <f t="shared" si="88"/>
+        <v>652.01085294175687</v>
+      </c>
+      <c r="CN18" s="1">
+        <f t="shared" si="88"/>
+        <v>645.49074441233927</v>
+      </c>
+      <c r="CO18" s="1">
+        <f t="shared" si="88"/>
+        <v>639.0358369682159</v>
+      </c>
+      <c r="CP18" s="1">
+        <f t="shared" si="88"/>
+        <v>632.64547859853371</v>
+      </c>
+      <c r="CQ18" s="1">
+        <f t="shared" si="88"/>
+        <v>626.31902381254838</v>
+      </c>
+      <c r="CR18" s="1">
+        <f t="shared" si="88"/>
+        <v>620.05583357442288</v>
+      </c>
+      <c r="CS18" s="1">
+        <f t="shared" si="88"/>
+        <v>613.85527523867859</v>
+      </c>
+      <c r="CT18" s="1">
+        <f t="shared" si="88"/>
+        <v>607.71672248629181</v>
+      </c>
+      <c r="CU18" s="1">
+        <f t="shared" si="88"/>
+        <v>601.63955526142888</v>
+      </c>
+      <c r="CV18" s="1">
+        <f t="shared" si="88"/>
+        <v>595.62315970881457</v>
+      </c>
+      <c r="CW18" s="1">
+        <f t="shared" si="88"/>
+        <v>589.66692811172641</v>
+      </c>
+      <c r="CX18" s="1">
+        <f t="shared" si="88"/>
+        <v>583.77025883060912</v>
+      </c>
+      <c r="CY18" s="1">
+        <f t="shared" si="88"/>
+        <v>577.93255624230301</v>
+      </c>
+      <c r="CZ18" s="1">
+        <f t="shared" si="88"/>
+        <v>572.15323067987993</v>
+      </c>
+      <c r="DA18" s="1">
+        <f t="shared" si="88"/>
+        <v>566.43169837308108</v>
+      </c>
+      <c r="DB18" s="1">
+        <f t="shared" si="88"/>
+        <v>560.76738138935025</v>
+      </c>
+      <c r="DC18" s="1">
+        <f t="shared" si="88"/>
+        <v>555.15970757545676</v>
+      </c>
+      <c r="DD18" s="1">
+        <f t="shared" si="88"/>
+        <v>549.60811049970221</v>
+      </c>
+      <c r="DE18" s="1">
+        <f t="shared" si="88"/>
+        <v>544.11202939470513</v>
+      </c>
+      <c r="DF18" s="1">
+        <f t="shared" si="88"/>
+        <v>538.67090910075808</v>
+      </c>
+      <c r="DG18" s="1">
+        <f t="shared" si="88"/>
+        <v>533.28420000975052</v>
+      </c>
+      <c r="DH18" s="1">
+        <f t="shared" si="88"/>
+        <v>527.95135800965306</v>
+      </c>
+      <c r="DI18" s="1">
+        <f t="shared" si="88"/>
+        <v>522.67184442955647</v>
+      </c>
+      <c r="DJ18" s="1">
+        <f t="shared" si="88"/>
+        <v>517.44512598526092</v>
+      </c>
+      <c r="DK18" s="1">
+        <f t="shared" si="88"/>
+        <v>512.2706747254083</v>
+      </c>
+      <c r="DL18" s="1">
+        <f t="shared" si="88"/>
+        <v>507.14796797815421</v>
+      </c>
+      <c r="DM18" s="1">
+        <f t="shared" si="88"/>
+        <v>502.07648829837268</v>
+      </c>
+      <c r="DN18" s="1">
+        <f t="shared" si="88"/>
+        <v>497.05572341538897</v>
+      </c>
+      <c r="DO18" s="1">
+        <f t="shared" si="88"/>
+        <v>492.08516618123508</v>
+      </c>
+      <c r="DP18" s="1">
+        <f t="shared" si="88"/>
+        <v>487.1643145194227</v>
+      </c>
+      <c r="DQ18" s="1">
+        <f t="shared" si="88"/>
+        <v>482.29267137422846</v>
+      </c>
+      <c r="DR18" s="1">
+        <f t="shared" si="88"/>
+        <v>477.46974466048619</v>
+      </c>
+      <c r="DS18" s="1">
+        <f t="shared" si="88"/>
+        <v>472.69504721388131</v>
+      </c>
+      <c r="DT18" s="1">
+        <f t="shared" ref="DT18:FL18" si="89">DS18*(1+$BI$24)</f>
+        <v>467.9680967417425</v>
+      </c>
+      <c r="DU18" s="1">
         <f t="shared" si="89"/>
-        <v>858.96692624675063</v>
-      </c>
-      <c r="BJ18" s="1">
+        <v>463.28841577432507</v>
+      </c>
+      <c r="DV18" s="1">
         <f t="shared" si="89"/>
-        <v>850.37725698428312</v>
-      </c>
-      <c r="BK18" s="1">
+        <v>458.65553161658181</v>
+      </c>
+      <c r="DW18" s="1">
         <f t="shared" si="89"/>
-        <v>841.87348441444033</v>
-      </c>
-      <c r="BL18" s="1">
+        <v>454.06897630041601</v>
+      </c>
+      <c r="DX18" s="1">
         <f t="shared" si="89"/>
-        <v>833.45474957029592</v>
-      </c>
-      <c r="BM18" s="1">
+        <v>449.52828653741187</v>
+      </c>
+      <c r="DY18" s="1">
         <f t="shared" si="89"/>
-        <v>825.12020207459295</v>
-      </c>
-      <c r="BN18" s="1">
+        <v>445.03300367203775</v>
+      </c>
+      <c r="DZ18" s="1">
         <f t="shared" si="89"/>
-        <v>816.869000053847</v>
-      </c>
-      <c r="BO18" s="1">
+        <v>440.58267363531735</v>
+      </c>
+      <c r="EA18" s="1">
         <f t="shared" si="89"/>
-        <v>808.7003100533085</v>
-      </c>
-      <c r="BP18" s="1">
+        <v>436.17684689896419</v>
+      </c>
+      <c r="EB18" s="1">
         <f t="shared" si="89"/>
-        <v>800.61330695277536</v>
-      </c>
-      <c r="BQ18" s="1">
+        <v>431.81507842997456</v>
+      </c>
+      <c r="EC18" s="1">
         <f t="shared" si="89"/>
-        <v>792.60717388324758</v>
-      </c>
-      <c r="BR18" s="1">
+        <v>427.49692764567482</v>
+      </c>
+      <c r="ED18" s="1">
         <f t="shared" si="89"/>
-        <v>784.68110214441515</v>
-      </c>
-      <c r="BS18" s="1">
+        <v>423.22195836921804</v>
+      </c>
+      <c r="EE18" s="1">
         <f t="shared" si="89"/>
-        <v>776.83429112297097</v>
-      </c>
-      <c r="BT18" s="1">
+        <v>418.98973878552584</v>
+      </c>
+      <c r="EF18" s="1">
         <f t="shared" si="89"/>
-        <v>769.06594821174122</v>
-      </c>
-      <c r="BU18" s="1">
+        <v>414.7998413976706</v>
+      </c>
+      <c r="EG18" s="1">
         <f t="shared" si="89"/>
-        <v>761.37528872962378</v>
-      </c>
-      <c r="BV18" s="1">
+        <v>410.65184298369388</v>
+      </c>
+      <c r="EH18" s="1">
         <f t="shared" si="89"/>
-        <v>753.76153584232748</v>
-      </c>
-      <c r="BW18" s="1">
+        <v>406.54532455385691</v>
+      </c>
+      <c r="EI18" s="1">
         <f t="shared" si="89"/>
-        <v>746.22392048390418</v>
-      </c>
-      <c r="BX18" s="1">
+        <v>402.47987130831837</v>
+      </c>
+      <c r="EJ18" s="1">
         <f t="shared" si="89"/>
-        <v>738.7616812790651</v>
-      </c>
-      <c r="BY18" s="1">
+        <v>398.45507259523515</v>
+      </c>
+      <c r="EK18" s="1">
         <f t="shared" si="89"/>
-        <v>731.37406446627449</v>
-      </c>
-      <c r="BZ18" s="1">
+        <v>394.47052186928278</v>
+      </c>
+      <c r="EL18" s="1">
         <f t="shared" si="89"/>
-        <v>724.06032382161175</v>
-      </c>
-      <c r="CA18" s="1">
+        <v>390.52581665058995</v>
+      </c>
+      <c r="EM18" s="1">
         <f t="shared" si="89"/>
-        <v>716.81972058339568</v>
-      </c>
-      <c r="CB18" s="1">
+        <v>386.62055848408403</v>
+      </c>
+      <c r="EN18" s="1">
         <f t="shared" si="89"/>
-        <v>709.65152337756172</v>
-      </c>
-      <c r="CC18" s="1">
+        <v>382.7543528992432</v>
+      </c>
+      <c r="EO18" s="1">
         <f t="shared" si="89"/>
-        <v>702.55500814378604</v>
-      </c>
-      <c r="CD18" s="1">
+        <v>378.92680937025079</v>
+      </c>
+      <c r="EP18" s="1">
         <f t="shared" si="89"/>
-        <v>695.52945806234823</v>
-      </c>
-      <c r="CE18" s="1">
+        <v>375.13754127654829</v>
+      </c>
+      <c r="EQ18" s="1">
         <f t="shared" si="89"/>
-        <v>688.57416348172478</v>
-      </c>
-      <c r="CF18" s="1">
+        <v>371.38616586378282</v>
+      </c>
+      <c r="ER18" s="1">
         <f t="shared" si="89"/>
-        <v>681.68842184690754</v>
-      </c>
-      <c r="CG18" s="1">
+        <v>367.672304205145</v>
+      </c>
+      <c r="ES18" s="1">
         <f t="shared" si="89"/>
-        <v>674.87153762843843</v>
-      </c>
-      <c r="CH18" s="1">
+        <v>363.99558116309356</v>
+      </c>
+      <c r="ET18" s="1">
         <f t="shared" si="89"/>
-        <v>668.12282225215404</v>
-      </c>
-      <c r="CI18" s="1">
+        <v>360.35562535146261</v>
+      </c>
+      <c r="EU18" s="1">
         <f t="shared" si="89"/>
-        <v>661.44159402963248</v>
-      </c>
-      <c r="CJ18" s="1">
+        <v>356.75206909794798</v>
+      </c>
+      <c r="EV18" s="1">
         <f t="shared" si="89"/>
-        <v>654.82717808933614</v>
-      </c>
-      <c r="CK18" s="1">
+        <v>353.18454840696847</v>
+      </c>
+      <c r="EW18" s="1">
         <f t="shared" si="89"/>
-        <v>648.27890630844274</v>
-      </c>
-      <c r="CL18" s="1">
+        <v>349.65270292289881</v>
+      </c>
+      <c r="EX18" s="1">
         <f t="shared" si="89"/>
-        <v>641.79611724535835</v>
-      </c>
-      <c r="CM18" s="1">
+        <v>346.1561758936698</v>
+      </c>
+      <c r="EY18" s="1">
         <f t="shared" si="89"/>
-        <v>635.37815607290474</v>
-      </c>
-      <c r="CN18" s="1">
+        <v>342.69461413473311</v>
+      </c>
+      <c r="EZ18" s="1">
         <f t="shared" si="89"/>
-        <v>629.02437451217565</v>
-      </c>
-      <c r="CO18" s="1">
+        <v>339.26766799338577</v>
+      </c>
+      <c r="FA18" s="1">
         <f t="shared" si="89"/>
-        <v>622.7341307670539</v>
-      </c>
-      <c r="CP18" s="1">
+        <v>335.87499131345191</v>
+      </c>
+      <c r="FB18" s="1">
         <f t="shared" si="89"/>
-        <v>616.5067894593833</v>
-      </c>
-      <c r="CQ18" s="1">
+        <v>332.51624140031737</v>
+      </c>
+      <c r="FC18" s="1">
         <f t="shared" si="89"/>
-        <v>610.34172156478951</v>
-      </c>
-      <c r="CR18" s="1">
+        <v>329.19107898631421</v>
+      </c>
+      <c r="FD18" s="1">
         <f t="shared" si="89"/>
-        <v>604.23830434914157</v>
-      </c>
-      <c r="CS18" s="1">
+        <v>325.89916819645106</v>
+      </c>
+      <c r="FE18" s="1">
         <f t="shared" si="89"/>
-        <v>598.19592130565013</v>
-      </c>
-      <c r="CT18" s="1">
+        <v>322.64017651448654</v>
+      </c>
+      <c r="FF18" s="1">
         <f t="shared" si="89"/>
-        <v>592.21396209259365</v>
-      </c>
-      <c r="CU18" s="1">
+        <v>319.41377474934166</v>
+      </c>
+      <c r="FG18" s="1">
         <f t="shared" si="89"/>
-        <v>586.29182247166773</v>
-      </c>
-      <c r="CV18" s="1">
+        <v>316.21963700184824</v>
+      </c>
+      <c r="FH18" s="1">
         <f t="shared" si="89"/>
-        <v>580.42890424695099</v>
-      </c>
-      <c r="CW18" s="1">
+        <v>313.05744063182976</v>
+      </c>
+      <c r="FI18" s="1">
         <f t="shared" si="89"/>
-        <v>574.62461520448153</v>
-      </c>
-      <c r="CX18" s="1">
+        <v>309.92686622551145</v>
+      </c>
+      <c r="FJ18" s="1">
         <f t="shared" si="89"/>
-        <v>568.87836905243671</v>
-      </c>
-      <c r="CY18" s="1">
+        <v>306.82759756325635</v>
+      </c>
+      <c r="FK18" s="1">
         <f t="shared" si="89"/>
-        <v>563.18958536191235</v>
-      </c>
-      <c r="CZ18" s="1">
+        <v>303.75932158762379</v>
+      </c>
+      <c r="FL18" s="1">
         <f t="shared" si="89"/>
-        <v>557.55768950829327</v>
-      </c>
-      <c r="DA18" s="1">
-        <f t="shared" si="89"/>
-        <v>551.98211261321035</v>
-      </c>
-      <c r="DB18" s="1">
-        <f t="shared" si="89"/>
-        <v>546.46229148707823</v>
-      </c>
-      <c r="DC18" s="1">
-        <f t="shared" si="89"/>
-        <v>540.99766857220743</v>
-      </c>
-      <c r="DD18" s="1">
-        <f t="shared" si="89"/>
-        <v>535.58769188648535</v>
-      </c>
-      <c r="DE18" s="1">
-        <f t="shared" si="89"/>
-        <v>530.23181496762049</v>
-      </c>
-      <c r="DF18" s="1">
-        <f t="shared" si="89"/>
-        <v>524.92949681794425</v>
-      </c>
-      <c r="DG18" s="1">
-        <f t="shared" si="89"/>
-        <v>519.68020184976479</v>
-      </c>
-      <c r="DH18" s="1">
-        <f t="shared" si="89"/>
-        <v>514.48339983126709</v>
-      </c>
-      <c r="DI18" s="1">
-        <f t="shared" si="89"/>
-        <v>509.33856583295443</v>
-      </c>
-      <c r="DJ18" s="1">
-        <f t="shared" si="89"/>
-        <v>504.24518017462486</v>
-      </c>
-      <c r="DK18" s="1">
-        <f t="shared" si="89"/>
-        <v>499.2027283728786</v>
-      </c>
-      <c r="DL18" s="1">
-        <f t="shared" si="89"/>
-        <v>494.21070108914978</v>
-      </c>
-      <c r="DM18" s="1">
-        <f t="shared" si="89"/>
-        <v>489.26859407825827</v>
-      </c>
-      <c r="DN18" s="1">
-        <f t="shared" si="89"/>
-        <v>484.37590813747568</v>
-      </c>
-      <c r="DO18" s="1">
-        <f t="shared" si="89"/>
-        <v>479.53214905610093</v>
-      </c>
-      <c r="DP18" s="1">
-        <f t="shared" si="89"/>
-        <v>474.7368275655399</v>
-      </c>
-      <c r="DQ18" s="1">
-        <f t="shared" si="89"/>
-        <v>469.98945928988451</v>
-      </c>
-      <c r="DR18" s="1">
-        <f t="shared" si="89"/>
-        <v>465.28956469698568</v>
-      </c>
-      <c r="DS18" s="1">
-        <f t="shared" si="89"/>
-        <v>460.63666905001583</v>
-      </c>
-      <c r="DT18" s="1">
-        <f t="shared" ref="DT18:FL18" si="90">DS18*(1+$BI$24)</f>
-        <v>456.03030235951564</v>
-      </c>
-      <c r="DU18" s="1">
-        <f t="shared" si="90"/>
-        <v>451.46999933592048</v>
-      </c>
-      <c r="DV18" s="1">
-        <f t="shared" si="90"/>
-        <v>446.95529934256126</v>
-      </c>
-      <c r="DW18" s="1">
-        <f t="shared" si="90"/>
-        <v>442.48574634913564</v>
-      </c>
-      <c r="DX18" s="1">
-        <f t="shared" si="90"/>
-        <v>438.06088888564426</v>
-      </c>
-      <c r="DY18" s="1">
-        <f t="shared" si="90"/>
-        <v>433.68027999678782</v>
-      </c>
-      <c r="DZ18" s="1">
-        <f t="shared" si="90"/>
-        <v>429.34347719681995</v>
-      </c>
-      <c r="EA18" s="1">
-        <f t="shared" si="90"/>
-        <v>425.05004242485177</v>
-      </c>
-      <c r="EB18" s="1">
-        <f t="shared" si="90"/>
-        <v>420.79954200060325</v>
-      </c>
-      <c r="EC18" s="1">
-        <f t="shared" si="90"/>
-        <v>416.5915465805972</v>
-      </c>
-      <c r="ED18" s="1">
-        <f t="shared" si="90"/>
-        <v>412.4256311147912</v>
-      </c>
-      <c r="EE18" s="1">
-        <f t="shared" si="90"/>
-        <v>408.30137480364328</v>
-      </c>
-      <c r="EF18" s="1">
-        <f t="shared" si="90"/>
-        <v>404.21836105560686</v>
-      </c>
-      <c r="EG18" s="1">
-        <f t="shared" si="90"/>
-        <v>400.17617744505077</v>
-      </c>
-      <c r="EH18" s="1">
-        <f t="shared" si="90"/>
-        <v>396.17441567060024</v>
-      </c>
-      <c r="EI18" s="1">
-        <f t="shared" si="90"/>
-        <v>392.21267151389424</v>
-      </c>
-      <c r="EJ18" s="1">
-        <f t="shared" si="90"/>
-        <v>388.29054479875526</v>
-      </c>
-      <c r="EK18" s="1">
-        <f t="shared" si="90"/>
-        <v>384.40763935076768</v>
-      </c>
-      <c r="EL18" s="1">
-        <f t="shared" si="90"/>
-        <v>380.56356295725999</v>
-      </c>
-      <c r="EM18" s="1">
-        <f t="shared" si="90"/>
-        <v>376.75792732768741</v>
-      </c>
-      <c r="EN18" s="1">
-        <f t="shared" si="90"/>
-        <v>372.99034805441056</v>
-      </c>
-      <c r="EO18" s="1">
-        <f t="shared" si="90"/>
-        <v>369.26044457386644</v>
-      </c>
-      <c r="EP18" s="1">
-        <f t="shared" si="90"/>
-        <v>365.56784012812778</v>
-      </c>
-      <c r="EQ18" s="1">
-        <f t="shared" si="90"/>
-        <v>361.91216172684648</v>
-      </c>
-      <c r="ER18" s="1">
-        <f t="shared" si="90"/>
-        <v>358.29304010957799</v>
-      </c>
-      <c r="ES18" s="1">
-        <f t="shared" si="90"/>
-        <v>354.71010970848221</v>
-      </c>
-      <c r="ET18" s="1">
-        <f t="shared" si="90"/>
-        <v>351.1630086113974</v>
-      </c>
-      <c r="EU18" s="1">
-        <f t="shared" si="90"/>
-        <v>347.65137852528341</v>
-      </c>
-      <c r="EV18" s="1">
-        <f t="shared" si="90"/>
-        <v>344.17486474003056</v>
-      </c>
-      <c r="EW18" s="1">
-        <f t="shared" si="90"/>
-        <v>340.73311609263027</v>
-      </c>
-      <c r="EX18" s="1">
-        <f t="shared" si="90"/>
-        <v>337.32578493170394</v>
-      </c>
-      <c r="EY18" s="1">
-        <f t="shared" si="90"/>
-        <v>333.95252708238689</v>
-      </c>
-      <c r="EZ18" s="1">
-        <f t="shared" si="90"/>
-        <v>330.61300181156304</v>
-      </c>
-      <c r="FA18" s="1">
-        <f t="shared" si="90"/>
-        <v>327.30687179344739</v>
-      </c>
-      <c r="FB18" s="1">
-        <f t="shared" si="90"/>
-        <v>324.03380307551294</v>
-      </c>
-      <c r="FC18" s="1">
-        <f t="shared" si="90"/>
-        <v>320.7934650447578</v>
-      </c>
-      <c r="FD18" s="1">
-        <f t="shared" si="90"/>
-        <v>317.58553039431024</v>
-      </c>
-      <c r="FE18" s="1">
-        <f t="shared" si="90"/>
-        <v>314.40967509036716</v>
-      </c>
-      <c r="FF18" s="1">
-        <f t="shared" si="90"/>
-        <v>311.2655783394635</v>
-      </c>
-      <c r="FG18" s="1">
-        <f t="shared" si="90"/>
-        <v>308.15292255606886</v>
-      </c>
-      <c r="FH18" s="1">
-        <f t="shared" si="90"/>
-        <v>305.07139333050816</v>
-      </c>
-      <c r="FI18" s="1">
-        <f t="shared" si="90"/>
-        <v>302.02067939720308</v>
-      </c>
-      <c r="FJ18" s="1">
-        <f t="shared" si="90"/>
-        <v>299.00047260323106</v>
-      </c>
-      <c r="FK18" s="1">
-        <f t="shared" si="90"/>
-        <v>296.01046787719872</v>
-      </c>
-      <c r="FL18" s="1">
-        <f t="shared" si="90"/>
-        <v>293.05036319842674</v>
+        <v>300.72172837174753</v>
       </c>
     </row>
     <row r="19" spans="2:168" x14ac:dyDescent="0.3">
@@ -4906,16 +4900,16 @@
         <v>147.9</v>
       </c>
       <c r="AJ19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f>147.1</f>
+        <v>147.1</v>
       </c>
       <c r="AK19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f>147.1</f>
+        <v>147.1</v>
       </c>
       <c r="AL19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f>147.1</f>
+        <v>147.1</v>
       </c>
       <c r="AO19" s="6">
         <v>168.4</v>
@@ -4943,44 +4937,44 @@
         <v>149</v>
       </c>
       <c r="AW19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" ref="AW19:BF19" si="90">147.1</f>
+        <v>147.1</v>
       </c>
       <c r="AX19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="AY19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="AZ19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="BA19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="BB19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="BC19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="BD19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="BE19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
       <c r="BF19" s="6">
-        <f>147.9</f>
-        <v>147.9</v>
+        <f t="shared" si="90"/>
+        <v>147.1</v>
       </c>
     </row>
     <row r="20" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5121,15 +5115,15 @@
       </c>
       <c r="AJ20" s="8">
         <f t="shared" si="101"/>
-        <v>1.0343517241379308</v>
+        <v>1.1604350781781096</v>
       </c>
       <c r="AK20" s="8">
         <f t="shared" si="101"/>
-        <v>1.533082842461122</v>
+        <v>1.6318632256968049</v>
       </c>
       <c r="AL20" s="8">
         <f t="shared" si="101"/>
-        <v>0.7410366963624071</v>
+        <v>0.73982543711760729</v>
       </c>
       <c r="AO20" s="8">
         <f t="shared" ref="AO20:AT20" si="102">AO18/AO19</f>
@@ -5165,43 +5159,43 @@
       </c>
       <c r="AW20" s="8">
         <f t="shared" si="103"/>
-        <v>4.2963008775659244</v>
+        <v>4.5253256444595538</v>
       </c>
       <c r="AX20" s="8">
         <f t="shared" si="103"/>
-        <v>5.0522168889747121</v>
+        <v>5.2132915565465678</v>
       </c>
       <c r="AY20" s="8">
         <f t="shared" si="103"/>
-        <v>5.2033398663014676</v>
+        <v>5.369077983726176</v>
       </c>
       <c r="AZ20" s="8">
         <f t="shared" si="103"/>
-        <v>5.3085208418154615</v>
+        <v>5.4775358841280921</v>
       </c>
       <c r="BA20" s="8">
         <f t="shared" si="103"/>
-        <v>5.415816578621615</v>
+        <v>5.5881737059453274</v>
       </c>
       <c r="BB20" s="8">
         <f t="shared" si="103"/>
-        <v>5.5252694833635889</v>
+        <v>5.7010351552402501</v>
       </c>
       <c r="BC20" s="8">
         <f t="shared" si="103"/>
-        <v>5.6369228119321013</v>
+        <v>5.8161648132728292</v>
       </c>
       <c r="BD20" s="8">
         <f t="shared" ref="BD20:BF20" si="104">BD18/BD19</f>
-        <v>5.7508206864609948</v>
+        <v>5.9336081540153423</v>
       </c>
       <c r="BE20" s="8">
         <f t="shared" si="104"/>
-        <v>5.867008112663366</v>
+        <v>6.0534115620174767</v>
       </c>
       <c r="BF20" s="8">
         <f t="shared" si="104"/>
-        <v>5.9855309975145188</v>
+        <v>6.1756223506288697</v>
       </c>
     </row>
     <row r="22" spans="2:168" x14ac:dyDescent="0.3">
@@ -5330,7 +5324,7 @@
       </c>
       <c r="AJ22" s="10">
         <f t="shared" ref="AJ22" si="119">AJ3/AF3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>6.2813620071684451E-2</v>
       </c>
       <c r="AK22" s="10">
         <f t="shared" ref="AK22" si="120">AK3/AG3-1</f>
@@ -5371,7 +5365,7 @@
       </c>
       <c r="AW22" s="10">
         <f t="shared" si="122"/>
-        <v>4.8899207446925441E-2</v>
+        <v>5.203868361544739E-2</v>
       </c>
       <c r="AX22" s="10">
         <f t="shared" si="122"/>
@@ -5548,11 +5542,11 @@
       </c>
       <c r="AJ23" s="10">
         <f t="shared" si="129"/>
-        <v>0.43</v>
+        <v>0.43562937357727</v>
       </c>
       <c r="AK23" s="10">
         <f t="shared" si="129"/>
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="AL23" s="10">
         <f t="shared" si="129"/>
@@ -5592,11 +5586,11 @@
       </c>
       <c r="AW23" s="10">
         <f t="shared" si="130"/>
-        <v>0.42740226903249751</v>
+        <v>0.43174024834664776</v>
       </c>
       <c r="AX23" s="10">
         <f t="shared" si="130"/>
-        <v>0.44</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="AY23" s="10">
         <f t="shared" si="130"/>
@@ -5608,19 +5602,19 @@
       </c>
       <c r="BA23" s="10">
         <f t="shared" si="130"/>
-        <v>0.44</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="BB23" s="10">
         <f t="shared" si="130"/>
-        <v>0.43999999999999995</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="BC23" s="10">
         <f t="shared" si="130"/>
-        <v>0.44000000000000006</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="BD23" s="10">
         <f t="shared" ref="BD23:BF23" si="131">BD5/BD3</f>
-        <v>0.44</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="BE23" s="10">
         <f t="shared" si="131"/>
@@ -5628,7 +5622,7 @@
       </c>
       <c r="BF23" s="10">
         <f t="shared" si="131"/>
-        <v>0.44</v>
+        <v>0.44000000000000006</v>
       </c>
     </row>
     <row r="24" spans="2:168" x14ac:dyDescent="0.3">
@@ -5769,15 +5763,15 @@
       </c>
       <c r="AJ24" s="10">
         <f t="shared" si="135"/>
-        <v>0.14915343915343912</v>
+        <v>0.16136919315403417</v>
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="135"/>
-        <v>0.18709542639707524</v>
+        <v>0.19829203127942216</v>
       </c>
       <c r="AL24" s="10">
         <f t="shared" si="135"/>
-        <v>0.11591833394238385</v>
+        <v>0.11476779950057862</v>
       </c>
       <c r="AO24" s="10">
         <f t="shared" ref="AO24:BC24" si="136">AO13/AO3</f>
@@ -5813,43 +5807,43 @@
       </c>
       <c r="AW24" s="10">
         <f t="shared" si="136"/>
-        <v>0.15113955849666916</v>
+        <v>0.15719324631343817</v>
       </c>
       <c r="AX24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17377731791212969</v>
+        <v>0.17563979651819503</v>
       </c>
       <c r="AY24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17385507400460504</v>
+        <v>0.17571338534107528</v>
       </c>
       <c r="AZ24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17389357089352667</v>
+        <v>0.17574981902299133</v>
       </c>
       <c r="BA24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17393169036196865</v>
+        <v>0.17578589551194765</v>
       </c>
       <c r="BB24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17396943611013174</v>
+        <v>0.17582161830983567</v>
       </c>
       <c r="BC24" s="10">
         <f t="shared" si="136"/>
-        <v>0.17400681180194041</v>
+        <v>0.17585699088421489</v>
       </c>
       <c r="BD24" s="10">
         <f t="shared" ref="BD24:BF24" si="137">BD13/BD3</f>
-        <v>0.17404382106539801</v>
+        <v>0.17589201666864934</v>
       </c>
       <c r="BE24" s="10">
         <f t="shared" si="137"/>
-        <v>0.17408046749293926</v>
+        <v>0.17592669906304031</v>
       </c>
       <c r="BF24" s="10">
         <f t="shared" si="137"/>
-        <v>0.17411675464177917</v>
+        <v>0.17596104143395683</v>
       </c>
       <c r="BH24" t="s">
         <v>55</v>
@@ -5996,7 +5990,7 @@
       </c>
       <c r="AJ25" s="10">
         <f t="shared" si="141"/>
-        <v>0.17</v>
+        <v>0.16777674732315995</v>
       </c>
       <c r="AK25" s="10">
         <f t="shared" si="141"/>
@@ -6040,7 +6034,7 @@
       </c>
       <c r="AW25" s="10">
         <f t="shared" si="142"/>
-        <v>0.1686522651079583</v>
+        <v>0.16810598691842596</v>
       </c>
       <c r="AX25" s="10">
         <f t="shared" si="142"/>
@@ -6211,7 +6205,7 @@
       </c>
       <c r="AJ26" s="10">
         <f t="shared" ref="AJ26:AJ27" si="173">AJ7/AF7-1</f>
-        <v>4.0000000000000036E-2</v>
+        <v>-1.312335958005395E-3</v>
       </c>
       <c r="AK26" s="10">
         <f t="shared" ref="AK26:AK27" si="174">AK7/AG7-1</f>
@@ -6252,7 +6246,7 @@
       </c>
       <c r="AW26" s="10">
         <f t="shared" si="176"/>
-        <v>3.0559870550161961E-2</v>
+        <v>2.0372168284789716E-2</v>
       </c>
       <c r="AX26" s="10">
         <f t="shared" si="176"/>
@@ -6295,7 +6289,7 @@
       </c>
       <c r="BI26" s="6">
         <f>NPV(BI25,AW18:FL18)</f>
-        <v>9777.4050859448016</v>
+        <v>10046.245389773256</v>
       </c>
     </row>
     <row r="27" spans="2:168" x14ac:dyDescent="0.3">
@@ -6424,15 +6418,15 @@
       </c>
       <c r="AJ27" s="10">
         <f t="shared" si="173"/>
-        <v>1.0000000000000009E-2</v>
+        <v>-5.4298642533936792E-2</v>
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="174"/>
-        <v>6.0000000000000053E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL27" s="10">
         <f t="shared" si="175"/>
-        <v>4.0000000000000036E-2</v>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AO27" s="10"/>
       <c r="AP27" s="10">
@@ -6465,7 +6459,7 @@
       </c>
       <c r="AW27" s="10">
         <f t="shared" si="180"/>
-        <v>5.4113345521023648E-2</v>
+        <v>3.3900060938452103E-2</v>
       </c>
       <c r="AX27" s="10">
         <f t="shared" si="180"/>
@@ -6508,7 +6502,7 @@
       </c>
       <c r="BI27" s="6">
         <f>Main!D8</f>
-        <v>1487.8</v>
+        <v>1375.8</v>
       </c>
     </row>
     <row r="28" spans="2:168" x14ac:dyDescent="0.3">
@@ -6649,7 +6643,7 @@
       </c>
       <c r="AJ28" s="10">
         <f t="shared" si="184"/>
-        <v>0.17</v>
+        <v>0.15952732644017731</v>
       </c>
       <c r="AK28" s="10">
         <f t="shared" si="184"/>
@@ -6693,50 +6687,50 @@
       </c>
       <c r="AW28" s="10">
         <f t="shared" si="185"/>
-        <v>0.16845317449517719</v>
+        <v>0.16585354874513081</v>
       </c>
       <c r="AX28" s="10">
         <f t="shared" si="185"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AY28" s="10">
         <f t="shared" si="185"/>
-        <v>0.18</v>
+        <v>0.17000000000000004</v>
       </c>
       <c r="AZ28" s="10">
         <f t="shared" si="185"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA28" s="10">
         <f t="shared" si="185"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BB28" s="10">
         <f t="shared" si="185"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BC28" s="10">
         <f t="shared" si="185"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BD28" s="10">
         <f t="shared" ref="BD28:BF28" si="186">BD17/BD16</f>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BE28" s="10">
         <f t="shared" si="186"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BF28" s="10">
         <f t="shared" si="186"/>
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BH28" t="s">
         <v>59</v>
       </c>
       <c r="BI28" s="6">
         <f>BI26+BI27</f>
-        <v>11265.205085944801</v>
+        <v>11422.045389773255</v>
       </c>
     </row>
     <row r="29" spans="2:168" x14ac:dyDescent="0.3">
@@ -6877,15 +6871,15 @@
       </c>
       <c r="AJ29" s="10">
         <f t="shared" si="190"/>
-        <v>0.13055181771633381</v>
+        <v>0.14391703903549444</v>
       </c>
       <c r="AK29" s="10">
         <f t="shared" si="190"/>
-        <v>0.1611174132301581</v>
+        <v>0.17057096705428421</v>
       </c>
       <c r="AL29" s="10">
         <f t="shared" si="190"/>
-        <v>0.1042992563798039</v>
+        <v>0.10356553554570926</v>
       </c>
       <c r="AO29" s="10">
         <f t="shared" ref="AO29:BC29" si="191">AO18/AO3</f>
@@ -6921,50 +6915,50 @@
       </c>
       <c r="AW29" s="10">
         <f t="shared" si="191"/>
-        <v>0.13299957652485095</v>
+        <v>0.13891589889336892</v>
       </c>
       <c r="AX29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15038489502903457</v>
+        <v>0.15387950878899742</v>
       </c>
       <c r="AY29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15037207740990233</v>
+        <v>0.15386196151510556</v>
       </c>
       <c r="AZ29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15040364485881808</v>
+        <v>0.15389220147109589</v>
       </c>
       <c r="BA29" s="10">
         <f t="shared" si="191"/>
-        <v>0.1504349028229405</v>
+        <v>0.15392214495692963</v>
       </c>
       <c r="BB29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15046585433643425</v>
+        <v>0.15395179487917668</v>
       </c>
       <c r="BC29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15049650240371737</v>
+        <v>0.15398115411591143</v>
       </c>
       <c r="BD29" s="10">
         <f t="shared" ref="BD29:BF29" si="192">BD18/BD3</f>
-        <v>0.15052684999975258</v>
+        <v>0.15401022551699203</v>
       </c>
       <c r="BE29" s="10">
         <f t="shared" si="192"/>
-        <v>0.1505569000703364</v>
+        <v>0.15403901190433655</v>
       </c>
       <c r="BF29" s="10">
         <f t="shared" si="192"/>
-        <v>0.15058665553238512</v>
+        <v>0.15406751607219724</v>
       </c>
       <c r="BH29" t="s">
         <v>60</v>
       </c>
       <c r="BI29" s="5">
         <f>BI28/BC19</f>
-        <v>76.167715253176468</v>
+        <v>77.648167163652317</v>
       </c>
     </row>
     <row r="30" spans="2:168" x14ac:dyDescent="0.3">
@@ -6973,7 +6967,7 @@
       </c>
       <c r="BI30" s="5">
         <f>Main!D3</f>
-        <v>96.92</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="31" spans="2:168" x14ac:dyDescent="0.3">
@@ -6982,7 +6976,7 @@
       </c>
       <c r="BI31" s="11">
         <f>BI29/BI30-1</f>
-        <v>-0.21411767175839391</v>
+        <v>-0.32655535851125483</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">

--- a/Financial Analysis/LOGI.xlsx
+++ b/Financial Analysis/LOGI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49AC922-E0A1-4C71-BAEA-3A9A9EEC12D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16D903F-6C0E-4046-B2F6-8D07ACF26098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{439F4133-7664-46FF-BA84-0DE877A2D3CB}"/>
   </bookViews>
@@ -268,7 +268,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -369,14 +369,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -393,7 +393,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26715720" y="7620"/>
+          <a:off x="27454860" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -793,17 +793,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>115.3</v>
+        <v>88.17</v>
       </c>
       <c r="E3" s="4">
-        <v>45959</v>
+        <v>46056</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45959</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="4">
-        <v>46048</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,11 +811,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>147.1</f>
-        <v>147.1</v>
+        <f>146.6</f>
+        <v>146.6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +824,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>16960.629999999997</v>
+        <v>12925.722</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -832,11 +832,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1375.8</f>
-        <v>1375.8</v>
+        <f>1817.8</f>
+        <v>1817.8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -856,7 +856,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>1375.8</v>
+        <v>1817.8</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>15584.829999999998</v>
+        <v>11107.922</v>
       </c>
     </row>
   </sheetData>
@@ -1321,12 +1321,11 @@
         <v>1186.0999999999999</v>
       </c>
       <c r="AK3" s="9">
-        <f t="shared" ref="AK3" si="0">AG3*1.05</f>
-        <v>1407.3150000000001</v>
+        <v>1421.5</v>
       </c>
       <c r="AL3" s="9">
-        <f>AH3*1.04</f>
-        <v>1050.816</v>
+        <f>AH3*1.06</f>
+        <v>1071.0240000000001</v>
       </c>
       <c r="AO3" s="9">
         <f>SUM(C3:F3)</f>
@@ -1362,43 +1361,43 @@
       </c>
       <c r="AW3" s="9">
         <f>SUM(AI3:AL3)</f>
-        <v>4791.9310000000005</v>
+        <v>4826.3240000000005</v>
       </c>
       <c r="AX3" s="9">
         <f>AW3*1.04</f>
-        <v>4983.6082400000005</v>
+        <v>5019.3769600000005</v>
       </c>
       <c r="AY3" s="9">
         <f>AX3*1.03</f>
-        <v>5133.1164872000008</v>
+        <v>5169.958268800001</v>
       </c>
       <c r="AZ3" s="9">
         <f>AY3*1.02</f>
-        <v>5235.7788169440009</v>
+        <v>5273.3574341760013</v>
       </c>
       <c r="BA3" s="9">
-        <f t="shared" ref="BA3:BF3" si="1">AZ3*1.02</f>
-        <v>5340.494393282881</v>
+        <f t="shared" ref="BA3:BF3" si="0">AZ3*1.02</f>
+        <v>5378.8245828595218</v>
       </c>
       <c r="BB3" s="9">
-        <f t="shared" si="1"/>
-        <v>5447.3042811485384</v>
+        <f t="shared" si="0"/>
+        <v>5486.4010745167125</v>
       </c>
       <c r="BC3" s="9">
-        <f t="shared" si="1"/>
-        <v>5556.2503667715091</v>
+        <f t="shared" si="0"/>
+        <v>5596.1290960070464</v>
       </c>
       <c r="BD3" s="9">
-        <f t="shared" si="1"/>
-        <v>5667.3753741069395</v>
+        <f t="shared" si="0"/>
+        <v>5708.0516779271875</v>
       </c>
       <c r="BE3" s="9">
-        <f t="shared" si="1"/>
-        <v>5780.7228815890785</v>
+        <f t="shared" si="0"/>
+        <v>5822.2127114857312</v>
       </c>
       <c r="BF3" s="9">
-        <f t="shared" si="1"/>
-        <v>5896.3373392208605</v>
+        <f t="shared" si="0"/>
+        <v>5938.6569657154459</v>
       </c>
     </row>
     <row r="4" spans="2:58" x14ac:dyDescent="0.3">
@@ -1508,12 +1507,11 @@
         <v>669.4</v>
       </c>
       <c r="AK4" s="6">
-        <f t="shared" ref="AK4:AL4" si="2">AK3-AK5</f>
-        <v>788.09640000000002</v>
+        <v>805.3</v>
       </c>
       <c r="AL4" s="6">
-        <f t="shared" si="2"/>
-        <v>598.96512000000007</v>
+        <f t="shared" ref="AL4" si="1">AL3-AL5</f>
+        <v>610.48368000000005</v>
       </c>
       <c r="AO4" s="6">
         <f>SUM(C4:F4)</f>
@@ -1549,43 +1547,43 @@
       </c>
       <c r="AW4" s="6">
         <f>SUM(AI4:AL4)</f>
-        <v>2723.0615200000002</v>
+        <v>2751.7836800000005</v>
       </c>
       <c r="AX4" s="6">
-        <f t="shared" ref="AX4:BC4" si="3">AX3-AX5</f>
-        <v>2790.8206144000001</v>
+        <f t="shared" ref="AX4:BC4" si="2">AX3-AX5</f>
+        <v>2861.0448672000002</v>
       </c>
       <c r="AY4" s="6">
+        <f t="shared" si="2"/>
+        <v>2946.8762132160005</v>
+      </c>
+      <c r="AZ4" s="6">
+        <f t="shared" si="2"/>
+        <v>3005.8137374803209</v>
+      </c>
+      <c r="BA4" s="6">
+        <f t="shared" si="2"/>
+        <v>3065.9300122299273</v>
+      </c>
+      <c r="BB4" s="6">
+        <f t="shared" si="2"/>
+        <v>3127.248612474526</v>
+      </c>
+      <c r="BC4" s="6">
+        <f t="shared" si="2"/>
+        <v>3189.7935847240165</v>
+      </c>
+      <c r="BD4" s="6">
+        <f t="shared" ref="BD4:BF4" si="3">BD3-BD5</f>
+        <v>3253.5894564184969</v>
+      </c>
+      <c r="BE4" s="6">
         <f t="shared" si="3"/>
-        <v>2874.5452328320002</v>
-      </c>
-      <c r="AZ4" s="6">
+        <v>3318.6612455468667</v>
+      </c>
+      <c r="BF4" s="6">
         <f t="shared" si="3"/>
-        <v>2932.0361374886406</v>
-      </c>
-      <c r="BA4" s="6">
-        <f t="shared" si="3"/>
-        <v>2990.6768602384132</v>
-      </c>
-      <c r="BB4" s="6">
-        <f t="shared" si="3"/>
-        <v>3050.4903974431813</v>
-      </c>
-      <c r="BC4" s="6">
-        <f t="shared" si="3"/>
-        <v>3111.5002053920452</v>
-      </c>
-      <c r="BD4" s="6">
-        <f t="shared" ref="BD4:BF4" si="4">BD3-BD5</f>
-        <v>3173.7302094998863</v>
-      </c>
-      <c r="BE4" s="6">
-        <f t="shared" si="4"/>
-        <v>3237.2048136898838</v>
-      </c>
-      <c r="BF4" s="6">
-        <f t="shared" si="4"/>
-        <v>3301.9489099636817</v>
+        <v>3385.0344704578042</v>
       </c>
     </row>
     <row r="5" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1593,220 +1591,220 @@
         <v>47</v>
       </c>
       <c r="C5" s="9">
-        <f t="shared" ref="C5:R5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:R5" si="4">C3-C4</f>
         <v>195.09999999999997</v>
       </c>
       <c r="D5" s="9">
+        <f t="shared" si="4"/>
+        <v>229.8</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="4"/>
+        <v>278.39999999999998</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="4"/>
+        <v>214.79999999999995</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" si="4"/>
+        <v>226.3</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" si="4"/>
+        <v>259</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="4"/>
+        <v>328.69999999999993</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" si="4"/>
+        <v>236.29999999999995</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="4"/>
+        <v>242.20000000000005</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" si="4"/>
+        <v>275.40000000000003</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="4"/>
+        <v>338.40000000000009</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="4"/>
+        <v>281.10000000000002</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" si="4"/>
+        <v>309.29999999999995</v>
+      </c>
+      <c r="P5" s="9">
+        <f t="shared" si="4"/>
+        <v>572.6</v>
+      </c>
+      <c r="Q5" s="9">
+        <f t="shared" si="4"/>
+        <v>752.4</v>
+      </c>
+      <c r="R5" s="9">
+        <f t="shared" si="4"/>
+        <v>714.80000000000007</v>
+      </c>
+      <c r="S5" s="9">
+        <f t="shared" ref="S5:AK5" si="5">S3-S4</f>
+        <v>572.99999999999989</v>
+      </c>
+      <c r="T5" s="9">
         <f t="shared" si="5"/>
-        <v>229.8</v>
-      </c>
-      <c r="E5" s="9">
+        <v>546</v>
+      </c>
+      <c r="U5" s="9">
         <f t="shared" si="5"/>
-        <v>278.39999999999998</v>
-      </c>
-      <c r="F5" s="9">
+        <v>661.19999999999993</v>
+      </c>
+      <c r="V5" s="9">
         <f t="shared" si="5"/>
-        <v>214.79999999999995</v>
-      </c>
-      <c r="G5" s="9">
+        <v>496.9</v>
+      </c>
+      <c r="W5" s="9">
         <f t="shared" si="5"/>
-        <v>226.3</v>
-      </c>
-      <c r="H5" s="9">
+        <v>462.70000000000005</v>
+      </c>
+      <c r="X5" s="9">
         <f t="shared" si="5"/>
-        <v>259</v>
-      </c>
-      <c r="I5" s="9">
+        <v>442</v>
+      </c>
+      <c r="Y5" s="9">
         <f t="shared" si="5"/>
-        <v>328.69999999999993</v>
-      </c>
-      <c r="J5" s="9">
+        <v>480.40000000000009</v>
+      </c>
+      <c r="Z5" s="9">
         <f t="shared" si="5"/>
-        <v>236.29999999999995</v>
-      </c>
-      <c r="K5" s="9">
+        <v>347.4</v>
+      </c>
+      <c r="AA5" s="9">
         <f t="shared" si="5"/>
-        <v>242.20000000000005</v>
-      </c>
-      <c r="L5" s="9">
+        <v>378.79999999999995</v>
+      </c>
+      <c r="AB5" s="9">
         <f t="shared" si="5"/>
-        <v>275.40000000000003</v>
-      </c>
-      <c r="M5" s="9">
+        <v>441.6</v>
+      </c>
+      <c r="AC5" s="9">
         <f t="shared" si="5"/>
-        <v>338.40000000000009</v>
-      </c>
-      <c r="N5" s="9">
+        <v>529</v>
+      </c>
+      <c r="AD5" s="9">
         <f t="shared" si="5"/>
-        <v>281.10000000000002</v>
-      </c>
-      <c r="O5" s="9">
+        <v>439.4</v>
+      </c>
+      <c r="AE5" s="9">
         <f t="shared" si="5"/>
-        <v>309.29999999999995</v>
-      </c>
-      <c r="P5" s="9">
+        <v>468.70000000000005</v>
+      </c>
+      <c r="AF5" s="9">
         <f t="shared" si="5"/>
-        <v>572.6</v>
-      </c>
-      <c r="Q5" s="9">
+        <v>488.5</v>
+      </c>
+      <c r="AG5" s="9">
         <f t="shared" si="5"/>
-        <v>752.4</v>
-      </c>
-      <c r="R5" s="9">
+        <v>576.9</v>
+      </c>
+      <c r="AH5" s="9">
         <f t="shared" si="5"/>
-        <v>714.80000000000007</v>
-      </c>
-      <c r="S5" s="9">
-        <f t="shared" ref="S5:AJ5" si="6">S3-S4</f>
-        <v>572.99999999999989</v>
-      </c>
-      <c r="T5" s="9">
-        <f t="shared" si="6"/>
-        <v>546</v>
-      </c>
-      <c r="U5" s="9">
-        <f t="shared" si="6"/>
-        <v>661.19999999999993</v>
-      </c>
-      <c r="V5" s="9">
-        <f t="shared" si="6"/>
-        <v>496.9</v>
-      </c>
-      <c r="W5" s="9">
-        <f t="shared" si="6"/>
-        <v>462.70000000000005</v>
-      </c>
-      <c r="X5" s="9">
-        <f t="shared" si="6"/>
-        <v>442</v>
-      </c>
-      <c r="Y5" s="9">
-        <f t="shared" si="6"/>
-        <v>480.40000000000009</v>
-      </c>
-      <c r="Z5" s="9">
-        <f t="shared" si="6"/>
-        <v>347.4</v>
-      </c>
-      <c r="AA5" s="9">
-        <f t="shared" si="6"/>
-        <v>378.79999999999995</v>
-      </c>
-      <c r="AB5" s="9">
-        <f t="shared" si="6"/>
-        <v>441.6</v>
-      </c>
-      <c r="AC5" s="9">
-        <f t="shared" si="6"/>
-        <v>529</v>
-      </c>
-      <c r="AD5" s="9">
-        <f t="shared" si="6"/>
-        <v>439.4</v>
-      </c>
-      <c r="AE5" s="9">
-        <f t="shared" si="6"/>
-        <v>468.70000000000005</v>
-      </c>
-      <c r="AF5" s="9">
-        <f t="shared" si="6"/>
-        <v>488.5</v>
-      </c>
-      <c r="AG5" s="9">
-        <f t="shared" si="6"/>
-        <v>576.9</v>
-      </c>
-      <c r="AH5" s="9">
-        <f t="shared" si="6"/>
         <v>438.1</v>
       </c>
       <c r="AI5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>481.1</v>
       </c>
       <c r="AJ5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>516.69999999999993</v>
       </c>
       <c r="AK5" s="9">
-        <f>AK3*0.44</f>
-        <v>619.21860000000004</v>
+        <f t="shared" si="5"/>
+        <v>616.20000000000005</v>
       </c>
       <c r="AL5" s="9">
-        <f t="shared" ref="AL5" si="7">AL3*0.43</f>
-        <v>451.85088000000002</v>
+        <f t="shared" ref="AL5" si="6">AL3*0.43</f>
+        <v>460.54032000000007</v>
       </c>
       <c r="AO5" s="9">
-        <f t="shared" ref="AO5:AW5" si="8">AO3-AO4</f>
+        <f t="shared" ref="AO5:AW5" si="7">AO3-AO4</f>
         <v>918.10000000000036</v>
       </c>
       <c r="AP5" s="9">
+        <f t="shared" si="7"/>
+        <v>1050.3000000000002</v>
+      </c>
+      <c r="AQ5" s="9">
+        <f t="shared" si="7"/>
+        <v>1137.1000000000004</v>
+      </c>
+      <c r="AR5" s="9">
+        <f t="shared" si="7"/>
+        <v>2349.0999999999995</v>
+      </c>
+      <c r="AS5" s="9">
+        <f t="shared" si="7"/>
+        <v>2277.1</v>
+      </c>
+      <c r="AT5" s="9">
+        <f t="shared" si="7"/>
+        <v>1732.5000000000009</v>
+      </c>
+      <c r="AU5" s="9">
+        <f t="shared" si="7"/>
+        <v>1788.8000000000002</v>
+      </c>
+      <c r="AV5" s="9">
+        <f t="shared" si="7"/>
+        <v>1972.1999999999998</v>
+      </c>
+      <c r="AW5" s="9">
+        <f t="shared" si="7"/>
+        <v>2074.5403200000001</v>
+      </c>
+      <c r="AX5" s="9">
+        <f>AX3*0.43</f>
+        <v>2158.3320928000003</v>
+      </c>
+      <c r="AY5" s="9">
+        <f t="shared" ref="AY5:BF5" si="8">AY3*0.43</f>
+        <v>2223.0820555840005</v>
+      </c>
+      <c r="AZ5" s="9">
         <f t="shared" si="8"/>
-        <v>1050.3000000000002</v>
-      </c>
-      <c r="AQ5" s="9">
+        <v>2267.5436966956804</v>
+      </c>
+      <c r="BA5" s="9">
         <f t="shared" si="8"/>
-        <v>1137.1000000000004</v>
-      </c>
-      <c r="AR5" s="9">
+        <v>2312.8945706295945</v>
+      </c>
+      <c r="BB5" s="9">
         <f t="shared" si="8"/>
-        <v>2349.0999999999995</v>
-      </c>
-      <c r="AS5" s="9">
+        <v>2359.1524620421865</v>
+      </c>
+      <c r="BC5" s="9">
         <f t="shared" si="8"/>
-        <v>2277.1</v>
-      </c>
-      <c r="AT5" s="9">
+        <v>2406.33551128303</v>
+      </c>
+      <c r="BD5" s="9">
         <f t="shared" si="8"/>
-        <v>1732.5000000000009</v>
-      </c>
-      <c r="AU5" s="9">
+        <v>2454.4622215086906</v>
+      </c>
+      <c r="BE5" s="9">
         <f t="shared" si="8"/>
-        <v>1788.8000000000002</v>
-      </c>
-      <c r="AV5" s="9">
+        <v>2503.5514659388646</v>
+      </c>
+      <c r="BF5" s="9">
         <f t="shared" si="8"/>
-        <v>1972.1999999999998</v>
-      </c>
-      <c r="AW5" s="9">
-        <f t="shared" si="8"/>
-        <v>2068.8694800000003</v>
-      </c>
-      <c r="AX5" s="9">
-        <f>AX3*0.44</f>
-        <v>2192.7876256000004</v>
-      </c>
-      <c r="AY5" s="9">
-        <f t="shared" ref="AY5:BF5" si="9">AY3*0.44</f>
-        <v>2258.5712543680006</v>
-      </c>
-      <c r="AZ5" s="9">
-        <f t="shared" si="9"/>
-        <v>2303.7426794553603</v>
-      </c>
-      <c r="BA5" s="9">
-        <f t="shared" si="9"/>
-        <v>2349.8175330444678</v>
-      </c>
-      <c r="BB5" s="9">
-        <f t="shared" si="9"/>
-        <v>2396.8138837053571</v>
-      </c>
-      <c r="BC5" s="9">
-        <f t="shared" si="9"/>
-        <v>2444.7501613794639</v>
-      </c>
-      <c r="BD5" s="9">
-        <f t="shared" si="9"/>
-        <v>2493.6451646070532</v>
-      </c>
-      <c r="BE5" s="9">
-        <f t="shared" si="9"/>
-        <v>2543.5180678991946</v>
-      </c>
-      <c r="BF5" s="9">
-        <f t="shared" si="9"/>
-        <v>2594.3884292571788</v>
+        <v>2553.6224952576417</v>
       </c>
     </row>
     <row r="6" spans="2:58" x14ac:dyDescent="0.3">
@@ -1916,19 +1914,18 @@
         <v>199</v>
       </c>
       <c r="AK6" s="6">
-        <f>AK3*0.15</f>
-        <v>211.09725</v>
+        <v>206.9</v>
       </c>
       <c r="AL6" s="6">
         <f>AL3*0.19</f>
-        <v>199.65504000000001</v>
+        <v>203.49456000000004</v>
       </c>
       <c r="AO6" s="6">
-        <f t="shared" ref="AO6:AO11" si="10">SUM(C6:F6)</f>
+        <f t="shared" ref="AO6:AO11" si="9">SUM(C6:F6)</f>
         <v>435.6</v>
       </c>
       <c r="AP6" s="6">
-        <f t="shared" ref="AP6:AP11" si="11">SUM(G6:J6)</f>
+        <f t="shared" ref="AP6:AP11" si="10">SUM(G6:J6)</f>
         <v>488.29999999999995</v>
       </c>
       <c r="AQ6" s="6">
@@ -1936,7 +1933,7 @@
         <v>533.4</v>
       </c>
       <c r="AR6" s="6">
-        <f t="shared" ref="AR6:AR11" si="12">SUM(O6:R6)</f>
+        <f t="shared" ref="AR6:AR11" si="11">SUM(O6:R6)</f>
         <v>770.3</v>
       </c>
       <c r="AS6" s="6">
@@ -1944,56 +1941,56 @@
         <v>1025.8</v>
       </c>
       <c r="AT6" s="6">
-        <f t="shared" ref="AT6:AT11" si="13">SUM(W6:Z6)</f>
+        <f t="shared" ref="AT6:AT11" si="12">SUM(W6:Z6)</f>
         <v>809.30000000000007</v>
       </c>
       <c r="AU6" s="6">
-        <f t="shared" ref="AU6:AU11" si="14">SUM(AA6:AD6)</f>
+        <f t="shared" ref="AU6:AU11" si="13">SUM(AA6:AD6)</f>
         <v>730.4</v>
       </c>
       <c r="AV6" s="6">
-        <f t="shared" ref="AV6:AV11" si="15">SUM(AE6:AH6)</f>
+        <f t="shared" ref="AV6:AV11" si="14">SUM(AE6:AH6)</f>
         <v>814.4</v>
       </c>
       <c r="AW6" s="6">
-        <f t="shared" ref="AW6:AW11" si="16">SUM(AI6:AL6)</f>
-        <v>805.55228999999997</v>
+        <f t="shared" ref="AW6:AW11" si="15">SUM(AI6:AL6)</f>
+        <v>805.19456000000014</v>
       </c>
       <c r="AX6" s="6">
-        <f t="shared" ref="AX6:BC6" si="17">AX3*0.16</f>
-        <v>797.37731840000015</v>
+        <f t="shared" ref="AX6:BC6" si="16">AX3*0.16</f>
+        <v>803.10031360000005</v>
       </c>
       <c r="AY6" s="6">
+        <f t="shared" si="16"/>
+        <v>827.19332300800022</v>
+      </c>
+      <c r="AZ6" s="6">
+        <f t="shared" si="16"/>
+        <v>843.73718946816018</v>
+      </c>
+      <c r="BA6" s="6">
+        <f t="shared" si="16"/>
+        <v>860.61193325752356</v>
+      </c>
+      <c r="BB6" s="6">
+        <f t="shared" si="16"/>
+        <v>877.82417192267405</v>
+      </c>
+      <c r="BC6" s="6">
+        <f t="shared" si="16"/>
+        <v>895.38065536112742</v>
+      </c>
+      <c r="BD6" s="6">
+        <f t="shared" ref="BD6:BF6" si="17">BD3*0.16</f>
+        <v>913.28826846835</v>
+      </c>
+      <c r="BE6" s="6">
         <f t="shared" si="17"/>
-        <v>821.29863795200015</v>
-      </c>
-      <c r="AZ6" s="6">
+        <v>931.55403383771704</v>
+      </c>
+      <c r="BF6" s="6">
         <f t="shared" si="17"/>
-        <v>837.72461071104021</v>
-      </c>
-      <c r="BA6" s="6">
-        <f t="shared" si="17"/>
-        <v>854.47910292526103</v>
-      </c>
-      <c r="BB6" s="6">
-        <f t="shared" si="17"/>
-        <v>871.56868498376616</v>
-      </c>
-      <c r="BC6" s="6">
-        <f t="shared" si="17"/>
-        <v>889.00005868344147</v>
-      </c>
-      <c r="BD6" s="6">
-        <f t="shared" ref="BD6:BF6" si="18">BD3*0.16</f>
-        <v>906.78005985711036</v>
-      </c>
-      <c r="BE6" s="6">
-        <f t="shared" si="18"/>
-        <v>924.91566105425261</v>
-      </c>
-      <c r="BF6" s="6">
-        <f t="shared" si="18"/>
-        <v>943.41397427533775</v>
+        <v>950.18511451447137</v>
       </c>
     </row>
     <row r="7" spans="2:58" x14ac:dyDescent="0.3">
@@ -2103,19 +2100,18 @@
         <v>76.099999999999994</v>
       </c>
       <c r="AK7" s="6">
-        <f>AG7*1.04</f>
-        <v>81.12</v>
+        <v>78.5</v>
       </c>
       <c r="AL7" s="6">
-        <f t="shared" ref="AL7" si="19">AH7*1.05</f>
+        <f t="shared" ref="AL7" si="18">AH7*1.05</f>
         <v>83.475000000000009</v>
       </c>
       <c r="AO7" s="6">
+        <f t="shared" si="9"/>
+        <v>143.69999999999999</v>
+      </c>
+      <c r="AP7" s="6">
         <f t="shared" si="10"/>
-        <v>143.69999999999999</v>
-      </c>
-      <c r="AP7" s="6">
-        <f t="shared" si="11"/>
         <v>161.19999999999999</v>
       </c>
       <c r="AQ7" s="6">
@@ -2123,7 +2119,7 @@
         <v>177.6</v>
       </c>
       <c r="AR7" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>226</v>
       </c>
       <c r="AS7" s="6">
@@ -2131,56 +2127,56 @@
         <v>291.8</v>
       </c>
       <c r="AT7" s="6">
+        <f t="shared" si="12"/>
+        <v>280.7</v>
+      </c>
+      <c r="AU7" s="6">
         <f t="shared" si="13"/>
-        <v>280.7</v>
-      </c>
-      <c r="AU7" s="6">
+        <v>287.29999999999995</v>
+      </c>
+      <c r="AV7" s="6">
         <f t="shared" si="14"/>
-        <v>287.29999999999995</v>
-      </c>
-      <c r="AV7" s="6">
+        <v>309</v>
+      </c>
+      <c r="AW7" s="6">
         <f t="shared" si="15"/>
-        <v>309</v>
-      </c>
-      <c r="AW7" s="6">
-        <f t="shared" si="16"/>
-        <v>315.29500000000002</v>
+        <v>312.67500000000001</v>
       </c>
       <c r="AX7" s="6">
         <f>AW7*1.03</f>
-        <v>324.75385</v>
+        <v>322.05525</v>
       </c>
       <c r="AY7" s="6">
         <f>AX7*1.03</f>
-        <v>334.4964655</v>
+        <v>331.71690749999999</v>
       </c>
       <c r="AZ7" s="6">
         <f>AY7*1.02</f>
-        <v>341.18639481000002</v>
+        <v>338.35124565000001</v>
       </c>
       <c r="BA7" s="6">
-        <f t="shared" ref="BA7:BC7" si="20">AZ7*1.02</f>
-        <v>348.01012270620004</v>
+        <f t="shared" ref="BA7:BC7" si="19">AZ7*1.02</f>
+        <v>345.11827056300001</v>
       </c>
       <c r="BB7" s="6">
-        <f t="shared" si="20"/>
-        <v>354.97032516032402</v>
+        <f t="shared" si="19"/>
+        <v>352.02063597426002</v>
       </c>
       <c r="BC7" s="6">
-        <f t="shared" si="20"/>
-        <v>362.06973166353049</v>
+        <f t="shared" si="19"/>
+        <v>359.06104869374525</v>
       </c>
       <c r="BD7" s="6">
-        <f t="shared" ref="BD7:BD8" si="21">BC7*1.02</f>
-        <v>369.31112629680109</v>
+        <f t="shared" ref="BD7:BD8" si="20">BC7*1.02</f>
+        <v>366.24226966762018</v>
       </c>
       <c r="BE7" s="6">
-        <f t="shared" ref="BE7:BE8" si="22">BD7*1.02</f>
-        <v>376.69734882273713</v>
+        <f t="shared" ref="BE7:BE8" si="21">BD7*1.02</f>
+        <v>373.56711506097258</v>
       </c>
       <c r="BF7" s="6">
-        <f t="shared" ref="BF7:BF8" si="23">BE7*1.02</f>
-        <v>384.23129579919186</v>
+        <f t="shared" ref="BF7:BF8" si="22">BE7*1.02</f>
+        <v>381.03845736219205</v>
       </c>
     </row>
     <row r="8" spans="2:58" x14ac:dyDescent="0.3">
@@ -2290,19 +2286,18 @@
         <v>41.8</v>
       </c>
       <c r="AK8" s="6">
-        <f>AG8*1.02</f>
-        <v>42.942</v>
+        <v>41.9</v>
       </c>
       <c r="AL8" s="6">
-        <f>AH8*1.07</f>
-        <v>43.121000000000002</v>
+        <f>AH8*1.04</f>
+        <v>41.911999999999999</v>
       </c>
       <c r="AO8" s="6">
+        <f t="shared" si="9"/>
+        <v>96.4</v>
+      </c>
+      <c r="AP8" s="6">
         <f t="shared" si="10"/>
-        <v>96.4</v>
-      </c>
-      <c r="AP8" s="6">
-        <f t="shared" si="11"/>
         <v>98.800000000000011</v>
       </c>
       <c r="AQ8" s="6">
@@ -2310,7 +2305,7 @@
         <v>94</v>
       </c>
       <c r="AR8" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>166.60000000000002</v>
       </c>
       <c r="AS8" s="6">
@@ -2318,56 +2313,56 @@
         <v>148.69999999999999</v>
       </c>
       <c r="AT8" s="6">
+        <f t="shared" si="12"/>
+        <v>124.69999999999999</v>
+      </c>
+      <c r="AU8" s="6">
         <f t="shared" si="13"/>
-        <v>124.69999999999999</v>
-      </c>
-      <c r="AU8" s="6">
+        <v>155</v>
+      </c>
+      <c r="AV8" s="6">
         <f t="shared" si="14"/>
-        <v>155</v>
-      </c>
-      <c r="AV8" s="6">
+        <v>164.10000000000002</v>
+      </c>
+      <c r="AW8" s="6">
         <f t="shared" si="15"/>
-        <v>164.10000000000002</v>
-      </c>
-      <c r="AW8" s="6">
-        <f t="shared" si="16"/>
-        <v>169.66300000000001</v>
+        <v>167.41200000000001</v>
       </c>
       <c r="AX8" s="6">
         <f>AW8*1.04</f>
-        <v>176.44952000000001</v>
+        <v>174.10848000000001</v>
       </c>
       <c r="AY8" s="6">
         <f>AX8*1.03</f>
-        <v>181.7430056</v>
+        <v>179.33173440000002</v>
       </c>
       <c r="AZ8" s="6">
         <f>AY8*1.02</f>
-        <v>185.37786571200002</v>
+        <v>182.91836908800002</v>
       </c>
       <c r="BA8" s="6">
-        <f t="shared" ref="BA8:BC8" si="24">AZ8*1.02</f>
-        <v>189.08542302624002</v>
+        <f t="shared" ref="BA8:BC8" si="23">AZ8*1.02</f>
+        <v>186.57673646976002</v>
       </c>
       <c r="BB8" s="6">
-        <f t="shared" si="24"/>
-        <v>192.86713148676483</v>
+        <f t="shared" si="23"/>
+        <v>190.30827119915523</v>
       </c>
       <c r="BC8" s="6">
-        <f t="shared" si="24"/>
-        <v>196.72447411650015</v>
+        <f t="shared" si="23"/>
+        <v>194.11443662313835</v>
       </c>
       <c r="BD8" s="6">
+        <f t="shared" si="20"/>
+        <v>197.99672535560111</v>
+      </c>
+      <c r="BE8" s="6">
         <f t="shared" si="21"/>
-        <v>200.65896359883016</v>
-      </c>
-      <c r="BE8" s="6">
+        <v>201.95665986271314</v>
+      </c>
+      <c r="BF8" s="6">
         <f t="shared" si="22"/>
-        <v>204.67214287080677</v>
-      </c>
-      <c r="BF8" s="6">
-        <f t="shared" si="23"/>
-        <v>208.7655857282229</v>
+        <v>205.99579305996741</v>
       </c>
     </row>
     <row r="9" spans="2:58" x14ac:dyDescent="0.3">
@@ -2511,17 +2506,18 @@
         <v>4</v>
       </c>
       <c r="AK9" s="6">
-        <v>5</v>
+        <f>1.6+0.9</f>
+        <v>2.5</v>
       </c>
       <c r="AL9" s="6">
         <v>5</v>
       </c>
       <c r="AO9" s="6">
+        <f t="shared" si="9"/>
+        <v>17.899999999999999</v>
+      </c>
+      <c r="AP9" s="6">
         <f t="shared" si="10"/>
-        <v>17.899999999999999</v>
-      </c>
-      <c r="AP9" s="6">
-        <f t="shared" si="11"/>
         <v>27.599999999999998</v>
       </c>
       <c r="AQ9" s="6">
@@ -2529,7 +2525,7 @@
         <v>32.5</v>
       </c>
       <c r="AR9" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>32.200000000000003</v>
       </c>
       <c r="AS9" s="6">
@@ -2537,56 +2533,56 @@
         <v>38</v>
       </c>
       <c r="AT9" s="6">
+        <f t="shared" si="12"/>
+        <v>24.7</v>
+      </c>
+      <c r="AU9" s="6">
         <f t="shared" si="13"/>
-        <v>24.7</v>
-      </c>
-      <c r="AU9" s="6">
+        <v>25.5</v>
+      </c>
+      <c r="AV9" s="6">
         <f t="shared" si="14"/>
-        <v>25.5</v>
-      </c>
-      <c r="AV9" s="6">
+        <v>20.200000000000003</v>
+      </c>
+      <c r="AW9" s="6">
         <f t="shared" si="15"/>
-        <v>20.200000000000003</v>
-      </c>
-      <c r="AW9" s="6">
-        <f t="shared" si="16"/>
-        <v>18.7</v>
+        <v>16.2</v>
       </c>
       <c r="AX9" s="6">
-        <f t="shared" ref="AX9:BC9" si="25">AW9*1.01</f>
-        <v>18.887</v>
+        <f t="shared" ref="AX9:BC9" si="24">AW9*1.01</f>
+        <v>16.361999999999998</v>
       </c>
       <c r="AY9" s="6">
-        <f t="shared" si="25"/>
-        <v>19.075870000000002</v>
+        <f t="shared" si="24"/>
+        <v>16.52562</v>
       </c>
       <c r="AZ9" s="6">
-        <f t="shared" si="25"/>
-        <v>19.266628700000002</v>
+        <f t="shared" si="24"/>
+        <v>16.690876200000002</v>
       </c>
       <c r="BA9" s="6">
-        <f t="shared" si="25"/>
-        <v>19.459294987000003</v>
+        <f t="shared" si="24"/>
+        <v>16.857784962</v>
       </c>
       <c r="BB9" s="6">
-        <f t="shared" si="25"/>
-        <v>19.653887936870003</v>
+        <f t="shared" si="24"/>
+        <v>17.02636281162</v>
       </c>
       <c r="BC9" s="6">
-        <f t="shared" si="25"/>
-        <v>19.850426816238702</v>
+        <f t="shared" si="24"/>
+        <v>17.1966264397362</v>
       </c>
       <c r="BD9" s="6">
-        <f t="shared" ref="BD9" si="26">BC9*1.01</f>
-        <v>20.04893108440109</v>
+        <f t="shared" ref="BD9" si="25">BC9*1.01</f>
+        <v>17.368592704133562</v>
       </c>
       <c r="BE9" s="6">
-        <f t="shared" ref="BE9" si="27">BD9*1.01</f>
-        <v>20.2494203952451</v>
+        <f t="shared" ref="BE9" si="26">BD9*1.01</f>
+        <v>17.542278631174899</v>
       </c>
       <c r="BF9" s="6">
-        <f t="shared" ref="BF9" si="28">BE9*1.01</f>
-        <v>20.451914599197551</v>
+        <f t="shared" ref="BF9" si="27">BE9*1.01</f>
+        <v>17.717701417486648</v>
       </c>
     </row>
     <row r="10" spans="2:58" x14ac:dyDescent="0.3">
@@ -2684,11 +2680,11 @@
         <v>0</v>
       </c>
       <c r="AO10" s="6">
+        <f t="shared" si="9"/>
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="AP10" s="6">
         <f t="shared" si="10"/>
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="AP10" s="6">
-        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AQ10" s="6">
@@ -2696,7 +2692,7 @@
         <v>23.2</v>
       </c>
       <c r="AR10" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>5.7</v>
       </c>
       <c r="AS10" s="6">
@@ -2704,19 +2700,19 @@
         <v>-3.5</v>
       </c>
       <c r="AT10" s="6">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AU10" s="6">
         <f t="shared" si="13"/>
+        <v>-0.3</v>
+      </c>
+      <c r="AV10" s="6">
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AU10" s="6">
-        <f t="shared" si="14"/>
-        <v>-0.3</v>
-      </c>
-      <c r="AV10" s="6">
+      <c r="AW10" s="6">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AW10" s="6">
-        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AX10" s="6">
@@ -2850,17 +2846,17 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AK11" s="6">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL11" s="6">
         <v>0</v>
       </c>
       <c r="AO11" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="6">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AP11" s="6">
-        <f t="shared" si="11"/>
         <v>11.2</v>
       </c>
       <c r="AQ11" s="6">
@@ -2868,7 +2864,7 @@
         <v>1.8</v>
       </c>
       <c r="AR11" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>-0.1</v>
       </c>
       <c r="AS11" s="6">
@@ -2876,20 +2872,20 @@
         <v>0</v>
       </c>
       <c r="AT11" s="6">
+        <f t="shared" si="12"/>
+        <v>34.6</v>
+      </c>
+      <c r="AU11" s="6">
         <f t="shared" si="13"/>
-        <v>34.6</v>
-      </c>
-      <c r="AU11" s="6">
+        <v>3.8</v>
+      </c>
+      <c r="AV11" s="6">
         <f t="shared" si="14"/>
-        <v>3.8</v>
-      </c>
-      <c r="AV11" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="AW11" s="6">
         <f t="shared" si="15"/>
-        <v>9.6</v>
-      </c>
-      <c r="AW11" s="6">
-        <f t="shared" si="16"/>
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="AX11" s="6">
         <v>0</v>
@@ -2924,148 +2920,148 @@
         <v>38</v>
       </c>
       <c r="C12" s="6">
-        <f t="shared" ref="C12:S12" si="29">SUM(C6:C11)</f>
+        <f t="shared" ref="C12:S12" si="28">SUM(C6:C11)</f>
         <v>163.9</v>
       </c>
       <c r="D12" s="6">
+        <f t="shared" si="28"/>
+        <v>170.8</v>
+      </c>
+      <c r="E12" s="6">
+        <f t="shared" si="28"/>
+        <v>178.20000000000002</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="28"/>
+        <v>175.79999999999998</v>
+      </c>
+      <c r="G12" s="6">
+        <f t="shared" si="28"/>
+        <v>193.9</v>
+      </c>
+      <c r="H12" s="6">
+        <f t="shared" si="28"/>
+        <v>193.9</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="28"/>
+        <v>205.29999999999998</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="28"/>
+        <v>193.99999999999997</v>
+      </c>
+      <c r="K12" s="6">
+        <f t="shared" si="28"/>
+        <v>194.79999999999998</v>
+      </c>
+      <c r="L12" s="6">
+        <f t="shared" si="28"/>
+        <v>207.29999999999998</v>
+      </c>
+      <c r="M12" s="6">
+        <f t="shared" si="28"/>
+        <v>209.60000000000002</v>
+      </c>
+      <c r="N12" s="6">
+        <f t="shared" si="28"/>
+        <v>249.09999999999997</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="28"/>
+        <v>225.69999999999996</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="28"/>
+        <v>251</v>
+      </c>
+      <c r="Q12" s="6">
+        <f t="shared" si="28"/>
+        <v>304.3</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="28"/>
+        <v>419.7</v>
+      </c>
+      <c r="S12" s="6">
+        <f t="shared" si="28"/>
+        <v>369.8</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" ref="T12:U12" si="29">SUM(T6:T11)</f>
+        <v>366.6</v>
+      </c>
+      <c r="U12" s="6">
         <f t="shared" si="29"/>
-        <v>170.8</v>
-      </c>
-      <c r="E12" s="6">
-        <f t="shared" si="29"/>
-        <v>178.20000000000002</v>
-      </c>
-      <c r="F12" s="6">
-        <f t="shared" si="29"/>
-        <v>175.79999999999998</v>
-      </c>
-      <c r="G12" s="6">
-        <f t="shared" si="29"/>
-        <v>193.9</v>
-      </c>
-      <c r="H12" s="6">
-        <f t="shared" si="29"/>
-        <v>193.9</v>
-      </c>
-      <c r="I12" s="6">
-        <f t="shared" si="29"/>
-        <v>205.29999999999998</v>
-      </c>
-      <c r="J12" s="6">
-        <f t="shared" si="29"/>
-        <v>193.99999999999997</v>
-      </c>
-      <c r="K12" s="6">
-        <f t="shared" si="29"/>
-        <v>194.79999999999998</v>
-      </c>
-      <c r="L12" s="6">
-        <f t="shared" si="29"/>
-        <v>207.29999999999998</v>
-      </c>
-      <c r="M12" s="6">
-        <f t="shared" si="29"/>
-        <v>209.60000000000002</v>
-      </c>
-      <c r="N12" s="6">
-        <f t="shared" si="29"/>
-        <v>249.09999999999997</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" si="29"/>
-        <v>225.69999999999996</v>
-      </c>
-      <c r="P12" s="6">
-        <f t="shared" si="29"/>
-        <v>251</v>
-      </c>
-      <c r="Q12" s="6">
-        <f t="shared" si="29"/>
-        <v>304.3</v>
-      </c>
-      <c r="R12" s="6">
-        <f t="shared" si="29"/>
-        <v>419.7</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="29"/>
-        <v>369.8</v>
-      </c>
-      <c r="T12" s="6">
-        <f t="shared" ref="T12:U12" si="30">SUM(T6:T11)</f>
-        <v>366.6</v>
-      </c>
-      <c r="U12" s="6">
+        <v>398.4</v>
+      </c>
+      <c r="V12" s="6">
+        <f t="shared" ref="V12:W12" si="30">SUM(V6:V11)</f>
+        <v>368.19999999999993</v>
+      </c>
+      <c r="W12" s="6">
         <f t="shared" si="30"/>
-        <v>398.4</v>
-      </c>
-      <c r="V12" s="6">
-        <f t="shared" ref="V12:W12" si="31">SUM(V6:V11)</f>
-        <v>368.19999999999993</v>
-      </c>
-      <c r="W12" s="6">
+        <v>347.19999999999993</v>
+      </c>
+      <c r="X12" s="6">
+        <f t="shared" ref="X12:Y12" si="31">SUM(X6:X11)</f>
+        <v>314.50000000000006</v>
+      </c>
+      <c r="Y12" s="6">
         <f t="shared" si="31"/>
-        <v>347.19999999999993</v>
-      </c>
-      <c r="X12" s="6">
-        <f t="shared" ref="X12:Y12" si="32">SUM(X6:X11)</f>
-        <v>314.50000000000006</v>
-      </c>
-      <c r="Y12" s="6">
-        <f t="shared" si="32"/>
         <v>303.79999999999995</v>
       </c>
       <c r="Z12" s="6">
-        <f t="shared" ref="Z12" si="33">SUM(Z6:Z11)</f>
+        <f t="shared" ref="Z12" si="32">SUM(Z6:Z11)</f>
         <v>308.5</v>
       </c>
       <c r="AA12" s="6">
-        <f t="shared" ref="AA12" si="34">SUM(AA6:AA11)</f>
+        <f t="shared" ref="AA12" si="33">SUM(AA6:AA11)</f>
         <v>300.39999999999998</v>
       </c>
       <c r="AB12" s="6">
-        <f t="shared" ref="AB12:AC12" si="35">SUM(AB6:AB11)</f>
+        <f t="shared" ref="AB12:AC12" si="34">SUM(AB6:AB11)</f>
         <v>285</v>
       </c>
       <c r="AC12" s="6">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>307.09999999999997</v>
       </c>
       <c r="AD12" s="6">
-        <f t="shared" ref="AD12" si="36">SUM(AD6:AD11)</f>
+        <f t="shared" ref="AD12" si="35">SUM(AD6:AD11)</f>
         <v>309.2</v>
       </c>
       <c r="AE12" s="6">
-        <f t="shared" ref="AE12" si="37">SUM(AE6:AE11)</f>
+        <f t="shared" ref="AE12" si="36">SUM(AE6:AE11)</f>
         <v>315.2</v>
       </c>
       <c r="AF12" s="6">
-        <f t="shared" ref="AF12:AH12" si="38">SUM(AF6:AF11)</f>
+        <f t="shared" ref="AF12:AH12" si="37">SUM(AF6:AF11)</f>
         <v>327.7</v>
       </c>
       <c r="AG12" s="6">
+        <f t="shared" si="37"/>
+        <v>342.30000000000007</v>
+      </c>
+      <c r="AH12" s="6">
+        <f t="shared" si="37"/>
+        <v>332.1</v>
+      </c>
+      <c r="AI12" s="6">
+        <f t="shared" ref="AI12:AL12" si="38">SUM(AI6:AI11)</f>
+        <v>318.89999999999998</v>
+      </c>
+      <c r="AJ12" s="6">
         <f t="shared" si="38"/>
-        <v>342.30000000000007</v>
-      </c>
-      <c r="AH12" s="6">
+        <v>325.3</v>
+      </c>
+      <c r="AK12" s="6">
         <f t="shared" si="38"/>
-        <v>332.1</v>
-      </c>
-      <c r="AI12" s="6">
-        <f t="shared" ref="AI12:AL12" si="39">SUM(AI6:AI11)</f>
-        <v>318.89999999999998</v>
-      </c>
-      <c r="AJ12" s="6">
-        <f t="shared" si="39"/>
-        <v>325.3</v>
-      </c>
-      <c r="AK12" s="6">
-        <f t="shared" si="39"/>
-        <v>340.15925000000004</v>
+        <v>330.29999999999995</v>
       </c>
       <c r="AL12" s="6">
-        <f t="shared" si="39"/>
-        <v>331.25103999999999</v>
+        <f t="shared" si="38"/>
+        <v>333.88156000000004</v>
       </c>
       <c r="AO12" s="6">
         <f>SUM(AO6:AO11)</f>
@@ -3088,56 +3084,56 @@
         <v>1500.8</v>
       </c>
       <c r="AT12" s="6">
-        <f t="shared" ref="AT12:BC12" si="40">SUM(AT6:AT11)</f>
+        <f t="shared" ref="AT12:BC12" si="39">SUM(AT6:AT11)</f>
         <v>1274</v>
       </c>
       <c r="AU12" s="6">
+        <f t="shared" si="39"/>
+        <v>1201.6999999999998</v>
+      </c>
+      <c r="AV12" s="6">
+        <f t="shared" si="39"/>
+        <v>1317.3</v>
+      </c>
+      <c r="AW12" s="6">
+        <f t="shared" si="39"/>
+        <v>1308.3815600000003</v>
+      </c>
+      <c r="AX12" s="6">
+        <f t="shared" si="39"/>
+        <v>1315.6260436000002</v>
+      </c>
+      <c r="AY12" s="6">
+        <f t="shared" si="39"/>
+        <v>1354.7675849080001</v>
+      </c>
+      <c r="AZ12" s="6">
+        <f t="shared" si="39"/>
+        <v>1381.6976804061603</v>
+      </c>
+      <c r="BA12" s="6">
+        <f t="shared" si="39"/>
+        <v>1409.1647252522835</v>
+      </c>
+      <c r="BB12" s="6">
+        <f t="shared" si="39"/>
+        <v>1437.1794419077091</v>
+      </c>
+      <c r="BC12" s="6">
+        <f t="shared" si="39"/>
+        <v>1465.7527671177472</v>
+      </c>
+      <c r="BD12" s="6">
+        <f t="shared" ref="BD12:BF12" si="40">SUM(BD6:BD11)</f>
+        <v>1494.8958561957047</v>
+      </c>
+      <c r="BE12" s="6">
         <f t="shared" si="40"/>
-        <v>1201.6999999999998</v>
-      </c>
-      <c r="AV12" s="6">
+        <v>1524.6200873925777</v>
+      </c>
+      <c r="BF12" s="6">
         <f t="shared" si="40"/>
-        <v>1317.3</v>
-      </c>
-      <c r="AW12" s="6">
-        <f t="shared" si="40"/>
-        <v>1315.6102900000001</v>
-      </c>
-      <c r="AX12" s="6">
-        <f t="shared" si="40"/>
-        <v>1317.4676884000003</v>
-      </c>
-      <c r="AY12" s="6">
-        <f t="shared" si="40"/>
-        <v>1356.6139790520001</v>
-      </c>
-      <c r="AZ12" s="6">
-        <f t="shared" si="40"/>
-        <v>1383.5554999330404</v>
-      </c>
-      <c r="BA12" s="6">
-        <f t="shared" si="40"/>
-        <v>1411.0339436447011</v>
-      </c>
-      <c r="BB12" s="6">
-        <f t="shared" si="40"/>
-        <v>1439.060029567725</v>
-      </c>
-      <c r="BC12" s="6">
-        <f t="shared" si="40"/>
-        <v>1467.644691279711</v>
-      </c>
-      <c r="BD12" s="6">
-        <f t="shared" ref="BD12:BF12" si="41">SUM(BD6:BD11)</f>
-        <v>1496.7990808371426</v>
-      </c>
-      <c r="BE12" s="6">
-        <f t="shared" si="41"/>
-        <v>1526.5345731430416</v>
-      </c>
-      <c r="BF12" s="6">
-        <f t="shared" si="41"/>
-        <v>1556.8627704019502</v>
+        <v>1554.9370663541174</v>
       </c>
     </row>
     <row r="13" spans="2:58" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3145,148 +3141,148 @@
         <v>39</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:S13" si="42">C5-C12</f>
+        <f t="shared" ref="C13:S13" si="41">C5-C12</f>
         <v>31.19999999999996</v>
       </c>
       <c r="D13" s="9">
+        <f t="shared" si="41"/>
+        <v>59</v>
+      </c>
+      <c r="E13" s="9">
+        <f t="shared" si="41"/>
+        <v>100.19999999999996</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="41"/>
+        <v>38.999999999999972</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="41"/>
+        <v>32.400000000000006</v>
+      </c>
+      <c r="H13" s="9">
+        <f t="shared" si="41"/>
+        <v>65.099999999999994</v>
+      </c>
+      <c r="I13" s="9">
+        <f t="shared" si="41"/>
+        <v>123.39999999999995</v>
+      </c>
+      <c r="J13" s="9">
+        <f t="shared" si="41"/>
+        <v>42.299999999999983</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="41"/>
+        <v>47.400000000000063</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="41"/>
+        <v>68.100000000000051</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="41"/>
+        <v>128.80000000000007</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="41"/>
+        <v>32.000000000000057</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="41"/>
+        <v>83.6</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" si="41"/>
+        <v>321.60000000000002</v>
+      </c>
+      <c r="Q13" s="9">
+        <f t="shared" si="41"/>
+        <v>448.09999999999997</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="41"/>
+        <v>295.10000000000008</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="41"/>
+        <v>203.19999999999987</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" ref="T13:U13" si="42">T5-T12</f>
+        <v>179.39999999999998</v>
+      </c>
+      <c r="U13" s="9">
         <f t="shared" si="42"/>
-        <v>59</v>
-      </c>
-      <c r="E13" s="9">
-        <f t="shared" si="42"/>
-        <v>100.19999999999996</v>
-      </c>
-      <c r="F13" s="9">
-        <f t="shared" si="42"/>
-        <v>38.999999999999972</v>
-      </c>
-      <c r="G13" s="9">
-        <f t="shared" si="42"/>
-        <v>32.400000000000006</v>
-      </c>
-      <c r="H13" s="9">
-        <f t="shared" si="42"/>
-        <v>65.099999999999994</v>
-      </c>
-      <c r="I13" s="9">
-        <f t="shared" si="42"/>
-        <v>123.39999999999995</v>
-      </c>
-      <c r="J13" s="9">
-        <f t="shared" si="42"/>
-        <v>42.299999999999983</v>
-      </c>
-      <c r="K13" s="9">
-        <f t="shared" si="42"/>
-        <v>47.400000000000063</v>
-      </c>
-      <c r="L13" s="9">
-        <f t="shared" si="42"/>
-        <v>68.100000000000051</v>
-      </c>
-      <c r="M13" s="9">
-        <f t="shared" si="42"/>
-        <v>128.80000000000007</v>
-      </c>
-      <c r="N13" s="9">
-        <f t="shared" si="42"/>
-        <v>32.000000000000057</v>
-      </c>
-      <c r="O13" s="9">
-        <f t="shared" si="42"/>
-        <v>83.6</v>
-      </c>
-      <c r="P13" s="9">
-        <f t="shared" si="42"/>
-        <v>321.60000000000002</v>
-      </c>
-      <c r="Q13" s="9">
-        <f t="shared" si="42"/>
-        <v>448.09999999999997</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="42"/>
-        <v>295.10000000000008</v>
-      </c>
-      <c r="S13" s="9">
-        <f t="shared" si="42"/>
-        <v>203.19999999999987</v>
-      </c>
-      <c r="T13" s="9">
-        <f t="shared" ref="T13:U13" si="43">T5-T12</f>
-        <v>179.39999999999998</v>
-      </c>
-      <c r="U13" s="9">
+        <v>262.79999999999995</v>
+      </c>
+      <c r="V13" s="9">
+        <f t="shared" ref="V13:W13" si="43">V5-V12</f>
+        <v>128.70000000000005</v>
+      </c>
+      <c r="W13" s="9">
         <f t="shared" si="43"/>
-        <v>262.79999999999995</v>
-      </c>
-      <c r="V13" s="9">
-        <f t="shared" ref="V13:W13" si="44">V5-V12</f>
-        <v>128.70000000000005</v>
-      </c>
-      <c r="W13" s="9">
+        <v>115.50000000000011</v>
+      </c>
+      <c r="X13" s="9">
+        <f t="shared" ref="X13:Y13" si="44">X5-X12</f>
+        <v>127.49999999999994</v>
+      </c>
+      <c r="Y13" s="9">
         <f t="shared" si="44"/>
-        <v>115.50000000000011</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" ref="X13:Y13" si="45">X5-X12</f>
-        <v>127.49999999999994</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" si="45"/>
         <v>176.60000000000014</v>
       </c>
       <c r="Z13" s="9">
-        <f t="shared" ref="Z13" si="46">Z5-Z12</f>
+        <f t="shared" ref="Z13" si="45">Z5-Z12</f>
         <v>38.899999999999977</v>
       </c>
       <c r="AA13" s="9">
-        <f t="shared" ref="AA13" si="47">AA5-AA12</f>
+        <f t="shared" ref="AA13" si="46">AA5-AA12</f>
         <v>78.399999999999977</v>
       </c>
       <c r="AB13" s="9">
-        <f t="shared" ref="AB13:AC13" si="48">AB5-AB12</f>
+        <f t="shared" ref="AB13:AC13" si="47">AB5-AB12</f>
         <v>156.60000000000002</v>
       </c>
       <c r="AC13" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>221.90000000000003</v>
       </c>
       <c r="AD13" s="9">
-        <f t="shared" ref="AD13" si="49">AD5-AD12</f>
+        <f t="shared" ref="AD13" si="48">AD5-AD12</f>
         <v>130.19999999999999</v>
       </c>
       <c r="AE13" s="9">
-        <f t="shared" ref="AE13" si="50">AE5-AE12</f>
+        <f t="shared" ref="AE13" si="49">AE5-AE12</f>
         <v>153.50000000000006</v>
       </c>
       <c r="AF13" s="9">
-        <f t="shared" ref="AF13:AH13" si="51">AF5-AF12</f>
+        <f t="shared" ref="AF13:AH13" si="50">AF5-AF12</f>
         <v>160.80000000000001</v>
       </c>
       <c r="AG13" s="9">
+        <f t="shared" si="50"/>
+        <v>234.59999999999991</v>
+      </c>
+      <c r="AH13" s="9">
+        <f t="shared" si="50"/>
+        <v>106</v>
+      </c>
+      <c r="AI13" s="9">
+        <f t="shared" ref="AI13:AL13" si="51">AI5-AI12</f>
+        <v>162.20000000000005</v>
+      </c>
+      <c r="AJ13" s="9">
         <f t="shared" si="51"/>
-        <v>234.59999999999991</v>
-      </c>
-      <c r="AH13" s="9">
+        <v>191.39999999999992</v>
+      </c>
+      <c r="AK13" s="9">
         <f t="shared" si="51"/>
-        <v>106</v>
-      </c>
-      <c r="AI13" s="9">
-        <f t="shared" ref="AI13:AL13" si="52">AI5-AI12</f>
-        <v>162.20000000000005</v>
-      </c>
-      <c r="AJ13" s="9">
-        <f t="shared" si="52"/>
-        <v>191.39999999999992</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" si="52"/>
-        <v>279.05934999999999</v>
+        <v>285.90000000000009</v>
       </c>
       <c r="AL13" s="9">
-        <f t="shared" si="52"/>
-        <v>120.59984000000003</v>
+        <f t="shared" si="51"/>
+        <v>126.65876000000003</v>
       </c>
       <c r="AO13" s="9">
         <f>AO5-AO12</f>
@@ -3309,56 +3305,56 @@
         <v>776.3</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13:BC13" si="53">AT5-AT12</f>
+        <f t="shared" ref="AT13:BC13" si="52">AT5-AT12</f>
         <v>458.50000000000091</v>
       </c>
       <c r="AU13" s="9">
+        <f t="shared" si="52"/>
+        <v>587.10000000000036</v>
+      </c>
+      <c r="AV13" s="9">
+        <f t="shared" si="52"/>
+        <v>654.89999999999986</v>
+      </c>
+      <c r="AW13" s="9">
+        <f t="shared" si="52"/>
+        <v>766.1587599999998</v>
+      </c>
+      <c r="AX13" s="9">
+        <f t="shared" si="52"/>
+        <v>842.70604920000005</v>
+      </c>
+      <c r="AY13" s="9">
+        <f t="shared" si="52"/>
+        <v>868.31447067600038</v>
+      </c>
+      <c r="AZ13" s="9">
+        <f t="shared" si="52"/>
+        <v>885.84601628952009</v>
+      </c>
+      <c r="BA13" s="9">
+        <f t="shared" si="52"/>
+        <v>903.72984537731099</v>
+      </c>
+      <c r="BB13" s="9">
+        <f t="shared" si="52"/>
+        <v>921.97302013447734</v>
+      </c>
+      <c r="BC13" s="9">
+        <f t="shared" si="52"/>
+        <v>940.58274416528275</v>
+      </c>
+      <c r="BD13" s="9">
+        <f t="shared" ref="BD13:BF13" si="53">BD5-BD12</f>
+        <v>959.56636531298591</v>
+      </c>
+      <c r="BE13" s="9">
         <f t="shared" si="53"/>
-        <v>587.10000000000036</v>
-      </c>
-      <c r="AV13" s="9">
+        <v>978.93137854628685</v>
+      </c>
+      <c r="BF13" s="9">
         <f t="shared" si="53"/>
-        <v>654.89999999999986</v>
-      </c>
-      <c r="AW13" s="9">
-        <f t="shared" si="53"/>
-        <v>753.25919000000022</v>
-      </c>
-      <c r="AX13" s="9">
-        <f t="shared" si="53"/>
-        <v>875.31993720000014</v>
-      </c>
-      <c r="AY13" s="9">
-        <f t="shared" si="53"/>
-        <v>901.9572753160005</v>
-      </c>
-      <c r="AZ13" s="9">
-        <f t="shared" si="53"/>
-        <v>920.18717952231987</v>
-      </c>
-      <c r="BA13" s="9">
-        <f t="shared" si="53"/>
-        <v>938.7835893997667</v>
-      </c>
-      <c r="BB13" s="9">
-        <f t="shared" si="53"/>
-        <v>957.75385413763206</v>
-      </c>
-      <c r="BC13" s="9">
-        <f t="shared" si="53"/>
-        <v>977.10547009975289</v>
-      </c>
-      <c r="BD13" s="9">
-        <f t="shared" ref="BD13:BF13" si="54">BD5-BD12</f>
-        <v>996.84608376991059</v>
-      </c>
-      <c r="BE13" s="9">
-        <f t="shared" si="54"/>
-        <v>1016.983494756153</v>
-      </c>
-      <c r="BF13" s="9">
-        <f t="shared" si="54"/>
-        <v>1037.5256588552286</v>
+        <v>998.68542890352433</v>
       </c>
     </row>
     <row r="14" spans="2:58" x14ac:dyDescent="0.3">
@@ -3468,12 +3464,11 @@
         <v>-11.8</v>
       </c>
       <c r="AK14" s="6">
-        <f t="shared" ref="AK14:AL14" si="55">AJ14*1.03</f>
-        <v>-12.154000000000002</v>
+        <v>-11</v>
       </c>
       <c r="AL14" s="6">
-        <f t="shared" si="55"/>
-        <v>-12.518620000000002</v>
+        <f t="shared" ref="AL14" si="54">AK14*1.03</f>
+        <v>-11.33</v>
       </c>
       <c r="AO14" s="6">
         <f>SUM(C14:F14)</f>
@@ -3508,44 +3503,44 @@
         <v>-54.999999999999993</v>
       </c>
       <c r="AW14" s="6">
-        <f t="shared" ref="AW14:AW15" si="56">SUM(AI14:AL14)</f>
-        <v>-47.672620000000009</v>
+        <f t="shared" ref="AW14:AW15" si="55">SUM(AI14:AL14)</f>
+        <v>-45.33</v>
       </c>
       <c r="AX14" s="6">
-        <f t="shared" ref="AX14:BF14" si="57">AW14*1.02</f>
-        <v>-48.626072400000012</v>
+        <f t="shared" ref="AX14:BF14" si="56">AW14*1.02</f>
+        <v>-46.236599999999996</v>
       </c>
       <c r="AY14" s="6">
-        <f t="shared" si="57"/>
-        <v>-49.598593848000014</v>
+        <f t="shared" si="56"/>
+        <v>-47.161331999999994</v>
       </c>
       <c r="AZ14" s="6">
-        <f t="shared" si="57"/>
-        <v>-50.590565724960015</v>
+        <f t="shared" si="56"/>
+        <v>-48.104558639999993</v>
       </c>
       <c r="BA14" s="6">
-        <f t="shared" si="57"/>
-        <v>-51.602377039459213</v>
+        <f t="shared" si="56"/>
+        <v>-49.066649812799994</v>
       </c>
       <c r="BB14" s="6">
-        <f t="shared" si="57"/>
-        <v>-52.6344245802484</v>
+        <f t="shared" si="56"/>
+        <v>-50.047982809055995</v>
       </c>
       <c r="BC14" s="6">
-        <f t="shared" si="57"/>
-        <v>-53.687113071853368</v>
+        <f t="shared" si="56"/>
+        <v>-51.048942465237118</v>
       </c>
       <c r="BD14" s="6">
-        <f t="shared" si="57"/>
-        <v>-54.760855333290436</v>
+        <f t="shared" si="56"/>
+        <v>-52.069921314541858</v>
       </c>
       <c r="BE14" s="6">
-        <f t="shared" si="57"/>
-        <v>-55.856072439956243</v>
+        <f t="shared" si="56"/>
+        <v>-53.111319740832698</v>
       </c>
       <c r="BF14" s="6">
-        <f t="shared" si="57"/>
-        <v>-56.973193888755368</v>
+        <f t="shared" si="56"/>
+        <v>-54.173546135649353</v>
       </c>
     </row>
     <row r="15" spans="2:58" x14ac:dyDescent="0.3">
@@ -3655,7 +3650,7 @@
         <v>0.1</v>
       </c>
       <c r="AK15" s="6">
-        <v>2</v>
+        <v>-2.1</v>
       </c>
       <c r="AL15" s="6">
         <v>2</v>
@@ -3693,8 +3688,8 @@
         <v>3</v>
       </c>
       <c r="AW15" s="6">
-        <f t="shared" si="56"/>
-        <v>2.9000000000000004</v>
+        <f t="shared" si="55"/>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="AX15" s="6">
         <v>0</v>
@@ -3729,220 +3724,220 @@
         <v>42</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C16:S16" si="58">C13-C14-C15</f>
+        <f t="shared" ref="C16:S16" si="57">C13-C14-C15</f>
         <v>31.399999999999963</v>
       </c>
       <c r="D16" s="9">
+        <f t="shared" si="57"/>
+        <v>60.5</v>
+      </c>
+      <c r="E16" s="9">
+        <f t="shared" si="57"/>
+        <v>100.79999999999997</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="57"/>
+        <v>39.39999999999997</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="57"/>
+        <v>33.200000000000003</v>
+      </c>
+      <c r="H16" s="9">
+        <f t="shared" si="57"/>
+        <v>70.400000000000006</v>
+      </c>
+      <c r="I16" s="9">
+        <f t="shared" si="57"/>
+        <v>122.19999999999995</v>
+      </c>
+      <c r="J16" s="9">
+        <f t="shared" si="57"/>
+        <v>45.499999999999986</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="57"/>
+        <v>51.900000000000063</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="57"/>
+        <v>70.400000000000063</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="57"/>
+        <v>132.00000000000006</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="57"/>
+        <v>70.000000000000057</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="57"/>
+        <v>86.199999999999989</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="57"/>
+        <v>323.20000000000005</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" si="57"/>
+        <v>454.9</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" si="57"/>
+        <v>283.90000000000009</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" si="57"/>
+        <v>211.89999999999989</v>
+      </c>
+      <c r="T16" s="9">
+        <f t="shared" ref="T16:U16" si="58">T13-T14-T15</f>
+        <v>172.89999999999998</v>
+      </c>
+      <c r="U16" s="9">
         <f t="shared" si="58"/>
-        <v>60.5</v>
-      </c>
-      <c r="E16" s="9">
-        <f t="shared" si="58"/>
-        <v>100.79999999999997</v>
-      </c>
-      <c r="F16" s="9">
-        <f t="shared" si="58"/>
-        <v>39.39999999999997</v>
-      </c>
-      <c r="G16" s="9">
-        <f t="shared" si="58"/>
-        <v>33.200000000000003</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="58"/>
-        <v>70.400000000000006</v>
-      </c>
-      <c r="I16" s="9">
-        <f t="shared" si="58"/>
-        <v>122.19999999999995</v>
-      </c>
-      <c r="J16" s="9">
-        <f t="shared" si="58"/>
-        <v>45.499999999999986</v>
-      </c>
-      <c r="K16" s="9">
-        <f t="shared" si="58"/>
-        <v>51.900000000000063</v>
-      </c>
-      <c r="L16" s="9">
-        <f t="shared" si="58"/>
-        <v>70.400000000000063</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="58"/>
-        <v>132.00000000000006</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="58"/>
-        <v>70.000000000000057</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="58"/>
-        <v>86.199999999999989</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="58"/>
-        <v>323.20000000000005</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="58"/>
-        <v>454.9</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="58"/>
-        <v>283.90000000000009</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="58"/>
-        <v>211.89999999999989</v>
-      </c>
-      <c r="T16" s="9">
-        <f t="shared" ref="T16:U16" si="59">T13-T14-T15</f>
-        <v>172.89999999999998</v>
-      </c>
-      <c r="U16" s="9">
+        <v>259.39999999999998</v>
+      </c>
+      <c r="V16" s="9">
+        <f t="shared" ref="V16:W16" si="59">V13-V14-V15</f>
+        <v>131.70000000000005</v>
+      </c>
+      <c r="W16" s="9">
         <f t="shared" si="59"/>
-        <v>259.39999999999998</v>
-      </c>
-      <c r="V16" s="9">
-        <f t="shared" ref="V16:W16" si="60">V13-V14-V15</f>
-        <v>131.70000000000005</v>
-      </c>
-      <c r="W16" s="9">
+        <v>122.50000000000011</v>
+      </c>
+      <c r="X16" s="9">
+        <f t="shared" ref="X16:Y16" si="60">X13-X14-X15</f>
+        <v>105.59999999999994</v>
+      </c>
+      <c r="Y16" s="9">
         <f t="shared" si="60"/>
-        <v>122.50000000000011</v>
-      </c>
-      <c r="X16" s="9">
-        <f t="shared" ref="X16:Y16" si="61">X13-X14-X15</f>
-        <v>105.59999999999994</v>
-      </c>
-      <c r="Y16" s="9">
-        <f t="shared" si="61"/>
         <v>182.70000000000013</v>
       </c>
       <c r="Z16" s="9">
-        <f t="shared" ref="Z16" si="62">Z13-Z14-Z15</f>
+        <f t="shared" ref="Z16" si="61">Z13-Z14-Z15</f>
         <v>52.799999999999976</v>
       </c>
       <c r="AA16" s="9">
-        <f t="shared" ref="AA16" si="63">AA13-AA14-AA15</f>
+        <f t="shared" ref="AA16" si="62">AA13-AA14-AA15</f>
         <v>75.199999999999974</v>
       </c>
       <c r="AB16" s="9">
-        <f t="shared" ref="AB16:AC16" si="64">AB13-AB14-AB15</f>
+        <f t="shared" ref="AB16:AC16" si="63">AB13-AB14-AB15</f>
         <v>167.50000000000003</v>
       </c>
       <c r="AC16" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>234.90000000000003</v>
       </c>
       <c r="AD16" s="9">
-        <f t="shared" ref="AD16" si="65">AD13-AD14-AD15</f>
+        <f t="shared" ref="AD16" si="64">AD13-AD14-AD15</f>
         <v>143.79999999999998</v>
       </c>
       <c r="AE16" s="9">
-        <f t="shared" ref="AE16" si="66">AE13-AE14-AE15</f>
+        <f t="shared" ref="AE16" si="65">AE13-AE14-AE15</f>
         <v>167.40000000000006</v>
       </c>
       <c r="AF16" s="9">
-        <f t="shared" ref="AF16:AH16" si="67">AF13-AF14-AF15</f>
+        <f t="shared" ref="AF16:AH16" si="66">AF13-AF14-AF15</f>
         <v>175.9</v>
       </c>
       <c r="AG16" s="9">
+        <f t="shared" si="66"/>
+        <v>245.2999999999999</v>
+      </c>
+      <c r="AH16" s="9">
+        <f t="shared" si="66"/>
+        <v>118.30000000000001</v>
+      </c>
+      <c r="AI16" s="9">
+        <f t="shared" ref="AI16:AL16" si="67">AI13-AI14-AI15</f>
+        <v>174.60000000000002</v>
+      </c>
+      <c r="AJ16" s="9">
         <f t="shared" si="67"/>
-        <v>245.2999999999999</v>
-      </c>
-      <c r="AH16" s="9">
+        <v>203.09999999999994</v>
+      </c>
+      <c r="AK16" s="9">
         <f t="shared" si="67"/>
-        <v>118.30000000000001</v>
-      </c>
-      <c r="AI16" s="9">
-        <f t="shared" ref="AI16:AL16" si="68">AI13-AI14-AI15</f>
-        <v>174.60000000000002</v>
-      </c>
-      <c r="AJ16" s="9">
+        <v>299.00000000000011</v>
+      </c>
+      <c r="AL16" s="9">
+        <f t="shared" si="67"/>
+        <v>135.98876000000004</v>
+      </c>
+      <c r="AO16" s="9">
+        <f t="shared" ref="AO16:AT16" si="68">AO13-AO14-AO15</f>
+        <v>232.10000000000042</v>
+      </c>
+      <c r="AP16" s="9">
         <f t="shared" si="68"/>
-        <v>203.09999999999994</v>
-      </c>
-      <c r="AK16" s="9">
+        <v>271.30000000000018</v>
+      </c>
+      <c r="AQ16" s="9">
         <f t="shared" si="68"/>
-        <v>289.21334999999999</v>
-      </c>
-      <c r="AL16" s="9">
+        <v>322.60000000000036</v>
+      </c>
+      <c r="AR16" s="9">
         <f t="shared" si="68"/>
-        <v>131.11846000000003</v>
-      </c>
-      <c r="AO16" s="9">
-        <f t="shared" ref="AO16:AT16" si="69">AO13-AO14-AO15</f>
-        <v>232.10000000000042</v>
-      </c>
-      <c r="AP16" s="9">
+        <v>1148.1999999999991</v>
+      </c>
+      <c r="AS16" s="9">
+        <f t="shared" si="68"/>
+        <v>778.09999999999991</v>
+      </c>
+      <c r="AT16" s="9">
+        <f t="shared" si="68"/>
+        <v>463.60000000000088</v>
+      </c>
+      <c r="AU16" s="9">
+        <f t="shared" ref="AU16:BC16" si="69">AU13-AU14-AU15</f>
+        <v>621.40000000000043</v>
+      </c>
+      <c r="AV16" s="9">
         <f t="shared" si="69"/>
-        <v>271.30000000000018</v>
-      </c>
-      <c r="AQ16" s="9">
+        <v>706.89999999999986</v>
+      </c>
+      <c r="AW16" s="9">
         <f t="shared" si="69"/>
-        <v>322.60000000000036</v>
-      </c>
-      <c r="AR16" s="9">
+        <v>812.68875999999989</v>
+      </c>
+      <c r="AX16" s="9">
         <f t="shared" si="69"/>
-        <v>1148.1999999999991</v>
-      </c>
-      <c r="AS16" s="9">
+        <v>888.94264920000001</v>
+      </c>
+      <c r="AY16" s="9">
         <f t="shared" si="69"/>
-        <v>778.09999999999991</v>
-      </c>
-      <c r="AT16" s="9">
+        <v>915.4758026760004</v>
+      </c>
+      <c r="AZ16" s="9">
         <f t="shared" si="69"/>
-        <v>463.60000000000088</v>
-      </c>
-      <c r="AU16" s="9">
-        <f t="shared" ref="AU16:BC16" si="70">AU13-AU14-AU15</f>
-        <v>621.40000000000043</v>
-      </c>
-      <c r="AV16" s="9">
+        <v>933.95057492952014</v>
+      </c>
+      <c r="BA16" s="9">
+        <f t="shared" si="69"/>
+        <v>952.79649519011105</v>
+      </c>
+      <c r="BB16" s="9">
+        <f t="shared" si="69"/>
+        <v>972.02100294353329</v>
+      </c>
+      <c r="BC16" s="9">
+        <f t="shared" si="69"/>
+        <v>991.63168663051988</v>
+      </c>
+      <c r="BD16" s="9">
+        <f t="shared" ref="BD16:BF16" si="70">BD13-BD14-BD15</f>
+        <v>1011.6362866275277</v>
+      </c>
+      <c r="BE16" s="9">
         <f t="shared" si="70"/>
-        <v>706.89999999999986</v>
-      </c>
-      <c r="AW16" s="9">
+        <v>1032.0426982871195</v>
+      </c>
+      <c r="BF16" s="9">
         <f t="shared" si="70"/>
-        <v>798.03181000000029</v>
-      </c>
-      <c r="AX16" s="9">
-        <f t="shared" si="70"/>
-        <v>923.94600960000014</v>
-      </c>
-      <c r="AY16" s="9">
-        <f t="shared" si="70"/>
-        <v>951.55586916400057</v>
-      </c>
-      <c r="AZ16" s="9">
-        <f t="shared" si="70"/>
-        <v>970.77774524727988</v>
-      </c>
-      <c r="BA16" s="9">
-        <f t="shared" si="70"/>
-        <v>990.38596643922597</v>
-      </c>
-      <c r="BB16" s="9">
-        <f t="shared" si="70"/>
-        <v>1010.3882787178804</v>
-      </c>
-      <c r="BC16" s="9">
-        <f t="shared" si="70"/>
-        <v>1030.7925831716063</v>
-      </c>
-      <c r="BD16" s="9">
-        <f t="shared" ref="BD16:BF16" si="71">BD13-BD14-BD15</f>
-        <v>1051.6069391032011</v>
-      </c>
-      <c r="BE16" s="9">
-        <f t="shared" si="71"/>
-        <v>1072.8395671961093</v>
-      </c>
-      <c r="BF16" s="9">
-        <f t="shared" si="71"/>
-        <v>1094.4988527439839</v>
+        <v>1052.8589750391736</v>
       </c>
     </row>
     <row r="17" spans="2:168" x14ac:dyDescent="0.3">
@@ -4052,12 +4047,11 @@
         <v>32.4</v>
       </c>
       <c r="AK17" s="6">
-        <f t="shared" ref="AK17:AL17" si="72">AK16*0.17</f>
-        <v>49.166269499999999</v>
+        <v>48.1</v>
       </c>
       <c r="AL17" s="6">
-        <f t="shared" si="72"/>
-        <v>22.290138200000005</v>
+        <f t="shared" ref="AL17" si="71">AL16*0.17</f>
+        <v>23.118089200000007</v>
       </c>
       <c r="AO17" s="6">
         <f>SUM(C17:F17)</f>
@@ -4093,43 +4087,43 @@
       </c>
       <c r="AW17" s="6">
         <f>SUM(AI17:AL17)</f>
-        <v>132.35640770000001</v>
+        <v>132.11808920000001</v>
       </c>
       <c r="AX17" s="6">
         <f>AX16*0.17</f>
-        <v>157.07082163200005</v>
+        <v>151.12025036400001</v>
       </c>
       <c r="AY17" s="6">
-        <f t="shared" ref="AY17:BF17" si="73">AY16*0.17</f>
-        <v>161.76449775788012</v>
+        <f t="shared" ref="AY17:BF17" si="72">AY16*0.17</f>
+        <v>155.63088645492007</v>
       </c>
       <c r="AZ17" s="6">
-        <f t="shared" si="73"/>
-        <v>165.03221669203759</v>
+        <f t="shared" si="72"/>
+        <v>158.77159773801844</v>
       </c>
       <c r="BA17" s="6">
-        <f t="shared" si="73"/>
-        <v>168.36561429466843</v>
+        <f t="shared" si="72"/>
+        <v>161.9754041823189</v>
       </c>
       <c r="BB17" s="6">
-        <f t="shared" si="73"/>
-        <v>171.76600738203967</v>
+        <f t="shared" si="72"/>
+        <v>165.24357050040066</v>
       </c>
       <c r="BC17" s="6">
-        <f t="shared" si="73"/>
-        <v>175.23473913917309</v>
+        <f t="shared" si="72"/>
+        <v>168.57738672718838</v>
       </c>
       <c r="BD17" s="6">
-        <f t="shared" si="73"/>
-        <v>178.7731796475442</v>
+        <f t="shared" si="72"/>
+        <v>171.97816872667974</v>
       </c>
       <c r="BE17" s="6">
-        <f t="shared" si="73"/>
-        <v>182.3827264233386</v>
+        <f t="shared" si="72"/>
+        <v>175.44725870881032</v>
       </c>
       <c r="BF17" s="6">
-        <f t="shared" si="73"/>
-        <v>186.06480496647728</v>
+        <f t="shared" si="72"/>
+        <v>178.98602575665953</v>
       </c>
     </row>
     <row r="18" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4137,660 +4131,660 @@
         <v>44</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" ref="C18:S18" si="74">C16-C17</f>
+        <f t="shared" ref="C18:S18" si="73">C16-C17</f>
         <v>36.799999999999962</v>
       </c>
       <c r="D18" s="9">
+        <f t="shared" si="73"/>
+        <v>56.4</v>
+      </c>
+      <c r="E18" s="9">
+        <f t="shared" si="73"/>
+        <v>80.799999999999969</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="73"/>
+        <v>34.39999999999997</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="73"/>
+        <v>38.400000000000006</v>
+      </c>
+      <c r="H18" s="9">
+        <f t="shared" si="73"/>
+        <v>64.2</v>
+      </c>
+      <c r="I18" s="9">
+        <f t="shared" si="73"/>
+        <v>112.89999999999995</v>
+      </c>
+      <c r="J18" s="9">
+        <f t="shared" si="73"/>
+        <v>42.199999999999989</v>
+      </c>
+      <c r="K18" s="9">
+        <f t="shared" si="73"/>
+        <v>45.400000000000063</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="73"/>
+        <v>73.000000000000057</v>
+      </c>
+      <c r="M18" s="9">
+        <f t="shared" si="73"/>
+        <v>117.50000000000006</v>
+      </c>
+      <c r="N18" s="9">
+        <f t="shared" si="73"/>
+        <v>213.80000000000007</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="73"/>
+        <v>72.199999999999989</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="73"/>
+        <v>266.90000000000003</v>
+      </c>
+      <c r="Q18" s="9">
+        <f t="shared" si="73"/>
+        <v>382.59999999999997</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="73"/>
+        <v>225.7000000000001</v>
+      </c>
+      <c r="S18" s="9">
+        <f t="shared" si="73"/>
+        <v>186.89999999999989</v>
+      </c>
+      <c r="T18" s="9">
+        <f t="shared" ref="T18:U18" si="74">T16-T17</f>
+        <v>139.39999999999998</v>
+      </c>
+      <c r="U18" s="9">
         <f t="shared" si="74"/>
-        <v>56.4</v>
-      </c>
-      <c r="E18" s="9">
-        <f t="shared" si="74"/>
-        <v>80.799999999999969</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" si="74"/>
-        <v>34.39999999999997</v>
-      </c>
-      <c r="G18" s="9">
-        <f t="shared" si="74"/>
-        <v>38.400000000000006</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="74"/>
-        <v>64.2</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="74"/>
-        <v>112.89999999999995</v>
-      </c>
-      <c r="J18" s="9">
-        <f t="shared" si="74"/>
-        <v>42.199999999999989</v>
-      </c>
-      <c r="K18" s="9">
-        <f t="shared" si="74"/>
-        <v>45.400000000000063</v>
-      </c>
-      <c r="L18" s="9">
-        <f t="shared" si="74"/>
-        <v>73.000000000000057</v>
-      </c>
-      <c r="M18" s="9">
-        <f t="shared" si="74"/>
-        <v>117.50000000000006</v>
-      </c>
-      <c r="N18" s="9">
-        <f t="shared" si="74"/>
-        <v>213.80000000000007</v>
-      </c>
-      <c r="O18" s="9">
-        <f t="shared" si="74"/>
-        <v>72.199999999999989</v>
-      </c>
-      <c r="P18" s="9">
-        <f t="shared" si="74"/>
-        <v>266.90000000000003</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="74"/>
-        <v>382.59999999999997</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="74"/>
-        <v>225.7000000000001</v>
-      </c>
-      <c r="S18" s="9">
-        <f t="shared" si="74"/>
-        <v>186.89999999999989</v>
-      </c>
-      <c r="T18" s="9">
-        <f t="shared" ref="T18:U18" si="75">T16-T17</f>
-        <v>139.39999999999998</v>
-      </c>
-      <c r="U18" s="9">
+        <v>210.09999999999997</v>
+      </c>
+      <c r="V18" s="9">
+        <f t="shared" ref="V18:W18" si="75">V16-V17</f>
+        <v>108.20000000000005</v>
+      </c>
+      <c r="W18" s="9">
         <f t="shared" si="75"/>
-        <v>210.09999999999997</v>
-      </c>
-      <c r="V18" s="9">
-        <f t="shared" ref="V18:W18" si="76">V16-V17</f>
-        <v>108.20000000000005</v>
-      </c>
-      <c r="W18" s="9">
+        <v>100.80000000000011</v>
+      </c>
+      <c r="X18" s="9">
+        <f t="shared" ref="X18:Y18" si="76">X16-X17</f>
+        <v>82.199999999999932</v>
+      </c>
+      <c r="Y18" s="9">
         <f t="shared" si="76"/>
-        <v>100.80000000000011</v>
-      </c>
-      <c r="X18" s="9">
-        <f t="shared" ref="X18:Y18" si="77">X16-X17</f>
-        <v>82.199999999999932</v>
-      </c>
-      <c r="Y18" s="9">
-        <f t="shared" si="77"/>
         <v>140.00000000000011</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="78">Z16-Z17</f>
+        <f t="shared" ref="Z18" si="77">Z16-Z17</f>
         <v>41.59999999999998</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18" si="79">AA16-AA17</f>
+        <f t="shared" ref="AA18" si="78">AA16-AA17</f>
         <v>62.699999999999974</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" ref="AB18:AC18" si="80">AB16-AB17</f>
+        <f t="shared" ref="AB18:AC18" si="79">AB16-AB17</f>
         <v>137.20000000000002</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>244.50000000000003</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="81">AD16-AD17</f>
+        <f t="shared" ref="AD18" si="80">AD16-AD17</f>
         <v>167.6</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" ref="AE18" si="82">AE16-AE17</f>
+        <f t="shared" ref="AE18" si="81">AE16-AE17</f>
         <v>141.80000000000007</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18:AH18" si="83">AF16-AF17</f>
+        <f t="shared" ref="AF18:AH18" si="82">AF16-AF17</f>
         <v>145.30000000000001</v>
       </c>
       <c r="AG18" s="9">
+        <f t="shared" si="82"/>
+        <v>200.1999999999999</v>
+      </c>
+      <c r="AH18" s="9">
+        <f t="shared" si="82"/>
+        <v>144.20000000000002</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" ref="AI18:AL18" si="83">AI16-AI17</f>
+        <v>146.10000000000002</v>
+      </c>
+      <c r="AJ18" s="9">
         <f t="shared" si="83"/>
-        <v>200.1999999999999</v>
-      </c>
-      <c r="AH18" s="9">
+        <v>170.69999999999993</v>
+      </c>
+      <c r="AK18" s="9">
         <f t="shared" si="83"/>
-        <v>144.20000000000002</v>
-      </c>
-      <c r="AI18" s="9">
-        <f t="shared" ref="AI18:AL18" si="84">AI16-AI17</f>
-        <v>146.10000000000002</v>
-      </c>
-      <c r="AJ18" s="9">
+        <v>250.90000000000012</v>
+      </c>
+      <c r="AL18" s="9">
+        <f t="shared" si="83"/>
+        <v>112.87067080000003</v>
+      </c>
+      <c r="AO18" s="9">
+        <f t="shared" ref="AO18:AT18" si="84">AO16-AO17</f>
+        <v>208.40000000000043</v>
+      </c>
+      <c r="AP18" s="9">
         <f t="shared" si="84"/>
-        <v>170.69999999999993</v>
-      </c>
-      <c r="AK18" s="9">
+        <v>257.70000000000016</v>
+      </c>
+      <c r="AQ18" s="9">
         <f t="shared" si="84"/>
-        <v>240.04708049999999</v>
-      </c>
-      <c r="AL18" s="9">
+        <v>448.00000000000034</v>
+      </c>
+      <c r="AR18" s="9">
         <f t="shared" si="84"/>
-        <v>108.82832180000003</v>
-      </c>
-      <c r="AO18" s="9">
-        <f t="shared" ref="AO18:AT18" si="85">AO16-AO17</f>
-        <v>208.40000000000043</v>
-      </c>
-      <c r="AP18" s="9">
+        <v>947.39999999999918</v>
+      </c>
+      <c r="AS18" s="9">
+        <f t="shared" si="84"/>
+        <v>646.79999999999995</v>
+      </c>
+      <c r="AT18" s="9">
+        <f t="shared" si="84"/>
+        <v>364.60000000000088</v>
+      </c>
+      <c r="AU18" s="9">
+        <f t="shared" ref="AU18:BC18" si="85">AU16-AU17</f>
+        <v>612.00000000000045</v>
+      </c>
+      <c r="AV18" s="9">
         <f t="shared" si="85"/>
-        <v>257.70000000000016</v>
-      </c>
-      <c r="AQ18" s="9">
+        <v>631.49999999999989</v>
+      </c>
+      <c r="AW18" s="9">
         <f t="shared" si="85"/>
-        <v>448.00000000000034</v>
-      </c>
-      <c r="AR18" s="9">
+        <v>680.5706707999999</v>
+      </c>
+      <c r="AX18" s="9">
         <f t="shared" si="85"/>
-        <v>947.39999999999918</v>
-      </c>
-      <c r="AS18" s="9">
+        <v>737.82239883600005</v>
+      </c>
+      <c r="AY18" s="9">
         <f t="shared" si="85"/>
-        <v>646.79999999999995</v>
-      </c>
-      <c r="AT18" s="9">
+        <v>759.84491622108033</v>
+      </c>
+      <c r="AZ18" s="9">
         <f t="shared" si="85"/>
-        <v>364.60000000000088</v>
-      </c>
-      <c r="AU18" s="9">
-        <f t="shared" ref="AU18:BC18" si="86">AU16-AU17</f>
-        <v>612.00000000000045</v>
-      </c>
-      <c r="AV18" s="9">
+        <v>775.17897719150164</v>
+      </c>
+      <c r="BA18" s="9">
+        <f t="shared" si="85"/>
+        <v>790.82109100779212</v>
+      </c>
+      <c r="BB18" s="9">
+        <f t="shared" si="85"/>
+        <v>806.77743244313262</v>
+      </c>
+      <c r="BC18" s="9">
+        <f t="shared" si="85"/>
+        <v>823.05429990333153</v>
+      </c>
+      <c r="BD18" s="9">
+        <f t="shared" ref="BD18:BF18" si="86">BD16-BD17</f>
+        <v>839.65811790084797</v>
+      </c>
+      <c r="BE18" s="9">
         <f t="shared" si="86"/>
-        <v>631.49999999999989</v>
-      </c>
-      <c r="AW18" s="9">
+        <v>856.5954395783092</v>
+      </c>
+      <c r="BF18" s="9">
         <f t="shared" si="86"/>
-        <v>665.67540230000031</v>
-      </c>
-      <c r="AX18" s="9">
-        <f t="shared" si="86"/>
-        <v>766.87518796800009</v>
-      </c>
-      <c r="AY18" s="9">
-        <f t="shared" si="86"/>
-        <v>789.79137140612045</v>
-      </c>
-      <c r="AZ18" s="9">
-        <f t="shared" si="86"/>
-        <v>805.74552855524234</v>
-      </c>
-      <c r="BA18" s="9">
-        <f t="shared" si="86"/>
-        <v>822.02035214455759</v>
-      </c>
-      <c r="BB18" s="9">
-        <f t="shared" si="86"/>
-        <v>838.62227133584076</v>
-      </c>
-      <c r="BC18" s="9">
-        <f t="shared" si="86"/>
-        <v>855.5578440324332</v>
-      </c>
-      <c r="BD18" s="9">
-        <f t="shared" ref="BD18:BF18" si="87">BD16-BD17</f>
-        <v>872.83375945565683</v>
-      </c>
-      <c r="BE18" s="9">
-        <f t="shared" si="87"/>
-        <v>890.45684077277076</v>
-      </c>
-      <c r="BF18" s="9">
-        <f t="shared" si="87"/>
-        <v>908.43404777750663</v>
+        <v>873.87294928251413</v>
       </c>
       <c r="BG18" s="1">
         <f>BF18*(1+$BI$24)</f>
-        <v>899.34970729973156</v>
+        <v>865.13421978968893</v>
       </c>
       <c r="BH18" s="1">
-        <f t="shared" ref="BH18:DS18" si="88">BG18*(1+$BI$24)</f>
-        <v>890.35621022673422</v>
+        <f t="shared" ref="BH18:DS18" si="87">BG18*(1+$BI$24)</f>
+        <v>856.48287759179198</v>
       </c>
       <c r="BI18" s="1">
+        <f t="shared" si="87"/>
+        <v>847.91804881587404</v>
+      </c>
+      <c r="BJ18" s="1">
+        <f t="shared" si="87"/>
+        <v>839.43886832771534</v>
+      </c>
+      <c r="BK18" s="1">
+        <f t="shared" si="87"/>
+        <v>831.04447964443818</v>
+      </c>
+      <c r="BL18" s="1">
+        <f t="shared" si="87"/>
+        <v>822.73403484799383</v>
+      </c>
+      <c r="BM18" s="1">
+        <f t="shared" si="87"/>
+        <v>814.50669449951386</v>
+      </c>
+      <c r="BN18" s="1">
+        <f t="shared" si="87"/>
+        <v>806.36162755451869</v>
+      </c>
+      <c r="BO18" s="1">
+        <f t="shared" si="87"/>
+        <v>798.29801127897349</v>
+      </c>
+      <c r="BP18" s="1">
+        <f t="shared" si="87"/>
+        <v>790.31503116618376</v>
+      </c>
+      <c r="BQ18" s="1">
+        <f t="shared" si="87"/>
+        <v>782.41188085452188</v>
+      </c>
+      <c r="BR18" s="1">
+        <f t="shared" si="87"/>
+        <v>774.58776204597666</v>
+      </c>
+      <c r="BS18" s="1">
+        <f t="shared" si="87"/>
+        <v>766.84188442551692</v>
+      </c>
+      <c r="BT18" s="1">
+        <f t="shared" si="87"/>
+        <v>759.17346558126178</v>
+      </c>
+      <c r="BU18" s="1">
+        <f t="shared" si="87"/>
+        <v>751.58173092544916</v>
+      </c>
+      <c r="BV18" s="1">
+        <f t="shared" si="87"/>
+        <v>744.06591361619462</v>
+      </c>
+      <c r="BW18" s="1">
+        <f t="shared" si="87"/>
+        <v>736.62525448003271</v>
+      </c>
+      <c r="BX18" s="1">
+        <f t="shared" si="87"/>
+        <v>729.25900193523239</v>
+      </c>
+      <c r="BY18" s="1">
+        <f t="shared" si="87"/>
+        <v>721.96641191588003</v>
+      </c>
+      <c r="BZ18" s="1">
+        <f t="shared" si="87"/>
+        <v>714.74674779672125</v>
+      </c>
+      <c r="CA18" s="1">
+        <f t="shared" si="87"/>
+        <v>707.59928031875404</v>
+      </c>
+      <c r="CB18" s="1">
+        <f t="shared" si="87"/>
+        <v>700.52328751556649</v>
+      </c>
+      <c r="CC18" s="1">
+        <f t="shared" si="87"/>
+        <v>693.51805464041081</v>
+      </c>
+      <c r="CD18" s="1">
+        <f t="shared" si="87"/>
+        <v>686.58287409400668</v>
+      </c>
+      <c r="CE18" s="1">
+        <f t="shared" si="87"/>
+        <v>679.71704535306662</v>
+      </c>
+      <c r="CF18" s="1">
+        <f t="shared" si="87"/>
+        <v>672.9198748995359</v>
+      </c>
+      <c r="CG18" s="1">
+        <f t="shared" si="87"/>
+        <v>666.19067615054053</v>
+      </c>
+      <c r="CH18" s="1">
+        <f t="shared" si="87"/>
+        <v>659.52876938903512</v>
+      </c>
+      <c r="CI18" s="1">
+        <f t="shared" si="87"/>
+        <v>652.93348169514479</v>
+      </c>
+      <c r="CJ18" s="1">
+        <f t="shared" si="87"/>
+        <v>646.40414687819339</v>
+      </c>
+      <c r="CK18" s="1">
+        <f t="shared" si="87"/>
+        <v>639.94010540941144</v>
+      </c>
+      <c r="CL18" s="1">
+        <f t="shared" si="87"/>
+        <v>633.5407043553173</v>
+      </c>
+      <c r="CM18" s="1">
+        <f t="shared" si="87"/>
+        <v>627.20529731176407</v>
+      </c>
+      <c r="CN18" s="1">
+        <f t="shared" si="87"/>
+        <v>620.93324433864643</v>
+      </c>
+      <c r="CO18" s="1">
+        <f t="shared" si="87"/>
+        <v>614.72391189526002</v>
+      </c>
+      <c r="CP18" s="1">
+        <f t="shared" si="87"/>
+        <v>608.57667277630742</v>
+      </c>
+      <c r="CQ18" s="1">
+        <f t="shared" si="87"/>
+        <v>602.49090604854439</v>
+      </c>
+      <c r="CR18" s="1">
+        <f t="shared" si="87"/>
+        <v>596.46599698805892</v>
+      </c>
+      <c r="CS18" s="1">
+        <f t="shared" si="87"/>
+        <v>590.50133701817833</v>
+      </c>
+      <c r="CT18" s="1">
+        <f t="shared" si="87"/>
+        <v>584.59632364799654</v>
+      </c>
+      <c r="CU18" s="1">
+        <f t="shared" si="87"/>
+        <v>578.75036041151657</v>
+      </c>
+      <c r="CV18" s="1">
+        <f t="shared" si="87"/>
+        <v>572.96285680740141</v>
+      </c>
+      <c r="CW18" s="1">
+        <f t="shared" si="87"/>
+        <v>567.23322823932745</v>
+      </c>
+      <c r="CX18" s="1">
+        <f t="shared" si="87"/>
+        <v>561.56089595693413</v>
+      </c>
+      <c r="CY18" s="1">
+        <f t="shared" si="87"/>
+        <v>555.94528699736475</v>
+      </c>
+      <c r="CZ18" s="1">
+        <f t="shared" si="87"/>
+        <v>550.38583412739115</v>
+      </c>
+      <c r="DA18" s="1">
+        <f t="shared" si="87"/>
+        <v>544.88197578611721</v>
+      </c>
+      <c r="DB18" s="1">
+        <f t="shared" si="87"/>
+        <v>539.43315602825601</v>
+      </c>
+      <c r="DC18" s="1">
+        <f t="shared" si="87"/>
+        <v>534.03882446797343</v>
+      </c>
+      <c r="DD18" s="1">
+        <f t="shared" si="87"/>
+        <v>528.6984362232937</v>
+      </c>
+      <c r="DE18" s="1">
+        <f t="shared" si="87"/>
+        <v>523.41145186106075</v>
+      </c>
+      <c r="DF18" s="1">
+        <f t="shared" si="87"/>
+        <v>518.17733734245019</v>
+      </c>
+      <c r="DG18" s="1">
+        <f t="shared" si="87"/>
+        <v>512.99556396902562</v>
+      </c>
+      <c r="DH18" s="1">
+        <f t="shared" si="87"/>
+        <v>507.86560832933537</v>
+      </c>
+      <c r="DI18" s="1">
+        <f t="shared" si="87"/>
+        <v>502.78695224604201</v>
+      </c>
+      <c r="DJ18" s="1">
+        <f t="shared" si="87"/>
+        <v>497.75908272358157</v>
+      </c>
+      <c r="DK18" s="1">
+        <f t="shared" si="87"/>
+        <v>492.78149189634576</v>
+      </c>
+      <c r="DL18" s="1">
+        <f t="shared" si="87"/>
+        <v>487.85367697738229</v>
+      </c>
+      <c r="DM18" s="1">
+        <f t="shared" si="87"/>
+        <v>482.97514020760849</v>
+      </c>
+      <c r="DN18" s="1">
+        <f t="shared" si="87"/>
+        <v>478.14538880553238</v>
+      </c>
+      <c r="DO18" s="1">
+        <f t="shared" si="87"/>
+        <v>473.36393491747702</v>
+      </c>
+      <c r="DP18" s="1">
+        <f t="shared" si="87"/>
+        <v>468.63029556830224</v>
+      </c>
+      <c r="DQ18" s="1">
+        <f t="shared" si="87"/>
+        <v>463.94399261261924</v>
+      </c>
+      <c r="DR18" s="1">
+        <f t="shared" si="87"/>
+        <v>459.30455268649303</v>
+      </c>
+      <c r="DS18" s="1">
+        <f t="shared" si="87"/>
+        <v>454.71150715962807</v>
+      </c>
+      <c r="DT18" s="1">
+        <f t="shared" ref="DT18:FL18" si="88">DS18*(1+$BI$24)</f>
+        <v>450.16439208803178</v>
+      </c>
+      <c r="DU18" s="1">
         <f t="shared" si="88"/>
-        <v>881.45264812446692</v>
-      </c>
-      <c r="BJ18" s="1">
+        <v>445.66274816715145</v>
+      </c>
+      <c r="DV18" s="1">
         <f t="shared" si="88"/>
-        <v>872.63812164322223</v>
-      </c>
-      <c r="BK18" s="1">
+        <v>441.2061206854799</v>
+      </c>
+      <c r="DW18" s="1">
         <f t="shared" si="88"/>
-        <v>863.91174042679006</v>
-      </c>
-      <c r="BL18" s="1">
+        <v>436.79405947862512</v>
+      </c>
+      <c r="DX18" s="1">
         <f t="shared" si="88"/>
-        <v>855.27262302252211</v>
-      </c>
-      <c r="BM18" s="1">
+        <v>432.42611888383885</v>
+      </c>
+      <c r="DY18" s="1">
         <f t="shared" si="88"/>
-        <v>846.71989679229694</v>
-      </c>
-      <c r="BN18" s="1">
+        <v>428.10185769500043</v>
+      </c>
+      <c r="DZ18" s="1">
         <f t="shared" si="88"/>
-        <v>838.25269782437397</v>
-      </c>
-      <c r="BO18" s="1">
+        <v>423.8208391180504</v>
+      </c>
+      <c r="EA18" s="1">
         <f t="shared" si="88"/>
-        <v>829.87017084613024</v>
-      </c>
-      <c r="BP18" s="1">
+        <v>419.58263072686987</v>
+      </c>
+      <c r="EB18" s="1">
         <f t="shared" si="88"/>
-        <v>821.57146913766894</v>
-      </c>
-      <c r="BQ18" s="1">
+        <v>415.38680441960116</v>
+      </c>
+      <c r="EC18" s="1">
         <f t="shared" si="88"/>
-        <v>813.35575444629228</v>
-      </c>
-      <c r="BR18" s="1">
+        <v>411.23293637540513</v>
+      </c>
+      <c r="ED18" s="1">
         <f t="shared" si="88"/>
-        <v>805.22219690182931</v>
-      </c>
-      <c r="BS18" s="1">
+        <v>407.12060701165109</v>
+      </c>
+      <c r="EE18" s="1">
         <f t="shared" si="88"/>
-        <v>797.16997493281099</v>
-      </c>
-      <c r="BT18" s="1">
+        <v>403.0494009415346</v>
+      </c>
+      <c r="EF18" s="1">
         <f t="shared" si="88"/>
-        <v>789.19827518348291</v>
-      </c>
-      <c r="BU18" s="1">
+        <v>399.01890693211925</v>
+      </c>
+      <c r="EG18" s="1">
         <f t="shared" si="88"/>
-        <v>781.3062924316481</v>
-      </c>
-      <c r="BV18" s="1">
+        <v>395.02871786279803</v>
+      </c>
+      <c r="EH18" s="1">
         <f t="shared" si="88"/>
-        <v>773.49322950733165</v>
-      </c>
-      <c r="BW18" s="1">
+        <v>391.07843068417003</v>
+      </c>
+      <c r="EI18" s="1">
         <f t="shared" si="88"/>
-        <v>765.7582972122583</v>
-      </c>
-      <c r="BX18" s="1">
+        <v>387.16764637732831</v>
+      </c>
+      <c r="EJ18" s="1">
         <f t="shared" si="88"/>
-        <v>758.10071424013574</v>
-      </c>
-      <c r="BY18" s="1">
+        <v>383.29596991355504</v>
+      </c>
+      <c r="EK18" s="1">
         <f t="shared" si="88"/>
-        <v>750.51970709773434</v>
-      </c>
-      <c r="BZ18" s="1">
+        <v>379.46301021441951</v>
+      </c>
+      <c r="EL18" s="1">
         <f t="shared" si="88"/>
-        <v>743.01451002675697</v>
-      </c>
-      <c r="CA18" s="1">
+        <v>375.66838011227532</v>
+      </c>
+      <c r="EM18" s="1">
         <f t="shared" si="88"/>
-        <v>735.58436492648934</v>
-      </c>
-      <c r="CB18" s="1">
+        <v>371.91169631115258</v>
+      </c>
+      <c r="EN18" s="1">
         <f t="shared" si="88"/>
-        <v>728.22852127722444</v>
-      </c>
-      <c r="CC18" s="1">
+        <v>368.19257934804108</v>
+      </c>
+      <c r="EO18" s="1">
         <f t="shared" si="88"/>
-        <v>720.94623606445225</v>
-      </c>
-      <c r="CD18" s="1">
+        <v>364.51065355456069</v>
+      </c>
+      <c r="EP18" s="1">
         <f t="shared" si="88"/>
-        <v>713.73677370380767</v>
-      </c>
-      <c r="CE18" s="1">
+        <v>360.86554701901508</v>
+      </c>
+      <c r="EQ18" s="1">
         <f t="shared" si="88"/>
-        <v>706.59940596676961</v>
-      </c>
-      <c r="CF18" s="1">
+        <v>357.25689154882491</v>
+      </c>
+      <c r="ER18" s="1">
         <f t="shared" si="88"/>
-        <v>699.53341190710194</v>
-      </c>
-      <c r="CG18" s="1">
+        <v>353.68432263333665</v>
+      </c>
+      <c r="ES18" s="1">
         <f t="shared" si="88"/>
-        <v>692.53807778803093</v>
-      </c>
-      <c r="CH18" s="1">
+        <v>350.14747940700329</v>
+      </c>
+      <c r="ET18" s="1">
         <f t="shared" si="88"/>
-        <v>685.61269701015067</v>
-      </c>
-      <c r="CI18" s="1">
+        <v>346.64600461293327</v>
+      </c>
+      <c r="EU18" s="1">
         <f t="shared" si="88"/>
-        <v>678.75657004004916</v>
-      </c>
-      <c r="CJ18" s="1">
+        <v>343.17954456680394</v>
+      </c>
+      <c r="EV18" s="1">
         <f t="shared" si="88"/>
-        <v>671.96900433964868</v>
-      </c>
-      <c r="CK18" s="1">
+        <v>339.74774912113588</v>
+      </c>
+      <c r="EW18" s="1">
         <f t="shared" si="88"/>
-        <v>665.24931429625224</v>
-      </c>
-      <c r="CL18" s="1">
+        <v>336.35027162992452</v>
+      </c>
+      <c r="EX18" s="1">
         <f t="shared" si="88"/>
-        <v>658.59682115328974</v>
-      </c>
-      <c r="CM18" s="1">
+        <v>332.98676891362527</v>
+      </c>
+      <c r="EY18" s="1">
         <f t="shared" si="88"/>
-        <v>652.01085294175687</v>
-      </c>
-      <c r="CN18" s="1">
+        <v>329.65690122448899</v>
+      </c>
+      <c r="EZ18" s="1">
         <f t="shared" si="88"/>
-        <v>645.49074441233927</v>
-      </c>
-      <c r="CO18" s="1">
+        <v>326.36033221224409</v>
+      </c>
+      <c r="FA18" s="1">
         <f t="shared" si="88"/>
-        <v>639.0358369682159</v>
-      </c>
-      <c r="CP18" s="1">
+        <v>323.09672889012165</v>
+      </c>
+      <c r="FB18" s="1">
         <f t="shared" si="88"/>
-        <v>632.64547859853371</v>
-      </c>
-      <c r="CQ18" s="1">
+        <v>319.86576160122041</v>
+      </c>
+      <c r="FC18" s="1">
         <f t="shared" si="88"/>
-        <v>626.31902381254838</v>
-      </c>
-      <c r="CR18" s="1">
+        <v>316.6671039852082</v>
+      </c>
+      <c r="FD18" s="1">
         <f t="shared" si="88"/>
-        <v>620.05583357442288</v>
-      </c>
-      <c r="CS18" s="1">
+        <v>313.50043294535612</v>
+      </c>
+      <c r="FE18" s="1">
         <f t="shared" si="88"/>
-        <v>613.85527523867859</v>
-      </c>
-      <c r="CT18" s="1">
+        <v>310.36542861590254</v>
+      </c>
+      <c r="FF18" s="1">
         <f t="shared" si="88"/>
-        <v>607.71672248629181</v>
-      </c>
-      <c r="CU18" s="1">
+        <v>307.2617743297435</v>
+      </c>
+      <c r="FG18" s="1">
         <f t="shared" si="88"/>
-        <v>601.63955526142888</v>
-      </c>
-      <c r="CV18" s="1">
+        <v>304.18915658644607</v>
+      </c>
+      <c r="FH18" s="1">
         <f t="shared" si="88"/>
-        <v>595.62315970881457</v>
-      </c>
-      <c r="CW18" s="1">
+        <v>301.14726502058159</v>
+      </c>
+      <c r="FI18" s="1">
         <f t="shared" si="88"/>
-        <v>589.66692811172641</v>
-      </c>
-      <c r="CX18" s="1">
+        <v>298.13579237037578</v>
+      </c>
+      <c r="FJ18" s="1">
         <f t="shared" si="88"/>
-        <v>583.77025883060912</v>
-      </c>
-      <c r="CY18" s="1">
+        <v>295.15443444667204</v>
+      </c>
+      <c r="FK18" s="1">
         <f t="shared" si="88"/>
-        <v>577.93255624230301</v>
-      </c>
-      <c r="CZ18" s="1">
+        <v>292.20289010220534</v>
+      </c>
+      <c r="FL18" s="1">
         <f t="shared" si="88"/>
-        <v>572.15323067987993</v>
-      </c>
-      <c r="DA18" s="1">
-        <f t="shared" si="88"/>
-        <v>566.43169837308108</v>
-      </c>
-      <c r="DB18" s="1">
-        <f t="shared" si="88"/>
-        <v>560.76738138935025</v>
-      </c>
-      <c r="DC18" s="1">
-        <f t="shared" si="88"/>
-        <v>555.15970757545676</v>
-      </c>
-      <c r="DD18" s="1">
-        <f t="shared" si="88"/>
-        <v>549.60811049970221</v>
-      </c>
-      <c r="DE18" s="1">
-        <f t="shared" si="88"/>
-        <v>544.11202939470513</v>
-      </c>
-      <c r="DF18" s="1">
-        <f t="shared" si="88"/>
-        <v>538.67090910075808</v>
-      </c>
-      <c r="DG18" s="1">
-        <f t="shared" si="88"/>
-        <v>533.28420000975052</v>
-      </c>
-      <c r="DH18" s="1">
-        <f t="shared" si="88"/>
-        <v>527.95135800965306</v>
-      </c>
-      <c r="DI18" s="1">
-        <f t="shared" si="88"/>
-        <v>522.67184442955647</v>
-      </c>
-      <c r="DJ18" s="1">
-        <f t="shared" si="88"/>
-        <v>517.44512598526092</v>
-      </c>
-      <c r="DK18" s="1">
-        <f t="shared" si="88"/>
-        <v>512.2706747254083</v>
-      </c>
-      <c r="DL18" s="1">
-        <f t="shared" si="88"/>
-        <v>507.14796797815421</v>
-      </c>
-      <c r="DM18" s="1">
-        <f t="shared" si="88"/>
-        <v>502.07648829837268</v>
-      </c>
-      <c r="DN18" s="1">
-        <f t="shared" si="88"/>
-        <v>497.05572341538897</v>
-      </c>
-      <c r="DO18" s="1">
-        <f t="shared" si="88"/>
-        <v>492.08516618123508</v>
-      </c>
-      <c r="DP18" s="1">
-        <f t="shared" si="88"/>
-        <v>487.1643145194227</v>
-      </c>
-      <c r="DQ18" s="1">
-        <f t="shared" si="88"/>
-        <v>482.29267137422846</v>
-      </c>
-      <c r="DR18" s="1">
-        <f t="shared" si="88"/>
-        <v>477.46974466048619</v>
-      </c>
-      <c r="DS18" s="1">
-        <f t="shared" si="88"/>
-        <v>472.69504721388131</v>
-      </c>
-      <c r="DT18" s="1">
-        <f t="shared" ref="DT18:FL18" si="89">DS18*(1+$BI$24)</f>
-        <v>467.9680967417425</v>
-      </c>
-      <c r="DU18" s="1">
-        <f t="shared" si="89"/>
-        <v>463.28841577432507</v>
-      </c>
-      <c r="DV18" s="1">
-        <f t="shared" si="89"/>
-        <v>458.65553161658181</v>
-      </c>
-      <c r="DW18" s="1">
-        <f t="shared" si="89"/>
-        <v>454.06897630041601</v>
-      </c>
-      <c r="DX18" s="1">
-        <f t="shared" si="89"/>
-        <v>449.52828653741187</v>
-      </c>
-      <c r="DY18" s="1">
-        <f t="shared" si="89"/>
-        <v>445.03300367203775</v>
-      </c>
-      <c r="DZ18" s="1">
-        <f t="shared" si="89"/>
-        <v>440.58267363531735</v>
-      </c>
-      <c r="EA18" s="1">
-        <f t="shared" si="89"/>
-        <v>436.17684689896419</v>
-      </c>
-      <c r="EB18" s="1">
-        <f t="shared" si="89"/>
-        <v>431.81507842997456</v>
-      </c>
-      <c r="EC18" s="1">
-        <f t="shared" si="89"/>
-        <v>427.49692764567482</v>
-      </c>
-      <c r="ED18" s="1">
-        <f t="shared" si="89"/>
-        <v>423.22195836921804</v>
-      </c>
-      <c r="EE18" s="1">
-        <f t="shared" si="89"/>
-        <v>418.98973878552584</v>
-      </c>
-      <c r="EF18" s="1">
-        <f t="shared" si="89"/>
-        <v>414.7998413976706</v>
-      </c>
-      <c r="EG18" s="1">
-        <f t="shared" si="89"/>
-        <v>410.65184298369388</v>
-      </c>
-      <c r="EH18" s="1">
-        <f t="shared" si="89"/>
-        <v>406.54532455385691</v>
-      </c>
-      <c r="EI18" s="1">
-        <f t="shared" si="89"/>
-        <v>402.47987130831837</v>
-      </c>
-      <c r="EJ18" s="1">
-        <f t="shared" si="89"/>
-        <v>398.45507259523515</v>
-      </c>
-      <c r="EK18" s="1">
-        <f t="shared" si="89"/>
-        <v>394.47052186928278</v>
-      </c>
-      <c r="EL18" s="1">
-        <f t="shared" si="89"/>
-        <v>390.52581665058995</v>
-      </c>
-      <c r="EM18" s="1">
-        <f t="shared" si="89"/>
-        <v>386.62055848408403</v>
-      </c>
-      <c r="EN18" s="1">
-        <f t="shared" si="89"/>
-        <v>382.7543528992432</v>
-      </c>
-      <c r="EO18" s="1">
-        <f t="shared" si="89"/>
-        <v>378.92680937025079</v>
-      </c>
-      <c r="EP18" s="1">
-        <f t="shared" si="89"/>
-        <v>375.13754127654829</v>
-      </c>
-      <c r="EQ18" s="1">
-        <f t="shared" si="89"/>
-        <v>371.38616586378282</v>
-      </c>
-      <c r="ER18" s="1">
-        <f t="shared" si="89"/>
-        <v>367.672304205145</v>
-      </c>
-      <c r="ES18" s="1">
-        <f t="shared" si="89"/>
-        <v>363.99558116309356</v>
-      </c>
-      <c r="ET18" s="1">
-        <f t="shared" si="89"/>
-        <v>360.35562535146261</v>
-      </c>
-      <c r="EU18" s="1">
-        <f t="shared" si="89"/>
-        <v>356.75206909794798</v>
-      </c>
-      <c r="EV18" s="1">
-        <f t="shared" si="89"/>
-        <v>353.18454840696847</v>
-      </c>
-      <c r="EW18" s="1">
-        <f t="shared" si="89"/>
-        <v>349.65270292289881</v>
-      </c>
-      <c r="EX18" s="1">
-        <f t="shared" si="89"/>
-        <v>346.1561758936698</v>
-      </c>
-      <c r="EY18" s="1">
-        <f t="shared" si="89"/>
-        <v>342.69461413473311</v>
-      </c>
-      <c r="EZ18" s="1">
-        <f t="shared" si="89"/>
-        <v>339.26766799338577</v>
-      </c>
-      <c r="FA18" s="1">
-        <f t="shared" si="89"/>
-        <v>335.87499131345191</v>
-      </c>
-      <c r="FB18" s="1">
-        <f t="shared" si="89"/>
-        <v>332.51624140031737</v>
-      </c>
-      <c r="FC18" s="1">
-        <f t="shared" si="89"/>
-        <v>329.19107898631421</v>
-      </c>
-      <c r="FD18" s="1">
-        <f t="shared" si="89"/>
-        <v>325.89916819645106</v>
-      </c>
-      <c r="FE18" s="1">
-        <f t="shared" si="89"/>
-        <v>322.64017651448654</v>
-      </c>
-      <c r="FF18" s="1">
-        <f t="shared" si="89"/>
-        <v>319.41377474934166</v>
-      </c>
-      <c r="FG18" s="1">
-        <f t="shared" si="89"/>
-        <v>316.21963700184824</v>
-      </c>
-      <c r="FH18" s="1">
-        <f t="shared" si="89"/>
-        <v>313.05744063182976</v>
-      </c>
-      <c r="FI18" s="1">
-        <f t="shared" si="89"/>
-        <v>309.92686622551145</v>
-      </c>
-      <c r="FJ18" s="1">
-        <f t="shared" si="89"/>
-        <v>306.82759756325635</v>
-      </c>
-      <c r="FK18" s="1">
-        <f t="shared" si="89"/>
-        <v>303.75932158762379</v>
-      </c>
-      <c r="FL18" s="1">
-        <f t="shared" si="89"/>
-        <v>300.72172837174753</v>
+        <v>289.28086120118331</v>
       </c>
     </row>
     <row r="19" spans="2:168" x14ac:dyDescent="0.3">
@@ -4904,12 +4898,12 @@
         <v>147.1</v>
       </c>
       <c r="AK19" s="6">
-        <f>147.1</f>
-        <v>147.1</v>
+        <f>146.6</f>
+        <v>146.6</v>
       </c>
       <c r="AL19" s="6">
-        <f>147.1</f>
-        <v>147.1</v>
+        <f>146.6</f>
+        <v>146.6</v>
       </c>
       <c r="AO19" s="6">
         <v>168.4</v>
@@ -4937,44 +4931,44 @@
         <v>149</v>
       </c>
       <c r="AW19" s="6">
-        <f t="shared" ref="AW19:BF19" si="90">147.1</f>
-        <v>147.1</v>
+        <f t="shared" ref="AW19:BF19" si="89">146.6</f>
+        <v>146.6</v>
       </c>
       <c r="AX19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="AY19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="AZ19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="BA19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="BB19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="BC19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="BD19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="BE19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
       <c r="BF19" s="6">
-        <f t="shared" si="90"/>
-        <v>147.1</v>
+        <f t="shared" si="89"/>
+        <v>146.6</v>
       </c>
     </row>
     <row r="20" spans="2:168" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4982,220 +4976,220 @@
         <v>45</v>
       </c>
       <c r="C20" s="8">
-        <f t="shared" ref="C20:S20" si="91">C18/C19</f>
+        <f t="shared" ref="C20:S20" si="90">C18/C19</f>
         <v>0.21852731591448907</v>
       </c>
       <c r="D20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.33491686460807601</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.4798099762470307</v>
+      </c>
+      <c r="F20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.20427553444180505</v>
+      </c>
+      <c r="G20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.22802850356294541</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.38123515439429928</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.67042755344418015</v>
+      </c>
+      <c r="J20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.25059382422802845</v>
+      </c>
+      <c r="K20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.26959619952494096</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.43349168646080793</v>
+      </c>
+      <c r="M20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.69774346793349196</v>
+      </c>
+      <c r="N20" s="8">
+        <f t="shared" si="90"/>
+        <v>1.269596199524941</v>
+      </c>
+      <c r="O20" s="8">
+        <f t="shared" si="90"/>
+        <v>0.4287410926365795</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="90"/>
+        <v>1.5849168646080762</v>
+      </c>
+      <c r="Q20" s="8">
+        <f t="shared" si="90"/>
+        <v>2.2719714964370543</v>
+      </c>
+      <c r="R20" s="8">
+        <f t="shared" si="90"/>
+        <v>1.3402612826603331</v>
+      </c>
+      <c r="S20" s="8">
+        <f t="shared" si="90"/>
+        <v>1.1098574821852725</v>
+      </c>
+      <c r="T20" s="8">
+        <f t="shared" ref="T20:U20" si="91">T18/T19</f>
+        <v>0.82779097387173384</v>
+      </c>
+      <c r="U20" s="8">
         <f t="shared" si="91"/>
-        <v>0.33491686460807601</v>
-      </c>
-      <c r="E20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.4798099762470307</v>
-      </c>
-      <c r="F20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.20427553444180505</v>
-      </c>
-      <c r="G20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.22802850356294541</v>
-      </c>
-      <c r="H20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.38123515439429928</v>
-      </c>
-      <c r="I20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.67042755344418015</v>
-      </c>
-      <c r="J20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.25059382422802845</v>
-      </c>
-      <c r="K20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.26959619952494096</v>
-      </c>
-      <c r="L20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.43349168646080793</v>
-      </c>
-      <c r="M20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.69774346793349196</v>
-      </c>
-      <c r="N20" s="8">
-        <f t="shared" si="91"/>
-        <v>1.269596199524941</v>
-      </c>
-      <c r="O20" s="8">
-        <f t="shared" si="91"/>
-        <v>0.4287410926365795</v>
-      </c>
-      <c r="P20" s="8">
-        <f t="shared" si="91"/>
-        <v>1.5849168646080762</v>
-      </c>
-      <c r="Q20" s="8">
-        <f t="shared" si="91"/>
-        <v>2.2719714964370543</v>
-      </c>
-      <c r="R20" s="8">
-        <f t="shared" si="91"/>
-        <v>1.3402612826603331</v>
-      </c>
-      <c r="S20" s="8">
-        <f t="shared" si="91"/>
-        <v>1.1098574821852725</v>
-      </c>
-      <c r="T20" s="8">
-        <f t="shared" ref="T20:U20" si="92">T18/T19</f>
-        <v>0.82779097387173384</v>
-      </c>
-      <c r="U20" s="8">
+        <v>1.2476247030878858</v>
+      </c>
+      <c r="V20" s="8">
+        <f t="shared" ref="V20:W20" si="92">V18/V19</f>
+        <v>0.64251781472684111</v>
+      </c>
+      <c r="W20" s="8">
         <f t="shared" si="92"/>
-        <v>1.2476247030878858</v>
-      </c>
-      <c r="V20" s="8">
-        <f t="shared" ref="V20:W20" si="93">V18/V19</f>
-        <v>0.64251781472684111</v>
-      </c>
-      <c r="W20" s="8">
+        <v>0.59857482185273225</v>
+      </c>
+      <c r="X20" s="8">
+        <f t="shared" ref="X20:Y20" si="93">X18/X19</f>
+        <v>0.4881235154394295</v>
+      </c>
+      <c r="Y20" s="8">
         <f t="shared" si="93"/>
-        <v>0.59857482185273225</v>
-      </c>
-      <c r="X20" s="8">
-        <f t="shared" ref="X20:Y20" si="94">X18/X19</f>
-        <v>0.4881235154394295</v>
-      </c>
-      <c r="Y20" s="8">
-        <f t="shared" si="94"/>
         <v>0.83135391923990565</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" ref="Z20" si="95">Z18/Z19</f>
+        <f t="shared" ref="Z20" si="94">Z18/Z19</f>
         <v>0.24703087885985736</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" ref="AA20" si="96">AA18/AA19</f>
+        <f t="shared" ref="AA20" si="95">AA18/AA19</f>
         <v>0.37232779097387159</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" ref="AB20:AC20" si="97">AB18/AB19</f>
+        <f t="shared" ref="AB20:AC20" si="96">AB18/AB19</f>
         <v>0.81472684085510694</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>1.4519002375296914</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" ref="AD20" si="98">AD18/AD19</f>
+        <f t="shared" ref="AD20" si="97">AD18/AD19</f>
         <v>0.99524940617577196</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" ref="AE20" si="99">AE18/AE19</f>
+        <f t="shared" ref="AE20" si="98">AE18/AE19</f>
         <v>0.84204275534441841</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" ref="AF20:AH20" si="100">AF18/AF19</f>
+        <f t="shared" ref="AF20:AH20" si="99">AF18/AF19</f>
         <v>0.95844327176781019</v>
       </c>
       <c r="AG20" s="8">
+        <f t="shared" si="99"/>
+        <v>1.3418230563002675</v>
+      </c>
+      <c r="AH20" s="8">
+        <f t="shared" si="99"/>
+        <v>0.96778523489932899</v>
+      </c>
+      <c r="AI20" s="8">
+        <f t="shared" ref="AI20:AL20" si="100">AI18/AI19</f>
+        <v>0.98782961460446261</v>
+      </c>
+      <c r="AJ20" s="8">
         <f t="shared" si="100"/>
-        <v>1.3418230563002675</v>
-      </c>
-      <c r="AH20" s="8">
+        <v>1.1604350781781096</v>
+      </c>
+      <c r="AK20" s="8">
         <f t="shared" si="100"/>
-        <v>0.96778523489932899</v>
-      </c>
-      <c r="AI20" s="8">
-        <f t="shared" ref="AI20:AL20" si="101">AI18/AI19</f>
-        <v>0.98782961460446261</v>
-      </c>
-      <c r="AJ20" s="8">
+        <v>1.7114597544338344</v>
+      </c>
+      <c r="AL20" s="8">
+        <f t="shared" si="100"/>
+        <v>0.76992272032742182</v>
+      </c>
+      <c r="AO20" s="8">
+        <f t="shared" ref="AO20:AT20" si="101">AO18/AO19</f>
+        <v>1.237529691211404</v>
+      </c>
+      <c r="AP20" s="8">
         <f t="shared" si="101"/>
-        <v>1.1604350781781096</v>
-      </c>
-      <c r="AK20" s="8">
+        <v>1.5302850356294546</v>
+      </c>
+      <c r="AQ20" s="8">
         <f t="shared" si="101"/>
-        <v>1.6318632256968049</v>
-      </c>
-      <c r="AL20" s="8">
+        <v>2.6603325415676977</v>
+      </c>
+      <c r="AR20" s="8">
         <f t="shared" si="101"/>
-        <v>0.73982543711760729</v>
-      </c>
-      <c r="AO20" s="8">
-        <f t="shared" ref="AO20:AT20" si="102">AO18/AO19</f>
-        <v>1.237529691211404</v>
-      </c>
-      <c r="AP20" s="8">
+        <v>5.6258907363420381</v>
+      </c>
+      <c r="AS20" s="8">
+        <f t="shared" si="101"/>
+        <v>3.8408551068883607</v>
+      </c>
+      <c r="AT20" s="8">
+        <f t="shared" si="101"/>
+        <v>2.1650831353919293</v>
+      </c>
+      <c r="AU20" s="8">
+        <f t="shared" ref="AU20:BC20" si="102">AU18/AU19</f>
+        <v>3.6342042755344446</v>
+      </c>
+      <c r="AV20" s="8">
         <f t="shared" si="102"/>
-        <v>1.5302850356294546</v>
-      </c>
-      <c r="AQ20" s="8">
+        <v>4.2382550335570466</v>
+      </c>
+      <c r="AW20" s="8">
         <f t="shared" si="102"/>
-        <v>2.6603325415676977</v>
-      </c>
-      <c r="AR20" s="8">
+        <v>4.6423647394270118</v>
+      </c>
+      <c r="AX20" s="8">
         <f t="shared" si="102"/>
-        <v>5.6258907363420381</v>
-      </c>
-      <c r="AS20" s="8">
+        <v>5.0328949443110513</v>
+      </c>
+      <c r="AY20" s="8">
         <f t="shared" si="102"/>
-        <v>3.8408551068883607</v>
-      </c>
-      <c r="AT20" s="8">
+        <v>5.1831167545776289</v>
+      </c>
+      <c r="AZ20" s="8">
         <f t="shared" si="102"/>
-        <v>2.1650831353919293</v>
-      </c>
-      <c r="AU20" s="8">
-        <f t="shared" ref="AU20:BC20" si="103">AU18/AU19</f>
-        <v>3.6342042755344446</v>
-      </c>
-      <c r="AV20" s="8">
+        <v>5.2877147148124264</v>
+      </c>
+      <c r="BA20" s="8">
+        <f t="shared" si="102"/>
+        <v>5.3944139905033568</v>
+      </c>
+      <c r="BB20" s="8">
+        <f t="shared" si="102"/>
+        <v>5.5032567015220506</v>
+      </c>
+      <c r="BC20" s="8">
+        <f t="shared" si="102"/>
+        <v>5.614285811073203</v>
+      </c>
+      <c r="BD20" s="8">
+        <f t="shared" ref="BD20:BF20" si="103">BD18/BD19</f>
+        <v>5.7275451425705866</v>
+      </c>
+      <c r="BE20" s="8">
         <f t="shared" si="103"/>
-        <v>4.2382550335570466</v>
-      </c>
-      <c r="AW20" s="8">
+        <v>5.8430793968506771</v>
+      </c>
+      <c r="BF20" s="8">
         <f t="shared" si="103"/>
-        <v>4.5253256444595538</v>
-      </c>
-      <c r="AX20" s="8">
-        <f t="shared" si="103"/>
-        <v>5.2132915565465678</v>
-      </c>
-      <c r="AY20" s="8">
-        <f t="shared" si="103"/>
-        <v>5.369077983726176</v>
-      </c>
-      <c r="AZ20" s="8">
-        <f t="shared" si="103"/>
-        <v>5.4775358841280921</v>
-      </c>
-      <c r="BA20" s="8">
-        <f t="shared" si="103"/>
-        <v>5.5881737059453274</v>
-      </c>
-      <c r="BB20" s="8">
-        <f t="shared" si="103"/>
-        <v>5.7010351552402501</v>
-      </c>
-      <c r="BC20" s="8">
-        <f t="shared" si="103"/>
-        <v>5.8161648132728292</v>
-      </c>
-      <c r="BD20" s="8">
-        <f t="shared" ref="BD20:BF20" si="104">BD18/BD19</f>
-        <v>5.9336081540153423</v>
-      </c>
-      <c r="BE20" s="8">
-        <f t="shared" si="104"/>
-        <v>6.0534115620174767</v>
-      </c>
-      <c r="BF20" s="8">
-        <f t="shared" si="104"/>
-        <v>6.1756223506288697</v>
+        <v>5.9609341697306562</v>
       </c>
     </row>
     <row r="22" spans="2:168" x14ac:dyDescent="0.3">
@@ -5211,128 +5205,128 @@
         <v>0.14832987356104921</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" ref="H22:V22" si="105">H3/D3-1</f>
+        <f t="shared" ref="H22:V22" si="104">H3/D3-1</f>
         <v>9.2648221343873516E-2</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>6.4532019704433452E-2</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>5.3848750844024185E-2</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>5.8668857847165246E-2</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>4.1383301982347076E-2</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>4.4308190652475821E-2</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>0.13599231138875556</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>0.22927662216702882</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>0.74683896067806033</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>0.84701451201949696</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>1.1656796390298929</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>0.65690112387927768</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>3.90550429525931E-2</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>-2.0692136987944587E-2</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>-0.19916661240966216</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" ref="W22" si="106">W3/S3-1</f>
+        <f t="shared" ref="W22" si="105">W3/S3-1</f>
         <v>-0.11599725630668378</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" ref="X22" si="107">X3/T3-1</f>
+        <f t="shared" ref="X22" si="106">X3/T3-1</f>
         <v>-0.12041644338972668</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" ref="Y22" si="108">Y3/U3-1</f>
+        <f t="shared" ref="Y22" si="107">Y3/U3-1</f>
         <v>-0.22225624693777557</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" ref="Z22" si="109">Z3/V3-1</f>
+        <f t="shared" ref="Z22" si="108">Z3/V3-1</f>
         <v>-0.21943089430894303</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" ref="AA22" si="110">AA3/W3-1</f>
+        <f t="shared" ref="AA22" si="109">AA3/W3-1</f>
         <v>-0.15984136563496865</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" ref="AB22" si="111">AB3/X3-1</f>
+        <f t="shared" ref="AB22" si="110">AB3/X3-1</f>
         <v>-8.006962576153176E-2</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" ref="AC22" si="112">AC3/Y3-1</f>
+        <f t="shared" ref="AC22" si="111">AC3/Y3-1</f>
         <v>-1.1339475549255962E-2</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" ref="AD22" si="113">AD3/Z3-1</f>
+        <f t="shared" ref="AD22" si="112">AD3/Z3-1</f>
         <v>5.3536089990625868E-2</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" ref="AE22" si="114">AE3/AA3-1</f>
+        <f t="shared" ref="AE22" si="113">AE3/AA3-1</f>
         <v>0.11667521806054393</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" ref="AF22" si="115">AF3/AB3-1</f>
+        <f t="shared" ref="AF22" si="114">AF3/AB3-1</f>
         <v>5.5818353831598833E-2</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" ref="AG22" si="116">AG3/AC3-1</f>
+        <f t="shared" ref="AG22" si="115">AG3/AC3-1</f>
         <v>6.7542811628833022E-2</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" ref="AH22" si="117">AH3/AD3-1</f>
+        <f t="shared" ref="AH22" si="116">AH3/AD3-1</f>
         <v>-1.0874938210578833E-3</v>
       </c>
       <c r="AI22" s="10">
-        <f t="shared" ref="AI22" si="118">AI3/AE3-1</f>
+        <f t="shared" ref="AI22" si="117">AI3/AE3-1</f>
         <v>5.4677448998345923E-2</v>
       </c>
       <c r="AJ22" s="10">
-        <f t="shared" ref="AJ22" si="119">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ22" si="118">AJ3/AF3-1</f>
         <v>6.2813620071684451E-2</v>
       </c>
       <c r="AK22" s="10">
-        <f t="shared" ref="AK22" si="120">AK3/AG3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AK22" si="119">AK3/AG3-1</f>
+        <v>6.0583451466089677E-2</v>
       </c>
       <c r="AL22" s="10">
-        <f t="shared" ref="AL22" si="121">AL3/AH3-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AL22" si="120">AL3/AH3-1</f>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AO22" s="10"/>
       <c r="AP22" s="10">
@@ -5340,67 +5334,67 @@
         <v>8.6294218482156682E-2</v>
       </c>
       <c r="AQ22" s="10">
-        <f t="shared" ref="AQ22:BC22" si="122">AQ3/AP3-1</f>
+        <f t="shared" ref="AQ22:BC22" si="121">AQ3/AP3-1</f>
         <v>6.7245274898683816E-2</v>
       </c>
       <c r="AR22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>0.76500436857315646</v>
       </c>
       <c r="AS22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>4.3580907411991054E-2</v>
       </c>
       <c r="AT22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>-0.171914909143983</v>
       </c>
       <c r="AU22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>-5.2964374628214017E-2</v>
       </c>
       <c r="AV22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>5.9648714667907221E-2</v>
       </c>
       <c r="AW22" s="10">
-        <f t="shared" si="122"/>
-        <v>5.203868361544739E-2</v>
+        <f t="shared" si="121"/>
+        <v>5.9589453116424274E-2</v>
       </c>
       <c r="AX22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AY22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC22" s="10">
-        <f t="shared" si="122"/>
+        <f t="shared" si="121"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD22" s="10">
-        <f t="shared" ref="BD22" si="123">BD3/BC3-1</f>
+        <f t="shared" ref="BD22" si="122">BD3/BC3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE22" s="10">
-        <f t="shared" ref="BE22" si="124">BE3/BD3-1</f>
+        <f t="shared" ref="BE22" si="123">BE3/BD3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF22" s="10">
-        <f t="shared" ref="BF22" si="125">BF3/BE3-1</f>
+        <f t="shared" ref="BF22" si="124">BF3/BE3-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -5409,19 +5403,19 @@
         <v>49</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:F23" si="126">C5/C3</f>
+        <f t="shared" ref="C23:F23" si="125">C5/C3</f>
         <v>0.36818267597659932</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="125"/>
         <v>0.3633201581027668</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="125"/>
         <v>0.3428571428571428</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="125"/>
         <v>0.36259284267386893</v>
       </c>
       <c r="G23" s="10">
@@ -5429,200 +5423,200 @@
         <v>0.37189811010682006</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" ref="H23:V23" si="127">H5/H3</f>
+        <f t="shared" ref="H23:V23" si="126">H5/H3</f>
         <v>0.37476486760237304</v>
       </c>
       <c r="I23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.3802637667746413</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.37850392439532271</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.3759701955914313</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.38265944143393082</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.374875373878365</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.3963620981387479</v>
+      </c>
+      <c r="O23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.39057961863871699</v>
+      </c>
+      <c r="P23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.45545657015590202</v>
+      </c>
+      <c r="Q23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.45126851796317397</v>
+      </c>
+      <c r="R23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.46539488247932809</v>
+      </c>
+      <c r="S23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.43670451947260114</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.4179744316007043</v>
+      </c>
+      <c r="U23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.40494855463008328</v>
+      </c>
+      <c r="V23" s="10">
+        <f t="shared" si="126"/>
+        <v>0.40398373983739838</v>
+      </c>
+      <c r="W23" s="10">
+        <f t="shared" ref="W23:AH23" si="127">W5/W3</f>
+        <v>0.39891369945684974</v>
+      </c>
+      <c r="X23" s="10">
         <f t="shared" si="127"/>
-        <v>0.3802637667746413</v>
-      </c>
-      <c r="J23" s="10">
+        <v>0.38468233246301131</v>
+      </c>
+      <c r="Y23" s="10">
         <f t="shared" si="127"/>
-        <v>0.37850392439532271</v>
-      </c>
-      <c r="K23" s="10">
+        <v>0.37829750374045207</v>
+      </c>
+      <c r="Z23" s="10">
         <f t="shared" si="127"/>
-        <v>0.3759701955914313</v>
-      </c>
-      <c r="L23" s="10">
+        <v>0.36183730861368602</v>
+      </c>
+      <c r="AA23" s="10">
         <f t="shared" si="127"/>
-        <v>0.38265944143393082</v>
-      </c>
-      <c r="M23" s="10">
+        <v>0.38871216008209336</v>
+      </c>
+      <c r="AB23" s="10">
         <f t="shared" si="127"/>
-        <v>0.374875373878365</v>
-      </c>
-      <c r="N23" s="10">
+        <v>0.41778618732261119</v>
+      </c>
+      <c r="AC23" s="10">
         <f t="shared" si="127"/>
-        <v>0.3963620981387479</v>
-      </c>
-      <c r="O23" s="10">
+        <v>0.42134607726005574</v>
+      </c>
+      <c r="AD23" s="10">
         <f t="shared" si="127"/>
-        <v>0.39057961863871699</v>
-      </c>
-      <c r="P23" s="10">
+        <v>0.43440434997528421</v>
+      </c>
+      <c r="AE23" s="10">
         <f t="shared" si="127"/>
-        <v>0.45545657015590202</v>
-      </c>
-      <c r="Q23" s="10">
+        <v>0.43071126631133982</v>
+      </c>
+      <c r="AF23" s="10">
         <f t="shared" si="127"/>
-        <v>0.45126851796317397</v>
-      </c>
-      <c r="R23" s="10">
+        <v>0.43772401433691754</v>
+      </c>
+      <c r="AG23" s="10">
         <f t="shared" si="127"/>
-        <v>0.46539488247932809</v>
-      </c>
-      <c r="S23" s="10">
+        <v>0.43042602402447211</v>
+      </c>
+      <c r="AH23" s="10">
         <f t="shared" si="127"/>
-        <v>0.43670451947260114</v>
-      </c>
-      <c r="T23" s="10">
-        <f t="shared" si="127"/>
-        <v>0.4179744316007043</v>
-      </c>
-      <c r="U23" s="10">
-        <f t="shared" si="127"/>
-        <v>0.40494855463008328</v>
-      </c>
-      <c r="V23" s="10">
-        <f t="shared" si="127"/>
-        <v>0.40398373983739838</v>
-      </c>
-      <c r="W23" s="10">
-        <f t="shared" ref="W23:AH23" si="128">W5/W3</f>
-        <v>0.39891369945684974</v>
-      </c>
-      <c r="X23" s="10">
+        <v>0.43359065716547907</v>
+      </c>
+      <c r="AI23" s="10">
+        <f t="shared" ref="AI23:AL23" si="128">AI5/AI3</f>
+        <v>0.41918619848392435</v>
+      </c>
+      <c r="AJ23" s="10">
         <f t="shared" si="128"/>
-        <v>0.38468233246301131</v>
-      </c>
-      <c r="Y23" s="10">
+        <v>0.43562937357727</v>
+      </c>
+      <c r="AK23" s="10">
         <f t="shared" si="128"/>
-        <v>0.37829750374045207</v>
-      </c>
-      <c r="Z23" s="10">
+        <v>0.43348575448469928</v>
+      </c>
+      <c r="AL23" s="10">
         <f t="shared" si="128"/>
-        <v>0.36183730861368602</v>
-      </c>
-      <c r="AA23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.38871216008209336</v>
-      </c>
-      <c r="AB23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.41778618732261119</v>
-      </c>
-      <c r="AC23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.42134607726005574</v>
-      </c>
-      <c r="AD23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.43440434997528421</v>
-      </c>
-      <c r="AE23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.43071126631133982</v>
-      </c>
-      <c r="AF23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.43772401433691754</v>
-      </c>
-      <c r="AG23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.43042602402447211</v>
-      </c>
-      <c r="AH23" s="10">
-        <f t="shared" si="128"/>
-        <v>0.43359065716547907</v>
-      </c>
-      <c r="AI23" s="10">
-        <f t="shared" ref="AI23:AL23" si="129">AI5/AI3</f>
-        <v>0.41918619848392435</v>
-      </c>
-      <c r="AJ23" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="AO23" s="10">
+        <f t="shared" ref="AO23:BC23" si="129">AO5/AO3</f>
+        <v>0.35768271778089461</v>
+      </c>
+      <c r="AP23" s="10">
         <f t="shared" si="129"/>
-        <v>0.43562937357727</v>
-      </c>
-      <c r="AK23" s="10">
+        <v>0.37668113187246716</v>
+      </c>
+      <c r="AQ23" s="10">
         <f t="shared" si="129"/>
-        <v>0.44</v>
-      </c>
-      <c r="AL23" s="10">
+        <v>0.38211573358424633</v>
+      </c>
+      <c r="AR23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.44725168021628614</v>
+      </c>
+      <c r="AS23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.41543822520615925</v>
+      </c>
+      <c r="AT23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.38170041199409566</v>
+      </c>
+      <c r="AU23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.41614516691869263</v>
+      </c>
+      <c r="AV23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.43298425871039981</v>
+      </c>
+      <c r="AW23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.42983859351340686</v>
+      </c>
+      <c r="AX23" s="10">
         <f t="shared" si="129"/>
         <v>0.43</v>
       </c>
-      <c r="AO23" s="10">
-        <f t="shared" ref="AO23:BC23" si="130">AO5/AO3</f>
-        <v>0.35768271778089461</v>
-      </c>
-      <c r="AP23" s="10">
+      <c r="AY23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.43</v>
+      </c>
+      <c r="AZ23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.43</v>
+      </c>
+      <c r="BA23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.43</v>
+      </c>
+      <c r="BB23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.43</v>
+      </c>
+      <c r="BC23" s="10">
+        <f t="shared" si="129"/>
+        <v>0.43</v>
+      </c>
+      <c r="BD23" s="10">
+        <f t="shared" ref="BD23:BF23" si="130">BD5/BD3</f>
+        <v>0.43</v>
+      </c>
+      <c r="BE23" s="10">
         <f t="shared" si="130"/>
-        <v>0.37668113187246716</v>
-      </c>
-      <c r="AQ23" s="10">
+        <v>0.43000000000000005</v>
+      </c>
+      <c r="BF23" s="10">
         <f t="shared" si="130"/>
-        <v>0.38211573358424633</v>
-      </c>
-      <c r="AR23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.44725168021628614</v>
-      </c>
-      <c r="AS23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.41543822520615925</v>
-      </c>
-      <c r="AT23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.38170041199409566</v>
-      </c>
-      <c r="AU23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.41614516691869263</v>
-      </c>
-      <c r="AV23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.43298425871039981</v>
-      </c>
-      <c r="AW23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.43174024834664776</v>
-      </c>
-      <c r="AX23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="AY23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="AZ23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.44</v>
-      </c>
-      <c r="BA23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="BB23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="BC23" s="10">
-        <f t="shared" si="130"/>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="BD23" s="10">
-        <f t="shared" ref="BD23:BF23" si="131">BD5/BD3</f>
-        <v>0.43999999999999995</v>
-      </c>
-      <c r="BE23" s="10">
-        <f t="shared" si="131"/>
-        <v>0.44</v>
-      </c>
-      <c r="BF23" s="10">
-        <f t="shared" si="131"/>
-        <v>0.44000000000000006</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="24" spans="2:168" x14ac:dyDescent="0.3">
@@ -5630,19 +5624,19 @@
         <v>50</v>
       </c>
       <c r="C24" s="10">
-        <f t="shared" ref="C24:F24" si="132">C13/C3</f>
+        <f t="shared" ref="C24:F24" si="131">C13/C3</f>
         <v>5.8879033779958408E-2</v>
       </c>
       <c r="D24" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>9.3280632411067196E-2</v>
       </c>
       <c r="E24" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>0.12339901477832507</v>
       </c>
       <c r="F24" s="10">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>6.5833896016205221E-2</v>
       </c>
       <c r="G24" s="10">
@@ -5650,200 +5644,200 @@
         <v>5.32456861133936E-2</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" ref="H24:V24" si="133">H13/H3</f>
+        <f t="shared" ref="H24:V24" si="132">H13/H3</f>
         <v>9.4197655910866721E-2</v>
       </c>
       <c r="I24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.1427579824155483</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="132"/>
+        <v>6.7755886592984121E-2</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="132"/>
+        <v>7.3579633654144772E-2</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="132"/>
+        <v>9.4622759483118032E-2</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.14268306192533517</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="132"/>
+        <v>4.5121263395375151E-2</v>
+      </c>
+      <c r="O24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.10556888496022225</v>
+      </c>
+      <c r="P24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.25580655424753423</v>
+      </c>
+      <c r="Q24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.26875787200863671</v>
+      </c>
+      <c r="R24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.19213490461618599</v>
+      </c>
+      <c r="S24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.15486624495084209</v>
+      </c>
+      <c r="T24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.13733445609737424</v>
+      </c>
+      <c r="U24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.16095051445369915</v>
+      </c>
+      <c r="V24" s="10">
+        <f t="shared" si="132"/>
+        <v>0.10463414634146345</v>
+      </c>
+      <c r="W24" s="10">
+        <f t="shared" ref="W24:AH24" si="133">W13/W3</f>
+        <v>9.9577549788774991E-2</v>
+      </c>
+      <c r="X24" s="10">
         <f t="shared" si="133"/>
-        <v>0.1427579824155483</v>
-      </c>
-      <c r="J24" s="10">
+        <v>0.11096605744125321</v>
+      </c>
+      <c r="Y24" s="10">
         <f t="shared" si="133"/>
-        <v>6.7755886592984121E-2</v>
-      </c>
-      <c r="K24" s="10">
+        <v>0.13906606819434611</v>
+      </c>
+      <c r="Z24" s="10">
         <f t="shared" si="133"/>
-        <v>7.3579633654144772E-2</v>
-      </c>
-      <c r="L24" s="10">
+        <v>4.0516612852827809E-2</v>
+      </c>
+      <c r="AA24" s="10">
         <f t="shared" si="133"/>
-        <v>9.4622759483118032E-2</v>
-      </c>
-      <c r="M24" s="10">
+        <v>8.0451513596716248E-2</v>
+      </c>
+      <c r="AB24" s="10">
         <f t="shared" si="133"/>
-        <v>0.14268306192533517</v>
-      </c>
-      <c r="N24" s="10">
+        <v>0.148155156102176</v>
+      </c>
+      <c r="AC24" s="10">
         <f t="shared" si="133"/>
-        <v>4.5121263395375151E-2</v>
-      </c>
-      <c r="O24" s="10">
+        <v>0.17674233373158107</v>
+      </c>
+      <c r="AD24" s="10">
         <f t="shared" si="133"/>
-        <v>0.10556888496022225</v>
-      </c>
-      <c r="P24" s="10">
+        <v>0.128719723183391</v>
+      </c>
+      <c r="AE24" s="10">
         <f t="shared" si="133"/>
-        <v>0.25580655424753423</v>
-      </c>
-      <c r="Q24" s="10">
+        <v>0.14105862892850585</v>
+      </c>
+      <c r="AF24" s="10">
         <f t="shared" si="133"/>
-        <v>0.26875787200863671</v>
-      </c>
-      <c r="R24" s="10">
+        <v>0.14408602150537636</v>
+      </c>
+      <c r="AG24" s="10">
         <f t="shared" si="133"/>
-        <v>0.19213490461618599</v>
-      </c>
-      <c r="S24" s="10">
+        <v>0.17503543982690437</v>
+      </c>
+      <c r="AH24" s="10">
         <f t="shared" si="133"/>
-        <v>0.15486624495084209</v>
-      </c>
-      <c r="T24" s="10">
-        <f t="shared" si="133"/>
-        <v>0.13733445609737424</v>
-      </c>
-      <c r="U24" s="10">
-        <f t="shared" si="133"/>
-        <v>0.16095051445369915</v>
-      </c>
-      <c r="V24" s="10">
-        <f t="shared" si="133"/>
-        <v>0.10463414634146345</v>
-      </c>
-      <c r="W24" s="10">
-        <f t="shared" ref="W24:AH24" si="134">W13/W3</f>
-        <v>9.9577549788774991E-2</v>
-      </c>
-      <c r="X24" s="10">
+        <v>0.1049089469517023</v>
+      </c>
+      <c r="AI24" s="10">
+        <f t="shared" ref="AI24:AL24" si="134">AI13/AI3</f>
+        <v>0.14132613052191342</v>
+      </c>
+      <c r="AJ24" s="10">
         <f t="shared" si="134"/>
-        <v>0.11096605744125321</v>
-      </c>
-      <c r="Y24" s="10">
+        <v>0.16136919315403417</v>
+      </c>
+      <c r="AK24" s="10">
         <f t="shared" si="134"/>
-        <v>0.13906606819434611</v>
-      </c>
-      <c r="Z24" s="10">
+        <v>0.20112557157931768</v>
+      </c>
+      <c r="AL24" s="10">
         <f t="shared" si="134"/>
-        <v>4.0516612852827809E-2</v>
-      </c>
-      <c r="AA24" s="10">
-        <f t="shared" si="134"/>
-        <v>8.0451513596716248E-2</v>
-      </c>
-      <c r="AB24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.148155156102176</v>
-      </c>
-      <c r="AC24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.17674233373158107</v>
-      </c>
-      <c r="AD24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.128719723183391</v>
-      </c>
-      <c r="AE24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.14105862892850585</v>
-      </c>
-      <c r="AF24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.14408602150537636</v>
-      </c>
-      <c r="AG24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.17503543982690437</v>
-      </c>
-      <c r="AH24" s="10">
-        <f t="shared" si="134"/>
-        <v>0.1049089469517023</v>
-      </c>
-      <c r="AI24" s="10">
-        <f t="shared" ref="AI24:AL24" si="135">AI13/AI3</f>
-        <v>0.14132613052191342</v>
-      </c>
-      <c r="AJ24" s="10">
+        <v>0.1182594974529049</v>
+      </c>
+      <c r="AO24" s="10">
+        <f t="shared" ref="AO24:BC24" si="135">AO13/AO3</f>
+        <v>8.9371980676328663E-2</v>
+      </c>
+      <c r="AP24" s="10">
         <f t="shared" si="135"/>
-        <v>0.16136919315403417</v>
-      </c>
-      <c r="AK24" s="10">
+        <v>9.4394433884445766E-2</v>
+      </c>
+      <c r="AQ24" s="10">
         <f t="shared" si="135"/>
-        <v>0.19829203127942216</v>
-      </c>
-      <c r="AL24" s="10">
+        <v>9.2277706835136891E-2</v>
+      </c>
+      <c r="AR24" s="10">
         <f t="shared" si="135"/>
-        <v>0.11476779950057862</v>
-      </c>
-      <c r="AO24" s="10">
-        <f t="shared" ref="AO24:BC24" si="136">AO13/AO3</f>
-        <v>8.9371980676328663E-2</v>
-      </c>
-      <c r="AP24" s="10">
+        <v>0.21864706890314706</v>
+      </c>
+      <c r="AS24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.14162957016711669</v>
+      </c>
+      <c r="AT24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.10101566458833657</v>
+      </c>
+      <c r="AU24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.13658252878911256</v>
+      </c>
+      <c r="AV24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.14377922676677862</v>
+      </c>
+      <c r="AW24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.15874581979991392</v>
+      </c>
+      <c r="AX24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.16789056807560435</v>
+      </c>
+      <c r="AY24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.16795386452462505</v>
+      </c>
+      <c r="AZ24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.16798520247242441</v>
+      </c>
+      <c r="BA24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.16801623318544159</v>
+      </c>
+      <c r="BB24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.16804695967578206</v>
+      </c>
+      <c r="BC24" s="10">
+        <f t="shared" si="135"/>
+        <v>0.16807738492602109</v>
+      </c>
+      <c r="BD24" s="10">
+        <f t="shared" ref="BD24:BF24" si="136">BD13/BD3</f>
+        <v>0.16810751188949313</v>
+      </c>
+      <c r="BE24" s="10">
         <f t="shared" si="136"/>
-        <v>9.4394433884445766E-2</v>
-      </c>
-      <c r="AQ24" s="10">
+        <v>0.16813734349057816</v>
+      </c>
+      <c r="BF24" s="10">
         <f t="shared" si="136"/>
-        <v>9.2277706835136891E-2</v>
-      </c>
-      <c r="AR24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.21864706890314706</v>
-      </c>
-      <c r="AS24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.14162957016711669</v>
-      </c>
-      <c r="AT24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.10101566458833657</v>
-      </c>
-      <c r="AU24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.13658252878911256</v>
-      </c>
-      <c r="AV24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.14377922676677862</v>
-      </c>
-      <c r="AW24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.15719324631343817</v>
-      </c>
-      <c r="AX24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.17563979651819503</v>
-      </c>
-      <c r="AY24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.17571338534107528</v>
-      </c>
-      <c r="AZ24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.17574981902299133</v>
-      </c>
-      <c r="BA24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.17578589551194765</v>
-      </c>
-      <c r="BB24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.17582161830983567</v>
-      </c>
-      <c r="BC24" s="10">
-        <f t="shared" si="136"/>
-        <v>0.17585699088421489</v>
-      </c>
-      <c r="BD24" s="10">
-        <f t="shared" ref="BD24:BF24" si="137">BD13/BD3</f>
-        <v>0.17589201666864934</v>
-      </c>
-      <c r="BE24" s="10">
-        <f t="shared" si="137"/>
-        <v>0.17592669906304031</v>
-      </c>
-      <c r="BF24" s="10">
-        <f t="shared" si="137"/>
-        <v>0.17596104143395683</v>
+        <v>0.16816688262498591</v>
       </c>
       <c r="BH24" t="s">
         <v>55</v>
@@ -5857,19 +5851,19 @@
         <v>51</v>
       </c>
       <c r="C25" s="10">
-        <f t="shared" ref="C25:F25" si="138">C6/C3</f>
+        <f t="shared" ref="C25:F25" si="137">C6/C3</f>
         <v>0.19324400830345351</v>
       </c>
       <c r="D25" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.16980237154150199</v>
       </c>
       <c r="E25" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.14310344827586208</v>
       </c>
       <c r="F25" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>0.1850101282916948</v>
       </c>
       <c r="G25" s="10">
@@ -5877,206 +5871,206 @@
         <v>0.18833196384552175</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" ref="H25:V25" si="139">H6/H3</f>
+        <f t="shared" ref="H25:V25" si="138">H6/H3</f>
         <v>0.17624077557517001</v>
       </c>
       <c r="I25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.15305414160111061</v>
+      </c>
+      <c r="J25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.19157456351113247</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.19093449239366656</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.18646658329859661</v>
+      </c>
+      <c r="M25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.14955134596211364</v>
+      </c>
+      <c r="N25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.19909757473209247</v>
+      </c>
+      <c r="O25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.16820305594140672</v>
+      </c>
+      <c r="P25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.12631244034362074</v>
+      </c>
+      <c r="Q25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.12265339171114976</v>
+      </c>
+      <c r="R25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.17826681424571911</v>
+      </c>
+      <c r="S25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.19228717323374744</v>
+      </c>
+      <c r="T25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.19643267243359108</v>
+      </c>
+      <c r="U25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.16529887310142086</v>
+      </c>
+      <c r="V25" s="10">
+        <f t="shared" si="138"/>
+        <v>0.20081300813008129</v>
+      </c>
+      <c r="W25" s="10">
+        <f t="shared" ref="W25:AH25" si="139">W6/W3</f>
+        <v>0.19777567031640658</v>
+      </c>
+      <c r="X25" s="10">
         <f t="shared" si="139"/>
-        <v>0.15305414160111061</v>
-      </c>
-      <c r="J25" s="10">
+        <v>0.17589208006962576</v>
+      </c>
+      <c r="Y25" s="10">
         <f t="shared" si="139"/>
-        <v>0.19157456351113247</v>
-      </c>
-      <c r="K25" s="10">
+        <v>0.1548940861485156</v>
+      </c>
+      <c r="Z25" s="10">
         <f t="shared" si="139"/>
-        <v>0.19093449239366656</v>
-      </c>
-      <c r="L25" s="10">
+        <v>0.18862618477241952</v>
+      </c>
+      <c r="AA25" s="10">
         <f t="shared" si="139"/>
-        <v>0.18646658329859661</v>
-      </c>
-      <c r="M25" s="10">
+        <v>0.18388917393535145</v>
+      </c>
+      <c r="AB25" s="10">
         <f t="shared" si="139"/>
-        <v>0.14955134596211364</v>
-      </c>
-      <c r="N25" s="10">
+        <v>0.16688741721854305</v>
+      </c>
+      <c r="AC25" s="10">
         <f t="shared" si="139"/>
-        <v>0.19909757473209247</v>
-      </c>
-      <c r="O25" s="10">
+        <v>0.15069693349263241</v>
+      </c>
+      <c r="AD25" s="10">
         <f t="shared" si="139"/>
-        <v>0.16820305594140672</v>
-      </c>
-      <c r="P25" s="10">
+        <v>0.18348986653484922</v>
+      </c>
+      <c r="AE25" s="10">
         <f t="shared" si="139"/>
-        <v>0.12631244034362074</v>
-      </c>
-      <c r="Q25" s="10">
+        <v>0.18094100349200515</v>
+      </c>
+      <c r="AF25" s="10">
         <f t="shared" si="139"/>
-        <v>0.12265339171114976</v>
-      </c>
-      <c r="R25" s="10">
+        <v>0.18091397849462365</v>
+      </c>
+      <c r="AG25" s="10">
         <f t="shared" si="139"/>
-        <v>0.17826681424571911</v>
-      </c>
-      <c r="S25" s="10">
+        <v>0.16190405133179139</v>
+      </c>
+      <c r="AH25" s="10">
         <f t="shared" si="139"/>
-        <v>0.19228717323374744</v>
-      </c>
-      <c r="T25" s="10">
-        <f t="shared" si="139"/>
-        <v>0.19643267243359108</v>
-      </c>
-      <c r="U25" s="10">
-        <f t="shared" si="139"/>
-        <v>0.16529887310142086</v>
-      </c>
-      <c r="V25" s="10">
-        <f t="shared" si="139"/>
-        <v>0.20081300813008129</v>
-      </c>
-      <c r="W25" s="10">
-        <f t="shared" ref="W25:AH25" si="140">W6/W3</f>
-        <v>0.19777567031640658</v>
-      </c>
-      <c r="X25" s="10">
+        <v>0.19655581947743467</v>
+      </c>
+      <c r="AI25" s="10">
+        <f t="shared" ref="AI25:AL25" si="140">AI6/AI3</f>
+        <v>0.17060207371264269</v>
+      </c>
+      <c r="AJ25" s="10">
         <f t="shared" si="140"/>
-        <v>0.17589208006962576</v>
-      </c>
-      <c r="Y25" s="10">
+        <v>0.16777674732315995</v>
+      </c>
+      <c r="AK25" s="10">
         <f t="shared" si="140"/>
-        <v>0.1548940861485156</v>
-      </c>
-      <c r="Z25" s="10">
+        <v>0.14555047485051004</v>
+      </c>
+      <c r="AL25" s="10">
         <f t="shared" si="140"/>
-        <v>0.18862618477241952</v>
-      </c>
-      <c r="AA25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.18388917393535145</v>
-      </c>
-      <c r="AB25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.16688741721854305</v>
-      </c>
-      <c r="AC25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.15069693349263241</v>
-      </c>
-      <c r="AD25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.18348986653484922</v>
-      </c>
-      <c r="AE25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.18094100349200515</v>
-      </c>
-      <c r="AF25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.18091397849462365</v>
-      </c>
-      <c r="AG25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.16190405133179139</v>
-      </c>
-      <c r="AH25" s="10">
-        <f t="shared" si="140"/>
-        <v>0.19655581947743467</v>
-      </c>
-      <c r="AI25" s="10">
-        <f t="shared" ref="AI25:AL25" si="141">AI6/AI3</f>
-        <v>0.17060207371264269</v>
-      </c>
-      <c r="AJ25" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="AO25" s="10">
+        <f t="shared" ref="AO25:BC25" si="141">AO6/AO3</f>
+        <v>0.1697054698457223</v>
+      </c>
+      <c r="AP25" s="10">
         <f t="shared" si="141"/>
-        <v>0.16777674732315995</v>
-      </c>
-      <c r="AK25" s="10">
+        <v>0.17512462790947886</v>
+      </c>
+      <c r="AQ25" s="10">
         <f t="shared" si="141"/>
-        <v>0.15</v>
-      </c>
-      <c r="AL25" s="10">
+        <v>0.17924591706431883</v>
+      </c>
+      <c r="AR25" s="10">
         <f t="shared" si="141"/>
-        <v>0.19</v>
-      </c>
-      <c r="AO25" s="10">
-        <f t="shared" ref="AO25:BC25" si="142">AO6/AO3</f>
-        <v>0.1697054698457223</v>
-      </c>
-      <c r="AP25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.17512462790947886</v>
-      </c>
-      <c r="AQ25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.17924591706431883</v>
-      </c>
-      <c r="AR25" s="10">
-        <f t="shared" si="142"/>
         <v>0.14665955866953526</v>
       </c>
       <c r="AS25" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>0.187148799532949</v>
       </c>
       <c r="AT25" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>0.17830311308907443</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>0.16991973944399208</v>
       </c>
       <c r="AV25" s="10">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>0.17879646095413732</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.16810598691842596</v>
+        <f t="shared" si="141"/>
+        <v>0.16683392163476801</v>
       </c>
       <c r="AX25" s="10">
+        <f t="shared" si="141"/>
+        <v>0.16</v>
+      </c>
+      <c r="AY25" s="10">
+        <f t="shared" si="141"/>
+        <v>0.16</v>
+      </c>
+      <c r="AZ25" s="10">
+        <f t="shared" si="141"/>
+        <v>0.16</v>
+      </c>
+      <c r="BA25" s="10">
+        <f t="shared" si="141"/>
+        <v>0.16</v>
+      </c>
+      <c r="BB25" s="10">
+        <f t="shared" si="141"/>
+        <v>0.16</v>
+      </c>
+      <c r="BC25" s="10">
+        <f t="shared" si="141"/>
+        <v>0.16</v>
+      </c>
+      <c r="BD25" s="10">
+        <f t="shared" ref="BD25:BF25" si="142">BD6/BD3</f>
+        <v>0.16</v>
+      </c>
+      <c r="BE25" s="10">
         <f t="shared" si="142"/>
         <v>0.16</v>
       </c>
-      <c r="AY25" s="10">
+      <c r="BF25" s="10">
         <f t="shared" si="142"/>
         <v>0.16</v>
       </c>
-      <c r="AZ25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.16</v>
-      </c>
-      <c r="BA25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.16</v>
-      </c>
-      <c r="BB25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.16</v>
-      </c>
-      <c r="BC25" s="10">
-        <f t="shared" si="142"/>
-        <v>0.16</v>
-      </c>
-      <c r="BD25" s="10">
-        <f t="shared" ref="BD25:BF25" si="143">BD6/BD3</f>
-        <v>0.16</v>
-      </c>
-      <c r="BE25" s="10">
-        <f t="shared" si="143"/>
-        <v>0.16</v>
-      </c>
-      <c r="BF25" s="10">
-        <f t="shared" si="143"/>
-        <v>0.16</v>
-      </c>
       <c r="BH25" t="s">
         <v>56</v>
       </c>
       <c r="BI25" s="10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="26" spans="2:168" x14ac:dyDescent="0.3">
@@ -6088,200 +6082,200 @@
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10">
-        <f t="shared" ref="G26:G27" si="144">G7/C7-1</f>
+        <f t="shared" ref="G26:G27" si="143">G7/C7-1</f>
         <v>0.11111111111111116</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" ref="H26:H27" si="145">H7/D7-1</f>
+        <f t="shared" ref="H26:H27" si="144">H7/D7-1</f>
         <v>7.9234972677595605E-2</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" ref="I26:I27" si="146">I7/E7-1</f>
+        <f t="shared" ref="I26:I27" si="145">I7/E7-1</f>
         <v>0.18023255813953498</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" ref="J26:J27" si="147">J7/F7-1</f>
+        <f t="shared" ref="J26:J27" si="146">J7/F7-1</f>
         <v>0.11968085106382986</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" ref="K26:K27" si="148">K7/G7-1</f>
+        <f t="shared" ref="K26:K27" si="147">K7/G7-1</f>
         <v>8.2051282051282204E-2</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" ref="L26:L27" si="149">L7/H7-1</f>
+        <f t="shared" ref="L26:L27" si="148">L7/H7-1</f>
         <v>6.3291139240506222E-2</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" ref="M26:M27" si="150">M7/I7-1</f>
+        <f t="shared" ref="M26:M27" si="149">M7/I7-1</f>
         <v>6.6502463054187055E-2</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" ref="N26:N27" si="151">N7/J7-1</f>
+        <f t="shared" ref="N26:N27" si="150">N7/J7-1</f>
         <v>0.19002375296912111</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" ref="O26:O27" si="152">O7/K7-1</f>
+        <f t="shared" ref="O26:O27" si="151">O7/K7-1</f>
         <v>0.17772511848341233</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" ref="P26:P27" si="153">P7/L7-1</f>
+        <f t="shared" ref="P26:P27" si="152">P7/L7-1</f>
         <v>0.27142857142857135</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" ref="Q26:Q27" si="154">Q7/M7-1</f>
+        <f t="shared" ref="Q26:Q27" si="153">Q7/M7-1</f>
         <v>0.24480369515011557</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" ref="R26:R27" si="155">R7/N7-1</f>
+        <f t="shared" ref="R26:R27" si="154">R7/N7-1</f>
         <v>0.3772455089820359</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" ref="S26:S27" si="156">S7/O7-1</f>
+        <f t="shared" ref="S26:S27" si="155">S7/O7-1</f>
         <v>0.39235412474849096</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" ref="T26:T27" si="157">T7/P7-1</f>
+        <f t="shared" ref="T26:T27" si="156">T7/P7-1</f>
         <v>0.28651685393258441</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" ref="U26:U27" si="158">U7/Q7-1</f>
+        <f t="shared" ref="U26:U27" si="157">U7/Q7-1</f>
         <v>0.40074211502782942</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" ref="V26:V27" si="159">V7/R7-1</f>
+        <f t="shared" ref="V26:V27" si="158">V7/R7-1</f>
         <v>0.13623188405797104</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" ref="W26:W27" si="160">W7/S7-1</f>
+        <f t="shared" ref="W26:W27" si="159">W7/S7-1</f>
         <v>9.1040462427745661E-2</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" ref="X26:X27" si="161">X7/T7-1</f>
+        <f t="shared" ref="X26:X27" si="160">X7/T7-1</f>
         <v>4.366812227074135E-3</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" ref="Y26:Y27" si="162">Y7/U7-1</f>
+        <f t="shared" ref="Y26:Y27" si="161">Y7/U7-1</f>
         <v>-0.13112582781456961</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" ref="Z26:Z27" si="163">Z7/V7-1</f>
+        <f t="shared" ref="Z26:Z27" si="162">Z7/V7-1</f>
         <v>-9.9489795918367485E-2</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" ref="AA26:AA27" si="164">AA7/W7-1</f>
+        <f t="shared" ref="AA26:AA27" si="163">AA7/W7-1</f>
         <v>-6.4900662251655694E-2</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" ref="AB26:AB27" si="165">AB7/X7-1</f>
+        <f t="shared" ref="AB26:AB27" si="164">AB7/X7-1</f>
         <v>-5.7971014492754769E-3</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" ref="AC26:AC27" si="166">AC7/Y7-1</f>
+        <f t="shared" ref="AC26:AC27" si="165">AC7/Y7-1</f>
         <v>0.10823170731707332</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" ref="AD26:AD27" si="167">AD7/Z7-1</f>
+        <f t="shared" ref="AD26:AD27" si="166">AD7/Z7-1</f>
         <v>6.7988668555240883E-2</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" ref="AE26:AE27" si="168">AE7/AA7-1</f>
+        <f t="shared" ref="AE26:AE27" si="167">AE7/AA7-1</f>
         <v>6.6572237960339953E-2</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" ref="AF26:AF27" si="169">AF7/AB7-1</f>
+        <f t="shared" ref="AF26:AF27" si="168">AF7/AB7-1</f>
         <v>0.11078717201166199</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" ref="AG26:AG27" si="170">AG7/AC7-1</f>
+        <f t="shared" ref="AG26:AG27" si="169">AG7/AC7-1</f>
         <v>7.2902338376891196E-2</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" ref="AH26:AH27" si="171">AH7/AD7-1</f>
+        <f t="shared" ref="AH26:AH27" si="170">AH7/AD7-1</f>
         <v>5.4376657824933616E-2</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" ref="AI26:AI27" si="172">AI7/AE7-1</f>
+        <f t="shared" ref="AI26:AI27" si="171">AI7/AE7-1</f>
         <v>-9.2961487383798058E-3</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" ref="AJ26:AJ27" si="173">AJ7/AF7-1</f>
+        <f t="shared" ref="AJ26:AJ27" si="172">AJ7/AF7-1</f>
         <v>-1.312335958005395E-3</v>
       </c>
       <c r="AK26" s="10">
-        <f t="shared" ref="AK26:AK27" si="174">AK7/AG7-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AK26:AK27" si="173">AK7/AG7-1</f>
+        <v>6.4102564102563875E-3</v>
       </c>
       <c r="AL26" s="10">
-        <f t="shared" ref="AL26:AL27" si="175">AL7/AH7-1</f>
+        <f t="shared" ref="AL26:AL27" si="174">AL7/AH7-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AO26" s="10"/>
       <c r="AP26" s="10">
-        <f t="shared" ref="AP26:BC26" si="176">AP7/AO7-1</f>
+        <f t="shared" ref="AP26:BC26" si="175">AP7/AO7-1</f>
         <v>0.12178148921363952</v>
       </c>
       <c r="AQ26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>0.1017369727047146</v>
       </c>
       <c r="AR26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>0.27252252252252251</v>
       </c>
       <c r="AS26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>0.29115044247787614</v>
       </c>
       <c r="AT26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>-3.8039753255654674E-2</v>
       </c>
       <c r="AU26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>2.3512646954043426E-2</v>
       </c>
       <c r="AV26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>7.5530804037591492E-2</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="176"/>
-        <v>2.0372168284789716E-2</v>
+        <f t="shared" si="175"/>
+        <v>1.1893203883495129E-2</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AY26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC26" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="175"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD26" s="10">
-        <f t="shared" ref="BD26:BD27" si="177">BD7/BC7-1</f>
+        <f t="shared" ref="BD26:BD27" si="176">BD7/BC7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE26" s="10">
-        <f t="shared" ref="BE26:BE27" si="178">BE7/BD7-1</f>
+        <f t="shared" ref="BE26:BE27" si="177">BE7/BD7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF26" s="10">
-        <f t="shared" ref="BF26:BF27" si="179">BF7/BE7-1</f>
+        <f t="shared" ref="BF26:BF27" si="178">BF7/BE7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BH26" t="s">
@@ -6289,7 +6283,7 @@
       </c>
       <c r="BI26" s="6">
         <f>NPV(BI25,AW18:FL18)</f>
-        <v>10046.245389773256</v>
+        <v>8665.8143208036399</v>
       </c>
     </row>
     <row r="27" spans="2:168" x14ac:dyDescent="0.3">
@@ -6301,208 +6295,208 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10">
+        <f t="shared" si="143"/>
+        <v>3.937007874015741E-3</v>
+      </c>
+      <c r="H27" s="10">
         <f t="shared" si="144"/>
-        <v>3.937007874015741E-3</v>
-      </c>
-      <c r="H27" s="10">
+        <v>-3.9525691699605625E-3</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="145"/>
-        <v>-3.9525691699605625E-3</v>
-      </c>
-      <c r="I27" s="10">
+        <v>9.8654708520179435E-2</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="146"/>
-        <v>9.8654708520179435E-2</v>
-      </c>
-      <c r="J27" s="10">
+        <v>8.5470085470087387E-3</v>
+      </c>
+      <c r="K27" s="10">
         <f t="shared" si="147"/>
-        <v>8.5470085470087387E-3</v>
-      </c>
-      <c r="K27" s="10">
+        <v>-0.12941176470588234</v>
+      </c>
+      <c r="L27" s="10">
         <f t="shared" si="148"/>
-        <v>-0.12941176470588234</v>
-      </c>
-      <c r="L27" s="10">
+        <v>-4.7619047619047561E-2</v>
+      </c>
+      <c r="M27" s="10">
         <f t="shared" si="149"/>
-        <v>-4.7619047619047561E-2</v>
-      </c>
-      <c r="M27" s="10">
+        <v>-8.9795918367346905E-2</v>
+      </c>
+      <c r="N27" s="10">
         <f t="shared" si="150"/>
-        <v>-8.9795918367346905E-2</v>
-      </c>
-      <c r="N27" s="10">
+        <v>8.0508474576271194E-2</v>
+      </c>
+      <c r="O27" s="10">
         <f t="shared" si="151"/>
-        <v>8.0508474576271194E-2</v>
-      </c>
-      <c r="O27" s="10">
+        <v>0.31081081081081097</v>
+      </c>
+      <c r="P27" s="10">
         <f t="shared" si="152"/>
-        <v>0.31081081081081097</v>
-      </c>
-      <c r="P27" s="10">
+        <v>0.3208333333333333</v>
+      </c>
+      <c r="Q27" s="10">
         <f t="shared" si="153"/>
-        <v>0.3208333333333333</v>
-      </c>
-      <c r="Q27" s="10">
+        <v>0.68609865470852016</v>
+      </c>
+      <c r="R27" s="10">
         <f t="shared" si="154"/>
-        <v>0.68609865470852016</v>
-      </c>
-      <c r="R27" s="10">
+        <v>1.6745098039215689</v>
+      </c>
+      <c r="S27" s="10">
         <f t="shared" si="155"/>
-        <v>1.6745098039215689</v>
-      </c>
-      <c r="S27" s="10">
+        <v>0.39175257731958757</v>
+      </c>
+      <c r="T27" s="10">
         <f t="shared" si="156"/>
-        <v>0.39175257731958757</v>
-      </c>
-      <c r="T27" s="10">
+        <v>5.0473186119873725E-2</v>
+      </c>
+      <c r="U27" s="10">
         <f t="shared" si="157"/>
-        <v>5.0473186119873725E-2</v>
-      </c>
-      <c r="U27" s="10">
+        <v>2.3936170212765839E-2</v>
+      </c>
+      <c r="V27" s="10">
         <f t="shared" si="158"/>
-        <v>2.3936170212765839E-2</v>
-      </c>
-      <c r="V27" s="10">
+        <v>-0.46627565982404695</v>
+      </c>
+      <c r="W27" s="10">
         <f t="shared" si="159"/>
-        <v>-0.46627565982404695</v>
-      </c>
-      <c r="W27" s="10">
+        <v>-0.11358024691358026</v>
+      </c>
+      <c r="X27" s="10">
         <f t="shared" si="160"/>
-        <v>-0.11358024691358026</v>
-      </c>
-      <c r="X27" s="10">
+        <v>-0.20120120120120111</v>
+      </c>
+      <c r="Y27" s="10">
         <f t="shared" si="161"/>
-        <v>-0.20120120120120111</v>
-      </c>
-      <c r="Y27" s="10">
+        <v>-0.22597402597402594</v>
+      </c>
+      <c r="Z27" s="10">
         <f t="shared" si="162"/>
-        <v>-0.22597402597402594</v>
-      </c>
-      <c r="Z27" s="10">
+        <v>-0.10989010989010994</v>
+      </c>
+      <c r="AA27" s="10">
         <f t="shared" si="163"/>
-        <v>-0.10989010989010994</v>
-      </c>
-      <c r="AA27" s="10">
+        <v>0.15041782729805009</v>
+      </c>
+      <c r="AB27" s="10">
         <f t="shared" si="164"/>
-        <v>0.15041782729805009</v>
-      </c>
-      <c r="AB27" s="10">
+        <v>0.33458646616541343</v>
+      </c>
+      <c r="AC27" s="10">
         <f t="shared" si="165"/>
-        <v>0.33458646616541343</v>
-      </c>
-      <c r="AC27" s="10">
+        <v>0.33221476510067127</v>
+      </c>
+      <c r="AD27" s="10">
         <f t="shared" si="166"/>
-        <v>0.33221476510067127</v>
-      </c>
-      <c r="AD27" s="10">
+        <v>0.18827160493827155</v>
+      </c>
+      <c r="AE27" s="10">
         <f t="shared" si="167"/>
-        <v>0.18827160493827155</v>
-      </c>
-      <c r="AE27" s="10">
+        <v>-9.2009685230024174E-2</v>
+      </c>
+      <c r="AF27" s="10">
         <f t="shared" si="168"/>
-        <v>-9.2009685230024174E-2</v>
-      </c>
-      <c r="AF27" s="10">
+        <v>0.24507042253521139</v>
+      </c>
+      <c r="AG27" s="10">
         <f t="shared" si="169"/>
-        <v>0.24507042253521139</v>
-      </c>
-      <c r="AG27" s="10">
+        <v>6.0453400503778232E-2</v>
+      </c>
+      <c r="AH27" s="10">
         <f t="shared" si="170"/>
-        <v>6.0453400503778232E-2</v>
-      </c>
-      <c r="AH27" s="10">
+        <v>4.6753246753246769E-2</v>
+      </c>
+      <c r="AI27" s="10">
         <f t="shared" si="171"/>
-        <v>4.6753246753246769E-2</v>
-      </c>
-      <c r="AI27" s="10">
+        <v>0.11466666666666669</v>
+      </c>
+      <c r="AJ27" s="10">
         <f t="shared" si="172"/>
-        <v>0.11466666666666669</v>
-      </c>
-      <c r="AJ27" s="10">
+        <v>-5.4298642533936792E-2</v>
+      </c>
+      <c r="AK27" s="10">
         <f t="shared" si="173"/>
-        <v>-5.4298642533936792E-2</v>
-      </c>
-      <c r="AK27" s="10">
+        <v>-4.7505938242280443E-3</v>
+      </c>
+      <c r="AL27" s="10">
         <f t="shared" si="174"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="175"/>
-        <v>7.0000000000000062E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AO27" s="10"/>
       <c r="AP27" s="10">
-        <f t="shared" ref="AP27:BC27" si="180">AP8/AO8-1</f>
+        <f t="shared" ref="AP27:BC27" si="179">AP8/AO8-1</f>
         <v>2.4896265560166109E-2</v>
       </c>
       <c r="AQ27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>-4.8582995951417129E-2</v>
       </c>
       <c r="AR27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.77234042553191506</v>
       </c>
       <c r="AS27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>-0.10744297719087659</v>
       </c>
       <c r="AT27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>-0.16139878950907871</v>
       </c>
       <c r="AU27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0.24298315958299921</v>
       </c>
       <c r="AV27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>5.8709677419354955E-2</v>
       </c>
       <c r="AW27" s="10">
-        <f t="shared" si="180"/>
-        <v>3.3900060938452103E-2</v>
+        <f t="shared" si="179"/>
+        <v>2.0182815356489803E-2</v>
       </c>
       <c r="AX27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AY27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AZ27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC27" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD27" s="10">
+        <f t="shared" si="176"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BE27" s="10">
         <f t="shared" si="177"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE27" s="10">
+      <c r="BF27" s="10">
         <f t="shared" si="178"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF27" s="10">
-        <f t="shared" si="179"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BH27" t="s">
         <v>58</v>
       </c>
       <c r="BI27" s="6">
         <f>Main!D8</f>
-        <v>1375.8</v>
+        <v>1817.8</v>
       </c>
     </row>
     <row r="28" spans="2:168" x14ac:dyDescent="0.3">
@@ -6510,19 +6504,19 @@
         <v>43</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:F28" si="181">C17/C16</f>
+        <f t="shared" ref="C28:F28" si="180">C17/C16</f>
         <v>-0.17197452229299384</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="180"/>
         <v>6.7768595041322308E-2</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="180"/>
         <v>0.19841269841269848</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="180"/>
         <v>0.12690355329949249</v>
       </c>
       <c r="G28" s="10">
@@ -6530,207 +6524,207 @@
         <v>-0.15662650602409639</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" ref="H28:V28" si="182">H17/H16</f>
+        <f t="shared" ref="H28:V28" si="181">H17/H16</f>
         <v>8.8068181818181809E-2</v>
       </c>
       <c r="I28" s="10">
+        <f t="shared" si="181"/>
+        <v>7.6104746317512309E-2</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" si="181"/>
+        <v>7.2527472527472547E-2</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.12524084778420022</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="181"/>
+        <v>-3.6931818181818149E-2</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.10984848484848481</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="181"/>
+        <v>-2.0542857142857129</v>
+      </c>
+      <c r="O28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.16241299303944318</v>
+      </c>
+      <c r="P28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.17419554455445541</v>
+      </c>
+      <c r="Q28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.1589360298966806</v>
+      </c>
+      <c r="R28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.20500176118351526</v>
+      </c>
+      <c r="S28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.11798017932987265</v>
+      </c>
+      <c r="T28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.19375361480624642</v>
+      </c>
+      <c r="U28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.19005397070161914</v>
+      </c>
+      <c r="V28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.1784358390280941</v>
+      </c>
+      <c r="W28" s="10">
+        <f t="shared" ref="W28:AH28" si="182">W17/W16</f>
+        <v>0.17714285714285696</v>
+      </c>
+      <c r="X28" s="10">
         <f t="shared" si="182"/>
-        <v>7.6104746317512309E-2</v>
-      </c>
-      <c r="J28" s="10">
+        <v>0.2215909090909092</v>
+      </c>
+      <c r="Y28" s="10">
         <f t="shared" si="182"/>
-        <v>7.2527472527472547E-2</v>
-      </c>
-      <c r="K28" s="10">
+        <v>0.23371647509578528</v>
+      </c>
+      <c r="Z28" s="10">
         <f t="shared" si="182"/>
-        <v>0.12524084778420022</v>
-      </c>
-      <c r="L28" s="10">
+        <v>0.21212121212121221</v>
+      </c>
+      <c r="AA28" s="10">
         <f t="shared" si="182"/>
-        <v>-3.6931818181818149E-2</v>
-      </c>
-      <c r="M28" s="10">
+        <v>0.1662234042553192</v>
+      </c>
+      <c r="AB28" s="10">
         <f t="shared" si="182"/>
-        <v>0.10984848484848481</v>
-      </c>
-      <c r="N28" s="10">
+        <v>0.18089552238805967</v>
+      </c>
+      <c r="AC28" s="10">
         <f t="shared" si="182"/>
-        <v>-2.0542857142857129</v>
-      </c>
-      <c r="O28" s="10">
+        <v>-4.0868454661558105E-2</v>
+      </c>
+      <c r="AD28" s="10">
         <f t="shared" si="182"/>
-        <v>0.16241299303944318</v>
-      </c>
-      <c r="P28" s="10">
+        <v>-0.16550764951321281</v>
+      </c>
+      <c r="AE28" s="10">
         <f t="shared" si="182"/>
-        <v>0.17419554455445541</v>
-      </c>
-      <c r="Q28" s="10">
+        <v>0.15292712066905612</v>
+      </c>
+      <c r="AF28" s="10">
         <f t="shared" si="182"/>
-        <v>0.1589360298966806</v>
-      </c>
-      <c r="R28" s="10">
+        <v>0.17396247868106879</v>
+      </c>
+      <c r="AG28" s="10">
         <f t="shared" si="182"/>
-        <v>0.20500176118351526</v>
-      </c>
-      <c r="S28" s="10">
+        <v>0.18385650224215255</v>
+      </c>
+      <c r="AH28" s="10">
         <f t="shared" si="182"/>
-        <v>0.11798017932987265</v>
-      </c>
-      <c r="T28" s="10">
-        <f t="shared" si="182"/>
-        <v>0.19375361480624642</v>
-      </c>
-      <c r="U28" s="10">
-        <f t="shared" si="182"/>
-        <v>0.19005397070161914</v>
-      </c>
-      <c r="V28" s="10">
-        <f t="shared" si="182"/>
-        <v>0.1784358390280941</v>
-      </c>
-      <c r="W28" s="10">
-        <f t="shared" ref="W28:AH28" si="183">W17/W16</f>
-        <v>0.17714285714285696</v>
-      </c>
-      <c r="X28" s="10">
+        <v>-0.21893491124260353</v>
+      </c>
+      <c r="AI28" s="10">
+        <f t="shared" ref="AI28:AL28" si="183">AI17/AI16</f>
+        <v>0.16323024054982815</v>
+      </c>
+      <c r="AJ28" s="10">
         <f t="shared" si="183"/>
-        <v>0.2215909090909092</v>
-      </c>
-      <c r="Y28" s="10">
+        <v>0.15952732644017731</v>
+      </c>
+      <c r="AK28" s="10">
         <f t="shared" si="183"/>
-        <v>0.23371647509578528</v>
-      </c>
-      <c r="Z28" s="10">
+        <v>0.16086956521739124</v>
+      </c>
+      <c r="AL28" s="10">
         <f t="shared" si="183"/>
-        <v>0.21212121212121221</v>
-      </c>
-      <c r="AA28" s="10">
-        <f t="shared" si="183"/>
-        <v>0.1662234042553192</v>
-      </c>
-      <c r="AB28" s="10">
-        <f t="shared" si="183"/>
-        <v>0.18089552238805967</v>
-      </c>
-      <c r="AC28" s="10">
-        <f t="shared" si="183"/>
-        <v>-4.0868454661558105E-2</v>
-      </c>
-      <c r="AD28" s="10">
-        <f t="shared" si="183"/>
-        <v>-0.16550764951321281</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="183"/>
-        <v>0.15292712066905612</v>
-      </c>
-      <c r="AF28" s="10">
-        <f t="shared" si="183"/>
-        <v>0.17396247868106879</v>
-      </c>
-      <c r="AG28" s="10">
-        <f t="shared" si="183"/>
-        <v>0.18385650224215255</v>
-      </c>
-      <c r="AH28" s="10">
-        <f t="shared" si="183"/>
-        <v>-0.21893491124260353</v>
-      </c>
-      <c r="AI28" s="10">
-        <f t="shared" ref="AI28:AL28" si="184">AI17/AI16</f>
-        <v>0.16323024054982815</v>
-      </c>
-      <c r="AJ28" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="AO28" s="10">
+        <f t="shared" ref="AO28:BC28" si="184">AO17/AO16</f>
+        <v>0.10211115898319671</v>
+      </c>
+      <c r="AP28" s="10">
         <f t="shared" si="184"/>
-        <v>0.15952732644017731</v>
-      </c>
-      <c r="AK28" s="10">
+        <v>5.0129008477699938E-2</v>
+      </c>
+      <c r="AQ28" s="10">
+        <f t="shared" si="184"/>
+        <v>-0.38871667699937962</v>
+      </c>
+      <c r="AR28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.1748824246646927</v>
+      </c>
+      <c r="AS28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.16874437732939215</v>
+      </c>
+      <c r="AT28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.21354616048317474</v>
+      </c>
+      <c r="AU28" s="10">
+        <f t="shared" si="184"/>
+        <v>1.5127132281943978E-2</v>
+      </c>
+      <c r="AV28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.10666289432734477</v>
+      </c>
+      <c r="AW28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.16256911095952653</v>
+      </c>
+      <c r="AX28" s="10">
         <f t="shared" si="184"/>
         <v>0.17</v>
       </c>
-      <c r="AL28" s="10">
+      <c r="AY28" s="10">
         <f t="shared" si="184"/>
         <v>0.17</v>
       </c>
-      <c r="AO28" s="10">
-        <f t="shared" ref="AO28:BC28" si="185">AO17/AO16</f>
-        <v>0.10211115898319671</v>
-      </c>
-      <c r="AP28" s="10">
-        <f t="shared" si="185"/>
-        <v>5.0129008477699938E-2</v>
-      </c>
-      <c r="AQ28" s="10">
-        <f t="shared" si="185"/>
-        <v>-0.38871667699937962</v>
-      </c>
-      <c r="AR28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.1748824246646927</v>
-      </c>
-      <c r="AS28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.16874437732939215</v>
-      </c>
-      <c r="AT28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.21354616048317474</v>
-      </c>
-      <c r="AU28" s="10">
-        <f t="shared" si="185"/>
-        <v>1.5127132281943978E-2</v>
-      </c>
-      <c r="AV28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.10666289432734477</v>
-      </c>
-      <c r="AW28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.16585354874513081</v>
-      </c>
-      <c r="AX28" s="10">
+      <c r="AZ28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.17</v>
+      </c>
+      <c r="BA28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.17</v>
+      </c>
+      <c r="BB28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.17</v>
+      </c>
+      <c r="BC28" s="10">
+        <f t="shared" si="184"/>
+        <v>0.17</v>
+      </c>
+      <c r="BD28" s="10">
+        <f t="shared" ref="BD28:BF28" si="185">BD17/BD16</f>
+        <v>0.17</v>
+      </c>
+      <c r="BE28" s="10">
         <f t="shared" si="185"/>
         <v>0.17</v>
       </c>
-      <c r="AY28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.17000000000000004</v>
-      </c>
-      <c r="AZ28" s="10">
+      <c r="BF28" s="10">
         <f t="shared" si="185"/>
         <v>0.17</v>
       </c>
-      <c r="BA28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.17</v>
-      </c>
-      <c r="BB28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.17</v>
-      </c>
-      <c r="BC28" s="10">
-        <f t="shared" si="185"/>
-        <v>0.17</v>
-      </c>
-      <c r="BD28" s="10">
-        <f t="shared" ref="BD28:BF28" si="186">BD17/BD16</f>
-        <v>0.17</v>
-      </c>
-      <c r="BE28" s="10">
-        <f t="shared" si="186"/>
-        <v>0.17</v>
-      </c>
-      <c r="BF28" s="10">
-        <f t="shared" si="186"/>
-        <v>0.17</v>
-      </c>
       <c r="BH28" t="s">
         <v>59</v>
       </c>
       <c r="BI28" s="6">
         <f>BI26+BI27</f>
-        <v>11422.045389773255</v>
+        <v>10483.614320803639</v>
       </c>
     </row>
     <row r="29" spans="2:168" x14ac:dyDescent="0.3">
@@ -6738,19 +6732,19 @@
         <v>54</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:F29" si="187">C18/C3</f>
+        <f t="shared" ref="C29:F29" si="186">C18/C3</f>
         <v>6.9447065484053522E-2</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="186"/>
         <v>8.9169960474308294E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="186"/>
         <v>9.9507389162561535E-2</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="186"/>
         <v>5.8068872383524595E-2</v>
       </c>
       <c r="G29" s="10">
@@ -6758,207 +6752,207 @@
         <v>6.3105998356614637E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:V29" si="188">H18/H3</f>
+        <f t="shared" ref="H29:V29" si="187">H18/H3</f>
         <v>9.2895384170163506E-2</v>
       </c>
       <c r="I29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.13061082832022206</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="187"/>
+        <v>6.7595707192055085E-2</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="187"/>
+        <v>7.0475007761564817E-2</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.10143115186883431</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.13016506037443232</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.30146644106034975</v>
+      </c>
+      <c r="O29" s="10">
+        <f t="shared" si="187"/>
+        <v>9.1173127920191929E-2</v>
+      </c>
+      <c r="P29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.21229716831053136</v>
+      </c>
+      <c r="Q29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.22947280033587236</v>
+      </c>
+      <c r="R29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.14694967120255231</v>
+      </c>
+      <c r="S29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.14244341132535623</v>
+      </c>
+      <c r="T29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.10671361861746917</v>
+      </c>
+      <c r="U29" s="10">
+        <f t="shared" si="187"/>
+        <v>0.12867466927976481</v>
+      </c>
+      <c r="V29" s="10">
+        <f t="shared" si="187"/>
+        <v>8.7967479674796789E-2</v>
+      </c>
+      <c r="W29" s="10">
+        <f t="shared" ref="W29:AH29" si="188">W18/W3</f>
+        <v>8.6904043452021809E-2</v>
+      </c>
+      <c r="X29" s="10">
         <f t="shared" si="188"/>
-        <v>0.13061082832022206</v>
-      </c>
-      <c r="J29" s="10">
+        <v>7.1540469973890283E-2</v>
+      </c>
+      <c r="Y29" s="10">
         <f t="shared" si="188"/>
-        <v>6.7595707192055085E-2</v>
-      </c>
-      <c r="K29" s="10">
+        <v>0.11024490117332082</v>
+      </c>
+      <c r="Z29" s="10">
         <f t="shared" si="188"/>
-        <v>7.0475007761564817E-2</v>
-      </c>
-      <c r="L29" s="10">
+        <v>4.3328819914592205E-2</v>
+      </c>
+      <c r="AA29" s="10">
         <f t="shared" si="188"/>
-        <v>0.10143115186883431</v>
-      </c>
-      <c r="M29" s="10">
+        <v>6.4340687532067703E-2</v>
+      </c>
+      <c r="AB29" s="10">
         <f t="shared" si="188"/>
-        <v>0.13016506037443232</v>
-      </c>
-      <c r="N29" s="10">
+        <v>0.12980132450331128</v>
+      </c>
+      <c r="AC29" s="10">
         <f t="shared" si="188"/>
-        <v>0.30146644106034975</v>
-      </c>
-      <c r="O29" s="10">
+        <v>0.19474313022700121</v>
+      </c>
+      <c r="AD29" s="10">
         <f t="shared" si="188"/>
-        <v>9.1173127920191929E-2</v>
-      </c>
-      <c r="P29" s="10">
+        <v>0.16569451309935737</v>
+      </c>
+      <c r="AE29" s="10">
         <f t="shared" si="188"/>
-        <v>0.21229716831053136</v>
-      </c>
-      <c r="Q29" s="10">
+        <v>0.13030692887336892</v>
+      </c>
+      <c r="AF29" s="10">
         <f t="shared" si="188"/>
-        <v>0.22947280033587236</v>
-      </c>
-      <c r="R29" s="10">
+        <v>0.13019713261648747</v>
+      </c>
+      <c r="AG29" s="10">
         <f t="shared" si="188"/>
-        <v>0.14694967120255231</v>
-      </c>
-      <c r="S29" s="10">
+        <v>0.1493695441319107</v>
+      </c>
+      <c r="AH29" s="10">
         <f t="shared" si="188"/>
-        <v>0.14244341132535623</v>
-      </c>
-      <c r="T29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.10671361861746917</v>
-      </c>
-      <c r="U29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.12867466927976481</v>
-      </c>
-      <c r="V29" s="10">
-        <f t="shared" si="188"/>
-        <v>8.7967479674796789E-2</v>
-      </c>
-      <c r="W29" s="10">
-        <f t="shared" ref="W29:AH29" si="189">W18/W3</f>
-        <v>8.6904043452021809E-2</v>
-      </c>
-      <c r="X29" s="10">
+        <v>0.1427157561361837</v>
+      </c>
+      <c r="AI29" s="10">
+        <f t="shared" ref="AI29:AL29" si="189">AI18/AI3</f>
+        <v>0.12729807440968896</v>
+      </c>
+      <c r="AJ29" s="10">
         <f t="shared" si="189"/>
-        <v>7.1540469973890283E-2</v>
-      </c>
-      <c r="Y29" s="10">
+        <v>0.14391703903549444</v>
+      </c>
+      <c r="AK29" s="10">
         <f t="shared" si="189"/>
-        <v>0.11024490117332082</v>
-      </c>
-      <c r="Z29" s="10">
+        <v>0.17650369328174473</v>
+      </c>
+      <c r="AL29" s="10">
         <f t="shared" si="189"/>
-        <v>4.3328819914592205E-2</v>
-      </c>
-      <c r="AA29" s="10">
-        <f t="shared" si="189"/>
-        <v>6.4340687532067703E-2</v>
-      </c>
-      <c r="AB29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.12980132450331128</v>
-      </c>
-      <c r="AC29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.19474313022700121</v>
-      </c>
-      <c r="AD29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.16569451309935737</v>
-      </c>
-      <c r="AE29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.13030692887336892</v>
-      </c>
-      <c r="AF29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.13019713261648747</v>
-      </c>
-      <c r="AG29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.1493695441319107</v>
-      </c>
-      <c r="AH29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.1427157561361837</v>
-      </c>
-      <c r="AI29" s="10">
-        <f t="shared" ref="AI29:AL29" si="190">AI18/AI3</f>
-        <v>0.12729807440968896</v>
-      </c>
-      <c r="AJ29" s="10">
+        <v>0.10538575307369398</v>
+      </c>
+      <c r="AO29" s="10">
+        <f t="shared" ref="AO29:BC29" si="190">AO18/AO3</f>
+        <v>8.1190587501948117E-2</v>
+      </c>
+      <c r="AP29" s="10">
         <f t="shared" si="190"/>
-        <v>0.14391703903549444</v>
-      </c>
-      <c r="AK29" s="10">
+        <v>9.2421905820751049E-2</v>
+      </c>
+      <c r="AQ29" s="10">
         <f t="shared" si="190"/>
-        <v>0.17057096705428421</v>
-      </c>
-      <c r="AL29" s="10">
+        <v>0.15054775186504479</v>
+      </c>
+      <c r="AR29" s="10">
         <f t="shared" si="190"/>
-        <v>0.10356553554570926</v>
-      </c>
-      <c r="AO29" s="10">
-        <f t="shared" ref="AO29:BC29" si="191">AO18/AO3</f>
-        <v>8.1190587501948117E-2</v>
-      </c>
-      <c r="AP29" s="10">
+        <v>0.18037812006168713</v>
+      </c>
+      <c r="AS29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.1180033569291396</v>
+      </c>
+      <c r="AT29" s="10">
+        <f t="shared" si="190"/>
+        <v>8.0327832734803775E-2</v>
+      </c>
+      <c r="AU29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14237524717924868</v>
+      </c>
+      <c r="AV29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.13864190212737929</v>
+      </c>
+      <c r="AW29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14101222188978607</v>
+      </c>
+      <c r="AX29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14699481722847133</v>
+      </c>
+      <c r="AY29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14697312371100588</v>
+      </c>
+      <c r="AZ29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14699913420767935</v>
+      </c>
+      <c r="BA29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.1470248896994836</v>
+      </c>
+      <c r="BB29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14705039268646619</v>
+      </c>
+      <c r="BC29" s="10">
+        <f t="shared" si="190"/>
+        <v>0.14707564564416459</v>
+      </c>
+      <c r="BD29" s="10">
+        <f t="shared" ref="BD29:BF29" si="191">BD18/BD3</f>
+        <v>0.14710065102384637</v>
+      </c>
+      <c r="BE29" s="10">
         <f t="shared" si="191"/>
-        <v>9.2421905820751049E-2</v>
-      </c>
-      <c r="AQ29" s="10">
+        <v>0.14712541125274697</v>
+      </c>
+      <c r="BF29" s="10">
         <f t="shared" si="191"/>
-        <v>0.15054775186504479</v>
-      </c>
-      <c r="AR29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.18037812006168713</v>
-      </c>
-      <c r="AS29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.1180033569291396</v>
-      </c>
-      <c r="AT29" s="10">
-        <f t="shared" si="191"/>
-        <v>8.0327832734803775E-2</v>
-      </c>
-      <c r="AU29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.14237524717924868</v>
-      </c>
-      <c r="AV29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.13864190212737929</v>
-      </c>
-      <c r="AW29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.13891589889336892</v>
-      </c>
-      <c r="AX29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15387950878899742</v>
-      </c>
-      <c r="AY29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15386196151510556</v>
-      </c>
-      <c r="AZ29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15389220147109589</v>
-      </c>
-      <c r="BA29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15392214495692963</v>
-      </c>
-      <c r="BB29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15395179487917668</v>
-      </c>
-      <c r="BC29" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15398115411591143</v>
-      </c>
-      <c r="BD29" s="10">
-        <f t="shared" ref="BD29:BF29" si="192">BD18/BD3</f>
-        <v>0.15401022551699203</v>
-      </c>
-      <c r="BE29" s="10">
-        <f t="shared" si="192"/>
-        <v>0.15403901190433655</v>
-      </c>
-      <c r="BF29" s="10">
-        <f t="shared" si="192"/>
-        <v>0.15406751607219724</v>
+        <v>0.14714992873430538</v>
       </c>
       <c r="BH29" t="s">
         <v>60</v>
       </c>
       <c r="BI29" s="5">
         <f>BI28/BC19</f>
-        <v>77.648167163652317</v>
+        <v>71.51169386632769</v>
       </c>
     </row>
     <row r="30" spans="2:168" x14ac:dyDescent="0.3">
@@ -6967,7 +6961,7 @@
       </c>
       <c r="BI30" s="5">
         <f>Main!D3</f>
-        <v>115.3</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="31" spans="2:168" x14ac:dyDescent="0.3">
@@ -6976,7 +6970,7 @@
       </c>
       <c r="BI31" s="11">
         <f>BI29/BI30-1</f>
-        <v>-0.32655535851125483</v>
+        <v>-0.18893394730262347</v>
       </c>
     </row>
     <row r="32" spans="2:168" x14ac:dyDescent="0.3">
